--- a/geonet_dimensionering_v1_3.xlsx
+++ b/geonet_dimensionering_v1_3.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://byggrosas.sharepoint.com/sites/Byg/Shared Documents/General/Personlige mapper/BDK/Dan Strand/Beregningsværktøj/geonet_beregning/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="11" documentId="8_{5B9A1539-7CDC-44A7-9F96-1AE74EB52AFD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{DD60B5B7-29EF-44D1-81A3-5B91246C3C6E}"/>
+  <xr:revisionPtr revIDLastSave="13" documentId="8_{5B9A1539-7CDC-44A7-9F96-1AE74EB52AFD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{0C7A7299-167C-494C-A77A-EF56C70B27A5}"/>
   <bookViews>
-    <workbookView xWindow="-105" yWindow="0" windowWidth="14610" windowHeight="17385" tabRatio="790" firstSheet="3" activeTab="7" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="28680" yWindow="-165" windowWidth="29040" windowHeight="15720" tabRatio="790" firstSheet="3" activeTab="5" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Claude Log" sheetId="1" state="hidden" r:id="rId1"/>
@@ -1016,9 +1016,6 @@
     <t>Bundlag, friktionsmateriale</t>
   </si>
   <si>
-    <t>Bundgrus 0-80</t>
-  </si>
-  <si>
     <t>SG I 0-32</t>
   </si>
   <si>
@@ -1866,6 +1863,9 @@
   </si>
   <si>
     <t>Eu 2 lag</t>
+  </si>
+  <si>
+    <t>Bundgrus 0-8</t>
   </si>
 </sst>
 </file>
@@ -2838,64 +2838,76 @@
     <xf numFmtId="0" fontId="6" fillId="20" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="6" fillId="7" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="3" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="2" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="4" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="34" fillId="15" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="35" fillId="16" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="9" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="2" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="3" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="7" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" indent="1"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="13" fillId="8" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="29" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="28" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="26" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="16" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="21" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="10" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="10" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
@@ -2905,26 +2917,17 @@
     <xf numFmtId="0" fontId="3" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="20" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    <xf numFmtId="0" fontId="13" fillId="8" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="26" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="28" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="29" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="14" fillId="13" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="7" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="9" fillId="2" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -2932,20 +2935,17 @@
     <xf numFmtId="0" fontId="9" fillId="2" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="37" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="38" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="39" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" indent="1"/>
     </xf>
     <xf numFmtId="0" fontId="40" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="41" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="6" fillId="7" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="39" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="37" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -5637,16 +5637,16 @@
         <v>46165</v>
       </c>
       <c r="C4" t="s">
+        <v>515</v>
+      </c>
+      <c r="D4" t="s">
         <v>516</v>
       </c>
-      <c r="D4" t="s">
+      <c r="E4" t="s">
         <v>517</v>
       </c>
-      <c r="E4" t="s">
+      <c r="F4" t="s">
         <v>518</v>
-      </c>
-      <c r="F4" t="s">
-        <v>519</v>
       </c>
     </row>
     <row r="5" spans="1:6" x14ac:dyDescent="0.25">
@@ -5657,16 +5657,16 @@
         <v>46165</v>
       </c>
       <c r="C5" t="s">
+        <v>519</v>
+      </c>
+      <c r="D5" t="s">
         <v>520</v>
       </c>
-      <c r="D5" t="s">
+      <c r="E5" t="s">
         <v>521</v>
       </c>
-      <c r="E5" t="s">
+      <c r="F5" t="s">
         <v>522</v>
-      </c>
-      <c r="F5" t="s">
-        <v>523</v>
       </c>
     </row>
     <row r="6" spans="1:6" x14ac:dyDescent="0.25">
@@ -5677,16 +5677,16 @@
         <v>46165</v>
       </c>
       <c r="C6" t="s">
+        <v>523</v>
+      </c>
+      <c r="D6" t="s">
         <v>524</v>
       </c>
-      <c r="D6" t="s">
+      <c r="E6" t="s">
         <v>525</v>
       </c>
-      <c r="E6" t="s">
+      <c r="F6" t="s">
         <v>526</v>
-      </c>
-      <c r="F6" t="s">
-        <v>527</v>
       </c>
     </row>
     <row r="7" spans="1:6" x14ac:dyDescent="0.25">
@@ -5697,16 +5697,16 @@
         <v>46165</v>
       </c>
       <c r="C7" t="s">
+        <v>527</v>
+      </c>
+      <c r="D7" t="s">
         <v>528</v>
       </c>
-      <c r="D7" t="s">
+      <c r="E7" t="s">
         <v>529</v>
       </c>
-      <c r="E7" t="s">
+      <c r="F7" t="s">
         <v>530</v>
-      </c>
-      <c r="F7" t="s">
-        <v>531</v>
       </c>
     </row>
     <row r="8" spans="1:6" x14ac:dyDescent="0.25">
@@ -5717,16 +5717,16 @@
         <v>46165</v>
       </c>
       <c r="C8" t="s">
+        <v>531</v>
+      </c>
+      <c r="D8" t="s">
         <v>532</v>
       </c>
-      <c r="D8" t="s">
+      <c r="E8" t="s">
         <v>533</v>
       </c>
-      <c r="E8" t="s">
+      <c r="F8" t="s">
         <v>534</v>
-      </c>
-      <c r="F8" t="s">
-        <v>535</v>
       </c>
     </row>
     <row r="9" spans="1:6" x14ac:dyDescent="0.25">
@@ -5737,16 +5737,16 @@
         <v>46165</v>
       </c>
       <c r="C9" t="s">
+        <v>535</v>
+      </c>
+      <c r="D9" t="s">
         <v>536</v>
       </c>
-      <c r="D9" t="s">
+      <c r="E9" t="s">
         <v>537</v>
       </c>
-      <c r="E9" t="s">
+      <c r="F9" t="s">
         <v>538</v>
-      </c>
-      <c r="F9" t="s">
-        <v>539</v>
       </c>
     </row>
     <row r="10" spans="1:6" x14ac:dyDescent="0.25">
@@ -5757,16 +5757,16 @@
         <v>46165</v>
       </c>
       <c r="C10" t="s">
+        <v>541</v>
+      </c>
+      <c r="D10" t="s">
         <v>542</v>
       </c>
-      <c r="D10" t="s">
+      <c r="E10" t="s">
         <v>543</v>
       </c>
-      <c r="E10" t="s">
+      <c r="F10" t="s">
         <v>544</v>
-      </c>
-      <c r="F10" t="s">
-        <v>545</v>
       </c>
     </row>
     <row r="11" spans="1:6" x14ac:dyDescent="0.25">
@@ -5777,16 +5777,16 @@
         <v>46165</v>
       </c>
       <c r="C11" t="s">
+        <v>546</v>
+      </c>
+      <c r="D11" t="s">
         <v>547</v>
       </c>
-      <c r="D11" t="s">
+      <c r="E11" t="s">
         <v>548</v>
       </c>
-      <c r="E11" t="s">
+      <c r="F11" t="s">
         <v>549</v>
-      </c>
-      <c r="F11" t="s">
-        <v>550</v>
       </c>
     </row>
     <row r="12" spans="1:6" x14ac:dyDescent="0.25">
@@ -5797,16 +5797,16 @@
         <v>46168</v>
       </c>
       <c r="C12" t="s">
+        <v>551</v>
+      </c>
+      <c r="D12" t="s">
         <v>552</v>
       </c>
-      <c r="D12" t="s">
+      <c r="E12" t="s">
         <v>553</v>
       </c>
-      <c r="E12" t="s">
+      <c r="F12" t="s">
         <v>554</v>
-      </c>
-      <c r="F12" t="s">
-        <v>555</v>
       </c>
     </row>
     <row r="13" spans="1:6" x14ac:dyDescent="0.25">
@@ -5817,16 +5817,16 @@
         <v>46168</v>
       </c>
       <c r="C13" t="s">
+        <v>555</v>
+      </c>
+      <c r="D13" t="s">
         <v>556</v>
       </c>
-      <c r="D13" t="s">
+      <c r="E13" t="s">
         <v>557</v>
       </c>
-      <c r="E13" t="s">
+      <c r="F13" t="s">
         <v>558</v>
-      </c>
-      <c r="F13" t="s">
-        <v>559</v>
       </c>
     </row>
     <row r="14" spans="1:6" x14ac:dyDescent="0.25">
@@ -5837,16 +5837,16 @@
         <v>46168</v>
       </c>
       <c r="C14" t="s">
+        <v>560</v>
+      </c>
+      <c r="D14" t="s">
         <v>561</v>
       </c>
-      <c r="D14" t="s">
+      <c r="E14" t="s">
         <v>562</v>
       </c>
-      <c r="E14" t="s">
+      <c r="F14" t="s">
         <v>563</v>
-      </c>
-      <c r="F14" t="s">
-        <v>564</v>
       </c>
     </row>
     <row r="15" spans="1:6" x14ac:dyDescent="0.25">
@@ -5857,16 +5857,16 @@
         <v>46171</v>
       </c>
       <c r="C15" t="s">
+        <v>577</v>
+      </c>
+      <c r="D15" t="s">
         <v>578</v>
       </c>
-      <c r="D15" t="s">
+      <c r="E15" t="s">
         <v>579</v>
       </c>
-      <c r="E15" t="s">
+      <c r="F15" t="s">
         <v>580</v>
-      </c>
-      <c r="F15" t="s">
-        <v>581</v>
       </c>
     </row>
     <row r="16" spans="1:6" x14ac:dyDescent="0.25">
@@ -5877,16 +5877,16 @@
         <v>46181</v>
       </c>
       <c r="C16" t="s">
+        <v>581</v>
+      </c>
+      <c r="D16" t="s">
         <v>582</v>
       </c>
-      <c r="D16" t="s">
+      <c r="E16" t="s">
         <v>583</v>
       </c>
-      <c r="E16" t="s">
+      <c r="F16" t="s">
         <v>584</v>
-      </c>
-      <c r="F16" t="s">
-        <v>585</v>
       </c>
     </row>
     <row r="17" spans="1:6" x14ac:dyDescent="0.25">
@@ -5897,16 +5897,16 @@
         <v>46181</v>
       </c>
       <c r="C17" t="s">
+        <v>585</v>
+      </c>
+      <c r="D17" t="s">
         <v>586</v>
       </c>
-      <c r="D17" t="s">
+      <c r="E17" t="s">
         <v>587</v>
       </c>
-      <c r="E17" t="s">
+      <c r="F17" t="s">
         <v>588</v>
-      </c>
-      <c r="F17" t="s">
-        <v>589</v>
       </c>
     </row>
   </sheetData>
@@ -5938,270 +5938,270 @@
   </cols>
   <sheetData>
     <row r="2" spans="2:8" ht="27.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B2" s="135" t="s">
+      <c r="B2" s="144" t="s">
         <v>14</v>
       </c>
-      <c r="C2" s="135"/>
-      <c r="D2" s="135"/>
-      <c r="E2" s="135"/>
-      <c r="F2" s="135"/>
-      <c r="G2" s="135"/>
-      <c r="H2" s="135"/>
+      <c r="C2" s="144"/>
+      <c r="D2" s="144"/>
+      <c r="E2" s="144"/>
+      <c r="F2" s="144"/>
+      <c r="G2" s="144"/>
+      <c r="H2" s="144"/>
     </row>
     <row r="4" spans="2:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B4" s="147" t="s">
+      <c r="B4" s="155" t="s">
         <v>15</v>
       </c>
-      <c r="C4" s="147"/>
-      <c r="D4" s="147"/>
-      <c r="E4" s="147"/>
-      <c r="F4" s="147"/>
-      <c r="G4" s="147"/>
-      <c r="H4" s="147"/>
+      <c r="C4" s="155"/>
+      <c r="D4" s="155"/>
+      <c r="E4" s="155"/>
+      <c r="F4" s="155"/>
+      <c r="G4" s="155"/>
+      <c r="H4" s="155"/>
     </row>
     <row r="6" spans="2:8" ht="24.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B6" s="148" t="s">
+      <c r="B6" s="154" t="s">
         <v>16</v>
       </c>
-      <c r="C6" s="148"/>
-      <c r="D6" s="148"/>
-      <c r="E6" s="148"/>
-      <c r="F6" s="148"/>
-      <c r="G6" s="148"/>
-      <c r="H6" s="148"/>
+      <c r="C6" s="154"/>
+      <c r="D6" s="154"/>
+      <c r="E6" s="154"/>
+      <c r="F6" s="154"/>
+      <c r="G6" s="154"/>
+      <c r="H6" s="154"/>
     </row>
     <row r="7" spans="2:8" ht="24.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B7" s="148"/>
-      <c r="C7" s="148"/>
-      <c r="D7" s="148"/>
-      <c r="E7" s="148"/>
-      <c r="F7" s="148"/>
-      <c r="G7" s="148"/>
-      <c r="H7" s="148"/>
+      <c r="B7" s="154"/>
+      <c r="C7" s="154"/>
+      <c r="D7" s="154"/>
+      <c r="E7" s="154"/>
+      <c r="F7" s="154"/>
+      <c r="G7" s="154"/>
+      <c r="H7" s="154"/>
     </row>
     <row r="8" spans="2:8" ht="24.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B8" s="148"/>
-      <c r="C8" s="148"/>
-      <c r="D8" s="148"/>
-      <c r="E8" s="148"/>
-      <c r="F8" s="148"/>
-      <c r="G8" s="148"/>
-      <c r="H8" s="148"/>
+      <c r="B8" s="154"/>
+      <c r="C8" s="154"/>
+      <c r="D8" s="154"/>
+      <c r="E8" s="154"/>
+      <c r="F8" s="154"/>
+      <c r="G8" s="154"/>
+      <c r="H8" s="154"/>
     </row>
     <row r="10" spans="2:8" ht="21.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B10" s="149" t="s">
+      <c r="B10" s="151" t="s">
         <v>17</v>
       </c>
-      <c r="C10" s="149"/>
-      <c r="D10" s="149"/>
-      <c r="E10" s="149"/>
-      <c r="F10" s="149"/>
-      <c r="G10" s="149"/>
-      <c r="H10" s="149"/>
+      <c r="C10" s="151"/>
+      <c r="D10" s="151"/>
+      <c r="E10" s="151"/>
+      <c r="F10" s="151"/>
+      <c r="G10" s="151"/>
+      <c r="H10" s="151"/>
     </row>
     <row r="12" spans="2:8" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B12" s="8" t="s">
         <v>18</v>
       </c>
-      <c r="C12" s="148" t="s">
+      <c r="C12" s="154" t="s">
         <v>19</v>
       </c>
-      <c r="D12" s="148"/>
-      <c r="E12" s="148"/>
-      <c r="F12" s="148"/>
-      <c r="G12" s="148"/>
-      <c r="H12" s="148"/>
+      <c r="D12" s="154"/>
+      <c r="E12" s="154"/>
+      <c r="F12" s="154"/>
+      <c r="G12" s="154"/>
+      <c r="H12" s="154"/>
     </row>
     <row r="13" spans="2:8" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B13" s="8" t="s">
         <v>20</v>
       </c>
-      <c r="C13" s="148" t="s">
+      <c r="C13" s="154" t="s">
         <v>21</v>
       </c>
-      <c r="D13" s="148"/>
-      <c r="E13" s="148"/>
-      <c r="F13" s="148"/>
-      <c r="G13" s="148"/>
-      <c r="H13" s="148"/>
+      <c r="D13" s="154"/>
+      <c r="E13" s="154"/>
+      <c r="F13" s="154"/>
+      <c r="G13" s="154"/>
+      <c r="H13" s="154"/>
     </row>
     <row r="14" spans="2:8" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B14" s="8" t="s">
         <v>22</v>
       </c>
-      <c r="C14" s="148" t="s">
+      <c r="C14" s="154" t="s">
         <v>23</v>
       </c>
-      <c r="D14" s="148"/>
-      <c r="E14" s="148"/>
-      <c r="F14" s="148"/>
-      <c r="G14" s="148"/>
-      <c r="H14" s="148"/>
+      <c r="D14" s="154"/>
+      <c r="E14" s="154"/>
+      <c r="F14" s="154"/>
+      <c r="G14" s="154"/>
+      <c r="H14" s="154"/>
     </row>
     <row r="15" spans="2:8" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B15" s="8" t="s">
         <v>24</v>
       </c>
-      <c r="C15" s="148" t="s">
+      <c r="C15" s="154" t="s">
         <v>25</v>
       </c>
-      <c r="D15" s="148"/>
-      <c r="E15" s="148"/>
-      <c r="F15" s="148"/>
-      <c r="G15" s="148"/>
-      <c r="H15" s="148"/>
+      <c r="D15" s="154"/>
+      <c r="E15" s="154"/>
+      <c r="F15" s="154"/>
+      <c r="G15" s="154"/>
+      <c r="H15" s="154"/>
     </row>
     <row r="16" spans="2:8" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B16" s="8" t="s">
         <v>26</v>
       </c>
-      <c r="C16" s="148" t="s">
+      <c r="C16" s="154" t="s">
         <v>27</v>
       </c>
-      <c r="D16" s="148"/>
-      <c r="E16" s="148"/>
-      <c r="F16" s="148"/>
-      <c r="G16" s="148"/>
-      <c r="H16" s="148"/>
+      <c r="D16" s="154"/>
+      <c r="E16" s="154"/>
+      <c r="F16" s="154"/>
+      <c r="G16" s="154"/>
+      <c r="H16" s="154"/>
     </row>
     <row r="17" spans="2:8" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B17" s="8" t="s">
         <v>28</v>
       </c>
-      <c r="C17" s="148" t="s">
+      <c r="C17" s="154" t="s">
         <v>29</v>
       </c>
-      <c r="D17" s="148"/>
-      <c r="E17" s="148"/>
-      <c r="F17" s="148"/>
-      <c r="G17" s="148"/>
-      <c r="H17" s="148"/>
+      <c r="D17" s="154"/>
+      <c r="E17" s="154"/>
+      <c r="F17" s="154"/>
+      <c r="G17" s="154"/>
+      <c r="H17" s="154"/>
     </row>
     <row r="18" spans="2:8" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B18" s="8" t="s">
         <v>30</v>
       </c>
-      <c r="C18" s="148" t="s">
+      <c r="C18" s="154" t="s">
         <v>31</v>
       </c>
-      <c r="D18" s="148"/>
-      <c r="E18" s="148"/>
-      <c r="F18" s="148"/>
-      <c r="G18" s="148"/>
-      <c r="H18" s="148"/>
+      <c r="D18" s="154"/>
+      <c r="E18" s="154"/>
+      <c r="F18" s="154"/>
+      <c r="G18" s="154"/>
+      <c r="H18" s="154"/>
     </row>
     <row r="19" spans="2:8" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B19" s="8" t="s">
         <v>32</v>
       </c>
-      <c r="C19" s="148" t="s">
+      <c r="C19" s="154" t="s">
         <v>33</v>
       </c>
-      <c r="D19" s="148"/>
-      <c r="E19" s="148"/>
-      <c r="F19" s="148"/>
-      <c r="G19" s="148"/>
-      <c r="H19" s="148"/>
+      <c r="D19" s="154"/>
+      <c r="E19" s="154"/>
+      <c r="F19" s="154"/>
+      <c r="G19" s="154"/>
+      <c r="H19" s="154"/>
     </row>
     <row r="21" spans="2:8" ht="21.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B21" s="149" t="s">
+      <c r="B21" s="151" t="s">
         <v>34</v>
       </c>
-      <c r="C21" s="149"/>
-      <c r="D21" s="149"/>
-      <c r="E21" s="149"/>
-      <c r="F21" s="149"/>
-      <c r="G21" s="149"/>
-      <c r="H21" s="149"/>
+      <c r="C21" s="151"/>
+      <c r="D21" s="151"/>
+      <c r="E21" s="151"/>
+      <c r="F21" s="151"/>
+      <c r="G21" s="151"/>
+      <c r="H21" s="151"/>
     </row>
     <row r="22" spans="2:8" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B22" s="9" t="s">
         <v>35</v>
       </c>
-      <c r="C22" s="148" t="s">
+      <c r="C22" s="154" t="s">
         <v>36</v>
       </c>
-      <c r="D22" s="148"/>
-      <c r="E22" s="148"/>
-      <c r="F22" s="148"/>
-      <c r="G22" s="148"/>
-      <c r="H22" s="148"/>
+      <c r="D22" s="154"/>
+      <c r="E22" s="154"/>
+      <c r="F22" s="154"/>
+      <c r="G22" s="154"/>
+      <c r="H22" s="154"/>
     </row>
     <row r="23" spans="2:8" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B23" s="9" t="s">
         <v>35</v>
       </c>
-      <c r="C23" s="148" t="s">
+      <c r="C23" s="154" t="s">
         <v>37</v>
       </c>
-      <c r="D23" s="148"/>
-      <c r="E23" s="148"/>
-      <c r="F23" s="148"/>
-      <c r="G23" s="148"/>
-      <c r="H23" s="148"/>
+      <c r="D23" s="154"/>
+      <c r="E23" s="154"/>
+      <c r="F23" s="154"/>
+      <c r="G23" s="154"/>
+      <c r="H23" s="154"/>
     </row>
     <row r="24" spans="2:8" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B24" s="9" t="s">
         <v>35</v>
       </c>
-      <c r="C24" s="148" t="s">
+      <c r="C24" s="154" t="s">
         <v>38</v>
       </c>
-      <c r="D24" s="148"/>
-      <c r="E24" s="148"/>
-      <c r="F24" s="148"/>
-      <c r="G24" s="148"/>
-      <c r="H24" s="148"/>
+      <c r="D24" s="154"/>
+      <c r="E24" s="154"/>
+      <c r="F24" s="154"/>
+      <c r="G24" s="154"/>
+      <c r="H24" s="154"/>
     </row>
     <row r="25" spans="2:8" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B25" s="9" t="s">
         <v>35</v>
       </c>
-      <c r="C25" s="148" t="s">
+      <c r="C25" s="154" t="s">
         <v>39</v>
       </c>
-      <c r="D25" s="148"/>
-      <c r="E25" s="148"/>
-      <c r="F25" s="148"/>
-      <c r="G25" s="148"/>
-      <c r="H25" s="148"/>
+      <c r="D25" s="154"/>
+      <c r="E25" s="154"/>
+      <c r="F25" s="154"/>
+      <c r="G25" s="154"/>
+      <c r="H25" s="154"/>
     </row>
     <row r="26" spans="2:8" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B26" s="9" t="s">
         <v>35</v>
       </c>
-      <c r="C26" s="148" t="s">
+      <c r="C26" s="154" t="s">
         <v>40</v>
       </c>
-      <c r="D26" s="148"/>
-      <c r="E26" s="148"/>
-      <c r="F26" s="148"/>
-      <c r="G26" s="148"/>
-      <c r="H26" s="148"/>
+      <c r="D26" s="154"/>
+      <c r="E26" s="154"/>
+      <c r="F26" s="154"/>
+      <c r="G26" s="154"/>
+      <c r="H26" s="154"/>
     </row>
     <row r="27" spans="2:8" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B27" s="9" t="s">
         <v>35</v>
       </c>
-      <c r="C27" s="148" t="s">
+      <c r="C27" s="154" t="s">
         <v>41</v>
       </c>
-      <c r="D27" s="148"/>
-      <c r="E27" s="148"/>
-      <c r="F27" s="148"/>
-      <c r="G27" s="148"/>
-      <c r="H27" s="148"/>
+      <c r="D27" s="154"/>
+      <c r="E27" s="154"/>
+      <c r="F27" s="154"/>
+      <c r="G27" s="154"/>
+      <c r="H27" s="154"/>
     </row>
     <row r="29" spans="2:8" ht="21.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B29" s="149" t="s">
+      <c r="B29" s="151" t="s">
         <v>42</v>
       </c>
-      <c r="C29" s="149"/>
-      <c r="D29" s="149"/>
-      <c r="E29" s="149"/>
-      <c r="F29" s="149"/>
-      <c r="G29" s="149"/>
-      <c r="H29" s="149"/>
+      <c r="C29" s="151"/>
+      <c r="D29" s="151"/>
+      <c r="E29" s="151"/>
+      <c r="F29" s="151"/>
+      <c r="G29" s="151"/>
+      <c r="H29" s="151"/>
     </row>
     <row r="30" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B30" s="10" t="s">
@@ -6212,9 +6212,9 @@
       </c>
       <c r="D30" s="150"/>
       <c r="E30" s="150"/>
-      <c r="F30" s="151"/>
-      <c r="G30" s="151"/>
-      <c r="H30" s="151"/>
+      <c r="F30" s="153"/>
+      <c r="G30" s="153"/>
+      <c r="H30" s="153"/>
     </row>
     <row r="31" spans="2:8" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B31" s="11" t="s">
@@ -6225,11 +6225,11 @@
       </c>
       <c r="D31" s="152"/>
       <c r="E31" s="152"/>
-      <c r="F31" s="146" t="s">
+      <c r="F31" s="136" t="s">
         <v>47</v>
       </c>
-      <c r="G31" s="146"/>
-      <c r="H31" s="146"/>
+      <c r="G31" s="136"/>
+      <c r="H31" s="136"/>
     </row>
     <row r="32" spans="2:8" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B32" s="11" t="s">
@@ -6240,11 +6240,11 @@
       </c>
       <c r="D32" s="152"/>
       <c r="E32" s="152"/>
-      <c r="F32" s="146" t="s">
+      <c r="F32" s="136" t="s">
         <v>50</v>
       </c>
-      <c r="G32" s="146"/>
-      <c r="H32" s="146"/>
+      <c r="G32" s="136"/>
+      <c r="H32" s="136"/>
     </row>
     <row r="33" spans="2:8" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B33" s="11" t="s">
@@ -6255,11 +6255,11 @@
       </c>
       <c r="D33" s="152"/>
       <c r="E33" s="152"/>
-      <c r="F33" s="146" t="s">
+      <c r="F33" s="136" t="s">
         <v>53</v>
       </c>
-      <c r="G33" s="146"/>
-      <c r="H33" s="146"/>
+      <c r="G33" s="136"/>
+      <c r="H33" s="136"/>
     </row>
     <row r="34" spans="2:8" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B34" s="11" t="s">
@@ -6270,22 +6270,22 @@
       </c>
       <c r="D34" s="152"/>
       <c r="E34" s="152"/>
-      <c r="F34" s="146" t="s">
+      <c r="F34" s="136" t="s">
         <v>56</v>
       </c>
-      <c r="G34" s="146"/>
-      <c r="H34" s="146"/>
+      <c r="G34" s="136"/>
+      <c r="H34" s="136"/>
     </row>
     <row r="36" spans="2:8" ht="21.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B36" s="149" t="s">
+      <c r="B36" s="151" t="s">
         <v>57</v>
       </c>
-      <c r="C36" s="149"/>
-      <c r="D36" s="149"/>
-      <c r="E36" s="149"/>
-      <c r="F36" s="149"/>
-      <c r="G36" s="149"/>
-      <c r="H36" s="149"/>
+      <c r="C36" s="151"/>
+      <c r="D36" s="151"/>
+      <c r="E36" s="151"/>
+      <c r="F36" s="151"/>
+      <c r="G36" s="151"/>
+      <c r="H36" s="151"/>
     </row>
     <row r="37" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B37" s="10" t="s">
@@ -6309,171 +6309,171 @@
       <c r="C38" s="12" t="s">
         <v>61</v>
       </c>
-      <c r="D38" s="146" t="s">
+      <c r="D38" s="136" t="s">
         <v>62</v>
       </c>
-      <c r="E38" s="146"/>
-      <c r="F38" s="146"/>
-      <c r="G38" s="146"/>
-      <c r="H38" s="146"/>
+      <c r="E38" s="136"/>
+      <c r="F38" s="136"/>
+      <c r="G38" s="136"/>
+      <c r="H38" s="136"/>
     </row>
     <row r="40" spans="2:8" ht="21.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B40" s="149" t="s">
+      <c r="B40" s="151" t="s">
         <v>63</v>
       </c>
-      <c r="C40" s="149"/>
-      <c r="D40" s="149"/>
-      <c r="E40" s="149"/>
-      <c r="F40" s="149"/>
-      <c r="G40" s="149"/>
-      <c r="H40" s="149"/>
+      <c r="C40" s="151"/>
+      <c r="D40" s="151"/>
+      <c r="E40" s="151"/>
+      <c r="F40" s="151"/>
+      <c r="G40" s="151"/>
+      <c r="H40" s="151"/>
     </row>
     <row r="41" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B41" s="14" t="s">
         <v>64</v>
       </c>
-      <c r="C41" s="153" t="s">
+      <c r="C41" s="149" t="s">
         <v>65</v>
       </c>
-      <c r="D41" s="153"/>
-      <c r="E41" s="153"/>
-      <c r="F41" s="153"/>
-      <c r="G41" s="153"/>
-      <c r="H41" s="153"/>
+      <c r="D41" s="149"/>
+      <c r="E41" s="149"/>
+      <c r="F41" s="149"/>
+      <c r="G41" s="149"/>
+      <c r="H41" s="149"/>
     </row>
     <row r="42" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B42" s="16" t="s">
         <v>66</v>
       </c>
-      <c r="C42" s="153" t="s">
+      <c r="C42" s="149" t="s">
         <v>67</v>
       </c>
-      <c r="D42" s="153"/>
-      <c r="E42" s="153"/>
-      <c r="F42" s="153"/>
-      <c r="G42" s="153"/>
-      <c r="H42" s="153"/>
+      <c r="D42" s="149"/>
+      <c r="E42" s="149"/>
+      <c r="F42" s="149"/>
+      <c r="G42" s="149"/>
+      <c r="H42" s="149"/>
     </row>
     <row r="43" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B43" s="17" t="s">
         <v>68</v>
       </c>
-      <c r="C43" s="153" t="s">
+      <c r="C43" s="149" t="s">
         <v>69</v>
       </c>
-      <c r="D43" s="153"/>
-      <c r="E43" s="153"/>
-      <c r="F43" s="153"/>
-      <c r="G43" s="153"/>
-      <c r="H43" s="153"/>
+      <c r="D43" s="149"/>
+      <c r="E43" s="149"/>
+      <c r="F43" s="149"/>
+      <c r="G43" s="149"/>
+      <c r="H43" s="149"/>
     </row>
     <row r="44" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B44" s="18" t="s">
         <v>70</v>
       </c>
-      <c r="C44" s="153" t="s">
+      <c r="C44" s="149" t="s">
         <v>71</v>
       </c>
-      <c r="D44" s="153"/>
-      <c r="E44" s="153"/>
-      <c r="F44" s="153"/>
-      <c r="G44" s="153"/>
-      <c r="H44" s="153"/>
+      <c r="D44" s="149"/>
+      <c r="E44" s="149"/>
+      <c r="F44" s="149"/>
+      <c r="G44" s="149"/>
+      <c r="H44" s="149"/>
     </row>
     <row r="45" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B45" s="19" t="s">
         <v>72</v>
       </c>
-      <c r="C45" s="153" t="s">
+      <c r="C45" s="149" t="s">
         <v>73</v>
       </c>
-      <c r="D45" s="153"/>
-      <c r="E45" s="153"/>
-      <c r="F45" s="153"/>
-      <c r="G45" s="153"/>
-      <c r="H45" s="153"/>
+      <c r="D45" s="149"/>
+      <c r="E45" s="149"/>
+      <c r="F45" s="149"/>
+      <c r="G45" s="149"/>
+      <c r="H45" s="149"/>
     </row>
     <row r="46" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B46" s="20" t="s">
         <v>74</v>
       </c>
-      <c r="C46" s="153" t="s">
+      <c r="C46" s="149" t="s">
         <v>75</v>
       </c>
-      <c r="D46" s="153"/>
-      <c r="E46" s="153"/>
-      <c r="F46" s="153"/>
-      <c r="G46" s="153"/>
-      <c r="H46" s="153"/>
+      <c r="D46" s="149"/>
+      <c r="E46" s="149"/>
+      <c r="F46" s="149"/>
+      <c r="G46" s="149"/>
+      <c r="H46" s="149"/>
     </row>
     <row r="47" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B47" s="21" t="s">
         <v>76</v>
       </c>
-      <c r="C47" s="153" t="s">
+      <c r="C47" s="149" t="s">
         <v>77</v>
       </c>
-      <c r="D47" s="153"/>
-      <c r="E47" s="153"/>
-      <c r="F47" s="153"/>
-      <c r="G47" s="153"/>
-      <c r="H47" s="153"/>
+      <c r="D47" s="149"/>
+      <c r="E47" s="149"/>
+      <c r="F47" s="149"/>
+      <c r="G47" s="149"/>
+      <c r="H47" s="149"/>
     </row>
     <row r="50" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B50" s="154" t="s">
+      <c r="B50" s="148" t="s">
         <v>78</v>
       </c>
-      <c r="C50" s="154"/>
-      <c r="D50" s="154"/>
-      <c r="E50" s="154"/>
-      <c r="F50" s="154"/>
-      <c r="G50" s="154"/>
-      <c r="H50" s="154"/>
+      <c r="C50" s="148"/>
+      <c r="D50" s="148"/>
+      <c r="E50" s="148"/>
+      <c r="F50" s="148"/>
+      <c r="G50" s="148"/>
+      <c r="H50" s="148"/>
     </row>
   </sheetData>
   <mergeCells count="42">
+    <mergeCell ref="B2:H2"/>
+    <mergeCell ref="B4:H4"/>
+    <mergeCell ref="B6:H8"/>
+    <mergeCell ref="B10:H10"/>
+    <mergeCell ref="C12:H12"/>
+    <mergeCell ref="C13:H13"/>
+    <mergeCell ref="C14:H14"/>
+    <mergeCell ref="C15:H15"/>
+    <mergeCell ref="C16:H16"/>
+    <mergeCell ref="C17:H17"/>
+    <mergeCell ref="C18:H18"/>
+    <mergeCell ref="C19:H19"/>
+    <mergeCell ref="B21:H21"/>
+    <mergeCell ref="C22:H22"/>
+    <mergeCell ref="C23:H23"/>
+    <mergeCell ref="C24:H24"/>
+    <mergeCell ref="C25:H25"/>
+    <mergeCell ref="C26:H26"/>
+    <mergeCell ref="C27:H27"/>
+    <mergeCell ref="B29:H29"/>
+    <mergeCell ref="C30:E30"/>
+    <mergeCell ref="F30:H30"/>
+    <mergeCell ref="C31:E31"/>
+    <mergeCell ref="F31:H31"/>
+    <mergeCell ref="C32:E32"/>
+    <mergeCell ref="F32:H32"/>
+    <mergeCell ref="C33:E33"/>
+    <mergeCell ref="F33:H33"/>
+    <mergeCell ref="C34:E34"/>
+    <mergeCell ref="F34:H34"/>
+    <mergeCell ref="B36:H36"/>
+    <mergeCell ref="D37:H37"/>
+    <mergeCell ref="D38:H38"/>
+    <mergeCell ref="B40:H40"/>
+    <mergeCell ref="C41:H41"/>
+    <mergeCell ref="C42:H42"/>
     <mergeCell ref="B50:H50"/>
     <mergeCell ref="C43:H43"/>
     <mergeCell ref="C44:H44"/>
     <mergeCell ref="C45:H45"/>
     <mergeCell ref="C46:H46"/>
     <mergeCell ref="C47:H47"/>
-    <mergeCell ref="D37:H37"/>
-    <mergeCell ref="D38:H38"/>
-    <mergeCell ref="B40:H40"/>
-    <mergeCell ref="C41:H41"/>
-    <mergeCell ref="C42:H42"/>
-    <mergeCell ref="C33:E33"/>
-    <mergeCell ref="F33:H33"/>
-    <mergeCell ref="C34:E34"/>
-    <mergeCell ref="F34:H34"/>
-    <mergeCell ref="B36:H36"/>
-    <mergeCell ref="C30:E30"/>
-    <mergeCell ref="F30:H30"/>
-    <mergeCell ref="C31:E31"/>
-    <mergeCell ref="F31:H31"/>
-    <mergeCell ref="C32:E32"/>
-    <mergeCell ref="F32:H32"/>
-    <mergeCell ref="C24:H24"/>
-    <mergeCell ref="C25:H25"/>
-    <mergeCell ref="C26:H26"/>
-    <mergeCell ref="C27:H27"/>
-    <mergeCell ref="B29:H29"/>
-    <mergeCell ref="C18:H18"/>
-    <mergeCell ref="C19:H19"/>
-    <mergeCell ref="B21:H21"/>
-    <mergeCell ref="C22:H22"/>
-    <mergeCell ref="C23:H23"/>
-    <mergeCell ref="C13:H13"/>
-    <mergeCell ref="C14:H14"/>
-    <mergeCell ref="C15:H15"/>
-    <mergeCell ref="C16:H16"/>
-    <mergeCell ref="C17:H17"/>
-    <mergeCell ref="B2:H2"/>
-    <mergeCell ref="B4:H4"/>
-    <mergeCell ref="B6:H8"/>
-    <mergeCell ref="B10:H10"/>
-    <mergeCell ref="C12:H12"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300"/>
@@ -6498,47 +6498,47 @@
   </cols>
   <sheetData>
     <row r="1" spans="2:14" ht="27.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B1" s="135" t="s">
+      <c r="B1" s="144" t="s">
         <v>79</v>
       </c>
-      <c r="C1" s="135"/>
-      <c r="D1" s="135"/>
-      <c r="E1" s="135"/>
-      <c r="F1" s="135"/>
-      <c r="G1" s="135"/>
-      <c r="H1" s="135"/>
-      <c r="I1" s="135"/>
-      <c r="J1" s="135"/>
+      <c r="C1" s="144"/>
+      <c r="D1" s="144"/>
+      <c r="E1" s="144"/>
+      <c r="F1" s="144"/>
+      <c r="G1" s="144"/>
+      <c r="H1" s="144"/>
+      <c r="I1" s="144"/>
+      <c r="J1" s="144"/>
     </row>
     <row r="3" spans="2:14" ht="27.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B3" s="137" t="s">
+      <c r="B3" s="138" t="s">
         <v>80</v>
       </c>
-      <c r="C3" s="137"/>
-      <c r="D3" s="137"/>
-      <c r="E3" s="137"/>
-      <c r="F3" s="137"/>
-      <c r="G3" s="137"/>
-      <c r="H3" s="137"/>
-      <c r="I3" s="137"/>
-      <c r="J3" s="137"/>
-      <c r="M3" s="155" t="s">
+      <c r="C3" s="138"/>
+      <c r="D3" s="138"/>
+      <c r="E3" s="138"/>
+      <c r="F3" s="138"/>
+      <c r="G3" s="138"/>
+      <c r="H3" s="138"/>
+      <c r="I3" s="138"/>
+      <c r="J3" s="138"/>
+      <c r="M3" s="170" t="s">
         <v>81</v>
       </c>
-      <c r="N3" s="155"/>
+      <c r="N3" s="170"/>
     </row>
     <row r="5" spans="2:14" ht="21.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B5" s="149" t="s">
+      <c r="B5" s="151" t="s">
         <v>82</v>
       </c>
-      <c r="C5" s="149"/>
-      <c r="D5" s="149"/>
-      <c r="E5" s="149"/>
-      <c r="F5" s="149"/>
-      <c r="G5" s="149"/>
-      <c r="H5" s="149"/>
-      <c r="I5" s="149"/>
-      <c r="J5" s="149"/>
+      <c r="C5" s="151"/>
+      <c r="D5" s="151"/>
+      <c r="E5" s="151"/>
+      <c r="F5" s="151"/>
+      <c r="G5" s="151"/>
+      <c r="H5" s="151"/>
+      <c r="I5" s="151"/>
+      <c r="J5" s="151"/>
       <c r="M5" s="2" t="s">
         <v>83</v>
       </c>
@@ -6548,17 +6548,17 @@
       </c>
     </row>
     <row r="6" spans="2:14" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B6" s="154" t="s">
+      <c r="B6" s="148" t="s">
         <v>84</v>
       </c>
-      <c r="C6" s="154"/>
-      <c r="D6" s="154"/>
-      <c r="E6" s="154"/>
-      <c r="F6" s="154"/>
-      <c r="G6" s="154"/>
-      <c r="H6" s="154"/>
-      <c r="I6" s="154"/>
-      <c r="J6" s="154"/>
+      <c r="C6" s="148"/>
+      <c r="D6" s="148"/>
+      <c r="E6" s="148"/>
+      <c r="F6" s="148"/>
+      <c r="G6" s="148"/>
+      <c r="H6" s="148"/>
+      <c r="I6" s="148"/>
+      <c r="J6" s="148"/>
       <c r="M6" s="2" t="s">
         <v>85</v>
       </c>
@@ -6572,7 +6572,7 @@
         <v>86</v>
       </c>
       <c r="C7" s="1" t="s">
-        <v>565</v>
+        <v>564</v>
       </c>
       <c r="M7" s="2" t="s">
         <v>87</v>
@@ -6589,15 +6589,15 @@
       <c r="C8" s="25">
         <v>54</v>
       </c>
-      <c r="D8" s="154" t="s">
+      <c r="D8" s="148" t="s">
         <v>89</v>
       </c>
-      <c r="E8" s="154"/>
-      <c r="F8" s="154"/>
-      <c r="G8" s="154"/>
-      <c r="H8" s="154"/>
-      <c r="I8" s="154"/>
-      <c r="J8" s="154"/>
+      <c r="E8" s="148"/>
+      <c r="F8" s="148"/>
+      <c r="G8" s="148"/>
+      <c r="H8" s="148"/>
+      <c r="I8" s="148"/>
+      <c r="J8" s="148"/>
       <c r="M8" s="2" t="s">
         <v>90</v>
       </c>
@@ -6613,15 +6613,15 @@
       <c r="C9" s="27">
         <v>10</v>
       </c>
-      <c r="D9" s="154" t="s">
+      <c r="D9" s="148" t="s">
         <v>92</v>
       </c>
-      <c r="E9" s="154"/>
-      <c r="F9" s="154"/>
-      <c r="G9" s="154"/>
-      <c r="H9" s="154"/>
-      <c r="I9" s="154"/>
-      <c r="J9" s="154"/>
+      <c r="E9" s="148"/>
+      <c r="F9" s="148"/>
+      <c r="G9" s="148"/>
+      <c r="H9" s="148"/>
+      <c r="I9" s="148"/>
+      <c r="J9" s="148"/>
     </row>
     <row r="10" spans="2:14" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B10" s="23" t="s">
@@ -6668,17 +6668,17 @@
       </c>
     </row>
     <row r="13" spans="2:14" ht="21.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B13" s="149" t="s">
+      <c r="B13" s="151" t="s">
         <v>99</v>
       </c>
-      <c r="C13" s="149"/>
-      <c r="D13" s="149"/>
-      <c r="E13" s="149"/>
-      <c r="F13" s="149"/>
-      <c r="G13" s="149"/>
-      <c r="H13" s="149"/>
-      <c r="I13" s="149"/>
-      <c r="J13" s="149"/>
+      <c r="C13" s="151"/>
+      <c r="D13" s="151"/>
+      <c r="E13" s="151"/>
+      <c r="F13" s="151"/>
+      <c r="G13" s="151"/>
+      <c r="H13" s="151"/>
+      <c r="I13" s="151"/>
+      <c r="J13" s="151"/>
       <c r="M13" s="2" t="s">
         <v>100</v>
       </c>
@@ -6688,17 +6688,17 @@
       </c>
     </row>
     <row r="14" spans="2:14" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B14" s="154" t="s">
+      <c r="B14" s="148" t="s">
         <v>101</v>
       </c>
-      <c r="C14" s="154"/>
-      <c r="D14" s="154"/>
-      <c r="E14" s="154"/>
-      <c r="F14" s="154"/>
-      <c r="G14" s="154"/>
-      <c r="H14" s="154"/>
-      <c r="I14" s="154"/>
-      <c r="J14" s="154"/>
+      <c r="C14" s="148"/>
+      <c r="D14" s="148"/>
+      <c r="E14" s="148"/>
+      <c r="F14" s="148"/>
+      <c r="G14" s="148"/>
+      <c r="H14" s="148"/>
+      <c r="I14" s="148"/>
+      <c r="J14" s="148"/>
       <c r="M14" s="2" t="s">
         <v>102</v>
       </c>
@@ -6711,10 +6711,10 @@
       <c r="B15" s="23" t="s">
         <v>103</v>
       </c>
-      <c r="C15" s="156" t="s">
-        <v>566</v>
-      </c>
-      <c r="D15" s="156"/>
+      <c r="C15" s="162" t="s">
+        <v>565</v>
+      </c>
+      <c r="D15" s="162"/>
       <c r="M15" s="2" t="s">
         <v>104</v>
       </c>
@@ -6728,15 +6728,15 @@
         <v>105</v>
       </c>
       <c r="C16" s="27"/>
-      <c r="D16" s="154" t="s">
+      <c r="D16" s="148" t="s">
         <v>106</v>
       </c>
-      <c r="E16" s="154"/>
-      <c r="F16" s="154"/>
-      <c r="G16" s="154"/>
-      <c r="H16" s="154"/>
-      <c r="I16" s="154"/>
-      <c r="J16" s="154"/>
+      <c r="E16" s="148"/>
+      <c r="F16" s="148"/>
+      <c r="G16" s="148"/>
+      <c r="H16" s="148"/>
+      <c r="I16" s="148"/>
+      <c r="J16" s="148"/>
       <c r="M16" s="2" t="s">
         <v>107</v>
       </c>
@@ -6771,30 +6771,30 @@
       </c>
     </row>
     <row r="19" spans="2:14" ht="21.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B19" s="149" t="s">
+      <c r="B19" s="151" t="s">
         <v>111</v>
       </c>
-      <c r="C19" s="149"/>
-      <c r="D19" s="149"/>
-      <c r="E19" s="149"/>
-      <c r="F19" s="149"/>
-      <c r="G19" s="149"/>
-      <c r="H19" s="149"/>
-      <c r="I19" s="149"/>
-      <c r="J19" s="149"/>
+      <c r="C19" s="151"/>
+      <c r="D19" s="151"/>
+      <c r="E19" s="151"/>
+      <c r="F19" s="151"/>
+      <c r="G19" s="151"/>
+      <c r="H19" s="151"/>
+      <c r="I19" s="151"/>
+      <c r="J19" s="151"/>
     </row>
     <row r="20" spans="2:14" ht="45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B20" s="137" t="s">
-        <v>540</v>
-      </c>
-      <c r="C20" s="137"/>
-      <c r="D20" s="137"/>
-      <c r="E20" s="137"/>
-      <c r="F20" s="137"/>
-      <c r="G20" s="137"/>
-      <c r="H20" s="137"/>
-      <c r="I20" s="137"/>
-      <c r="J20" s="137"/>
+      <c r="B20" s="138" t="s">
+        <v>539</v>
+      </c>
+      <c r="C20" s="138"/>
+      <c r="D20" s="138"/>
+      <c r="E20" s="138"/>
+      <c r="F20" s="138"/>
+      <c r="G20" s="138"/>
+      <c r="H20" s="138"/>
+      <c r="I20" s="138"/>
+      <c r="J20" s="138"/>
       <c r="M20" s="2" t="s">
         <v>112</v>
       </c>
@@ -6807,18 +6807,18 @@
       <c r="B21" s="23" t="s">
         <v>86</v>
       </c>
-      <c r="C21" s="156" t="s">
+      <c r="C21" s="162" t="s">
         <v>113</v>
       </c>
-      <c r="D21" s="156"/>
-      <c r="E21" s="154" t="s">
+      <c r="D21" s="162"/>
+      <c r="E21" s="148" t="s">
         <v>114</v>
       </c>
-      <c r="F21" s="154"/>
-      <c r="G21" s="154"/>
-      <c r="H21" s="154"/>
-      <c r="I21" s="154"/>
-      <c r="J21" s="154"/>
+      <c r="F21" s="148"/>
+      <c r="G21" s="148"/>
+      <c r="H21" s="148"/>
+      <c r="I21" s="148"/>
+      <c r="J21" s="148"/>
       <c r="M21" s="2" t="s">
         <v>115</v>
       </c>
@@ -6853,7 +6853,7 @@
     </row>
     <row r="23" spans="2:14" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B23" s="92" t="s">
-        <v>308</v>
+        <v>307</v>
       </c>
       <c r="C23" s="36">
         <v>1</v>
@@ -6921,15 +6921,15 @@
         <f>SUM(D23:D25)</f>
         <v>600</v>
       </c>
-      <c r="E26" s="157" t="str">
+      <c r="E26" s="165" t="str">
         <f>IF($C$21="Procent",IF(ABS($C$26-1)&gt;0.001,"⚠ Sum skal være 100% i Procent-mode",""),IF($D$26=0,"⚠ Indtast lagtykkelser i mm","Total opbygning: "&amp;TEXT($D$26,"0")&amp;" mm"))</f>
         <v>Total opbygning: 600 mm</v>
       </c>
-      <c r="F26" s="157"/>
-      <c r="G26" s="157"/>
-      <c r="H26" s="157"/>
-      <c r="I26" s="157"/>
-      <c r="J26" s="157"/>
+      <c r="F26" s="165"/>
+      <c r="G26" s="165"/>
+      <c r="H26" s="165"/>
+      <c r="I26" s="165"/>
+      <c r="J26" s="165"/>
       <c r="M26" s="2" t="s">
         <v>126</v>
       </c>
@@ -6942,17 +6942,17 @@
       <c r="B27" s="23" t="s">
         <v>127</v>
       </c>
-      <c r="C27" s="158" t="str">
+      <c r="C27" s="159" t="str">
         <f>IF($C$21="Procent","",IF(AND(F23="Bundsikring",F24="Bærelag"),"⚠ Lag 1 er bundsikring og lag 2 er bærelag — har du byttet rækkefølgen? Bærelag skal stå øverst.",IF(AND(F24="Bundsikring",F25="Bærelag"),"⚠ Lag 2 er bundsikring og lag 3 er bærelag — har du byttet rækkefølgen?","")))</f>
         <v/>
       </c>
-      <c r="D27" s="158"/>
-      <c r="E27" s="158"/>
-      <c r="F27" s="158"/>
-      <c r="G27" s="158"/>
-      <c r="H27" s="158"/>
-      <c r="I27" s="158"/>
-      <c r="J27" s="158"/>
+      <c r="D27" s="159"/>
+      <c r="E27" s="159"/>
+      <c r="F27" s="159"/>
+      <c r="G27" s="159"/>
+      <c r="H27" s="159"/>
+      <c r="I27" s="159"/>
+      <c r="J27" s="159"/>
       <c r="M27" s="2" t="s">
         <v>128</v>
       </c>
@@ -6982,15 +6982,15 @@
         <v>131</v>
       </c>
       <c r="C29" s="42"/>
-      <c r="D29" s="154" t="s">
+      <c r="D29" s="148" t="s">
         <v>132</v>
       </c>
-      <c r="E29" s="154"/>
-      <c r="F29" s="154"/>
-      <c r="G29" s="154"/>
-      <c r="H29" s="154"/>
-      <c r="I29" s="154"/>
-      <c r="J29" s="154"/>
+      <c r="E29" s="148"/>
+      <c r="F29" s="148"/>
+      <c r="G29" s="148"/>
+      <c r="H29" s="148"/>
+      <c r="I29" s="148"/>
+      <c r="J29" s="148"/>
     </row>
     <row r="30" spans="2:14" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B30" s="23" t="s">
@@ -7011,17 +7011,17 @@
       </c>
     </row>
     <row r="32" spans="2:14" ht="33.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B32" s="137" t="s">
+      <c r="B32" s="138" t="s">
         <v>135</v>
       </c>
-      <c r="C32" s="137"/>
-      <c r="D32" s="137"/>
-      <c r="E32" s="137"/>
-      <c r="F32" s="137"/>
-      <c r="G32" s="137"/>
-      <c r="H32" s="137"/>
-      <c r="I32" s="137"/>
-      <c r="J32" s="137"/>
+      <c r="C32" s="138"/>
+      <c r="D32" s="138"/>
+      <c r="E32" s="138"/>
+      <c r="F32" s="138"/>
+      <c r="G32" s="138"/>
+      <c r="H32" s="138"/>
+      <c r="I32" s="138"/>
+      <c r="J32" s="138"/>
     </row>
     <row r="33" spans="2:14" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="M33" s="2" t="s">
@@ -7029,17 +7029,17 @@
       </c>
     </row>
     <row r="34" spans="2:14" ht="21.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B34" s="149" t="s">
+      <c r="B34" s="151" t="s">
         <v>137</v>
       </c>
-      <c r="C34" s="149"/>
-      <c r="D34" s="149"/>
-      <c r="E34" s="149"/>
-      <c r="F34" s="149"/>
-      <c r="G34" s="149"/>
-      <c r="H34" s="149"/>
-      <c r="I34" s="149"/>
-      <c r="J34" s="149"/>
+      <c r="C34" s="151"/>
+      <c r="D34" s="151"/>
+      <c r="E34" s="151"/>
+      <c r="F34" s="151"/>
+      <c r="G34" s="151"/>
+      <c r="H34" s="151"/>
+      <c r="I34" s="151"/>
+      <c r="J34" s="151"/>
       <c r="M34" s="2" t="s">
         <v>138</v>
       </c>
@@ -7049,17 +7049,17 @@
       </c>
     </row>
     <row r="35" spans="2:14" ht="30" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B35" s="137" t="s">
+      <c r="B35" s="138" t="s">
         <v>139</v>
       </c>
-      <c r="C35" s="137"/>
-      <c r="D35" s="137"/>
-      <c r="E35" s="137"/>
-      <c r="F35" s="137"/>
-      <c r="G35" s="137"/>
-      <c r="H35" s="137"/>
-      <c r="I35" s="137"/>
-      <c r="J35" s="137"/>
+      <c r="C35" s="138"/>
+      <c r="D35" s="138"/>
+      <c r="E35" s="138"/>
+      <c r="F35" s="138"/>
+      <c r="G35" s="138"/>
+      <c r="H35" s="138"/>
+      <c r="I35" s="138"/>
+      <c r="J35" s="138"/>
       <c r="M35" s="2" t="s">
         <v>140</v>
       </c>
@@ -7072,11 +7072,11 @@
       <c r="B36" s="23" t="s">
         <v>141</v>
       </c>
-      <c r="C36" s="159" t="s">
+      <c r="C36" s="167" t="s">
         <v>295</v>
       </c>
-      <c r="D36" s="160"/>
-      <c r="E36" s="161" t="str">
+      <c r="D36" s="168"/>
+      <c r="E36" s="169" t="str">
         <f t="array" ref="E36">_xlfn.LET(
   _xlpm.eo, $C$17,
   _xlpm.net, $C$36,
@@ -7152,11 +7152,11 @@
 )</f>
         <v>✓ Det valgte geonet kan anvendes indenfor belastningsklasse 4, 5 og 6</v>
       </c>
-      <c r="F36" s="161"/>
-      <c r="G36" s="161"/>
-      <c r="H36" s="161"/>
-      <c r="I36" s="161"/>
-      <c r="J36" s="161"/>
+      <c r="F36" s="169"/>
+      <c r="G36" s="169"/>
+      <c r="H36" s="169"/>
+      <c r="I36" s="169"/>
+      <c r="J36" s="169"/>
       <c r="M36" s="2" t="s">
         <v>143</v>
       </c>
@@ -7192,15 +7192,15 @@
         <v>146</v>
       </c>
       <c r="C38" s="47"/>
-      <c r="D38" s="154" t="s">
+      <c r="D38" s="148" t="s">
         <v>147</v>
       </c>
-      <c r="E38" s="154"/>
-      <c r="F38" s="154"/>
-      <c r="G38" s="154"/>
-      <c r="H38" s="154"/>
-      <c r="I38" s="154"/>
-      <c r="J38" s="154"/>
+      <c r="E38" s="148"/>
+      <c r="F38" s="148"/>
+      <c r="G38" s="148"/>
+      <c r="H38" s="148"/>
+      <c r="I38" s="148"/>
+      <c r="J38" s="148"/>
     </row>
     <row r="39" spans="2:14" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B39" s="23" t="s">
@@ -7217,32 +7217,32 @@
       <c r="N40" s="31"/>
     </row>
     <row r="41" spans="2:14" ht="21.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B41" s="149" t="s">
+      <c r="B41" s="151" t="s">
         <v>149</v>
       </c>
-      <c r="C41" s="149"/>
-      <c r="D41" s="149"/>
-      <c r="E41" s="149"/>
-      <c r="F41" s="149"/>
-      <c r="G41" s="149"/>
-      <c r="H41" s="149"/>
-      <c r="I41" s="149"/>
-      <c r="J41" s="149"/>
+      <c r="C41" s="151"/>
+      <c r="D41" s="151"/>
+      <c r="E41" s="151"/>
+      <c r="F41" s="151"/>
+      <c r="G41" s="151"/>
+      <c r="H41" s="151"/>
+      <c r="I41" s="151"/>
+      <c r="J41" s="151"/>
       <c r="M41" s="2"/>
       <c r="N41" s="26"/>
     </row>
     <row r="42" spans="2:14" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B42" s="154" t="s">
+      <c r="B42" s="148" t="s">
         <v>150</v>
       </c>
-      <c r="C42" s="154"/>
-      <c r="D42" s="154"/>
-      <c r="E42" s="154"/>
-      <c r="F42" s="154"/>
-      <c r="G42" s="154"/>
-      <c r="H42" s="154"/>
-      <c r="I42" s="154"/>
-      <c r="J42" s="154"/>
+      <c r="C42" s="148"/>
+      <c r="D42" s="148"/>
+      <c r="E42" s="148"/>
+      <c r="F42" s="148"/>
+      <c r="G42" s="148"/>
+      <c r="H42" s="148"/>
+      <c r="I42" s="148"/>
+      <c r="J42" s="148"/>
       <c r="M42" s="2"/>
       <c r="N42" s="26"/>
     </row>
@@ -7251,7 +7251,7 @@
         <v>151</v>
       </c>
       <c r="C43" s="1" t="s">
-        <v>497</v>
+        <v>496</v>
       </c>
       <c r="M43" s="2"/>
       <c r="N43" s="26"/>
@@ -7261,17 +7261,17 @@
       <c r="N44" s="26"/>
     </row>
     <row r="45" spans="2:14" ht="21.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B45" s="149" t="s">
+      <c r="B45" s="151" t="s">
         <v>153</v>
       </c>
-      <c r="C45" s="149"/>
-      <c r="D45" s="149"/>
-      <c r="E45" s="149"/>
-      <c r="F45" s="149"/>
-      <c r="G45" s="149"/>
-      <c r="H45" s="149"/>
-      <c r="I45" s="149"/>
-      <c r="J45" s="149"/>
+      <c r="C45" s="151"/>
+      <c r="D45" s="151"/>
+      <c r="E45" s="151"/>
+      <c r="F45" s="151"/>
+      <c r="G45" s="151"/>
+      <c r="H45" s="151"/>
+      <c r="I45" s="151"/>
+      <c r="J45" s="151"/>
     </row>
     <row r="46" spans="2:14" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B46" s="23" t="s">
@@ -7281,15 +7281,15 @@
         <f ca="1">$N$28</f>
         <v>1100</v>
       </c>
-      <c r="D46" s="154" t="s">
+      <c r="D46" s="148" t="s">
         <v>155</v>
       </c>
-      <c r="E46" s="154"/>
-      <c r="F46" s="154"/>
-      <c r="G46" s="154"/>
-      <c r="H46" s="154"/>
-      <c r="I46" s="154"/>
-      <c r="J46" s="154"/>
+      <c r="E46" s="148"/>
+      <c r="F46" s="148"/>
+      <c r="G46" s="148"/>
+      <c r="H46" s="148"/>
+      <c r="I46" s="148"/>
+      <c r="J46" s="148"/>
     </row>
     <row r="47" spans="2:14" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B47" s="23" t="s">
@@ -7299,15 +7299,15 @@
         <f ca="1">$N$23</f>
         <v>566.94999999999993</v>
       </c>
-      <c r="D47" s="154" t="s">
+      <c r="D47" s="148" t="s">
         <v>157</v>
       </c>
-      <c r="E47" s="154"/>
-      <c r="F47" s="154"/>
-      <c r="G47" s="154"/>
-      <c r="H47" s="154"/>
-      <c r="I47" s="154"/>
-      <c r="J47" s="154"/>
+      <c r="E47" s="148"/>
+      <c r="F47" s="148"/>
+      <c r="G47" s="148"/>
+      <c r="H47" s="148"/>
+      <c r="I47" s="148"/>
+      <c r="J47" s="148"/>
     </row>
     <row r="48" spans="2:14" ht="25.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B48" s="23"/>
@@ -7326,27 +7326,27 @@
         <f ca="1">IFERROR(($C$46-$C$47)/$C$46,"")</f>
         <v>0.48459090909090913</v>
       </c>
-      <c r="F49" s="154" t="s">
+      <c r="F49" s="148" t="s">
         <v>159</v>
       </c>
-      <c r="G49" s="154"/>
-      <c r="H49" s="154"/>
-      <c r="I49" s="154"/>
-      <c r="J49" s="154"/>
+      <c r="G49" s="148"/>
+      <c r="H49" s="148"/>
+      <c r="I49" s="148"/>
+      <c r="J49" s="148"/>
     </row>
     <row r="51" spans="2:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B51" s="162" t="str">
+      <c r="B51" s="166" t="str">
         <f>IF($C$21="Lagtykkelser","━━━ Sammenligning med din planlagte opbygning ━━━","")</f>
         <v>━━━ Sammenligning med din planlagte opbygning ━━━</v>
       </c>
-      <c r="C51" s="162"/>
-      <c r="D51" s="162"/>
-      <c r="E51" s="162"/>
-      <c r="F51" s="162"/>
-      <c r="G51" s="162"/>
-      <c r="H51" s="162"/>
-      <c r="I51" s="162"/>
-      <c r="J51" s="162"/>
+      <c r="C51" s="166"/>
+      <c r="D51" s="166"/>
+      <c r="E51" s="166"/>
+      <c r="F51" s="166"/>
+      <c r="G51" s="166"/>
+      <c r="H51" s="166"/>
+      <c r="I51" s="166"/>
+      <c r="J51" s="166"/>
     </row>
     <row r="52" spans="2:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B52" s="23" t="s">
@@ -7356,16 +7356,16 @@
         <f>IF($C$21="Lagtykkelser",$D$26,"")</f>
         <v>600</v>
       </c>
-      <c r="D52" s="154" t="str">
+      <c r="D52" s="148" t="str">
         <f>IF($C$21="Lagtykkelser","(sum af lagtykkelser fra Sektion C)","")</f>
         <v>(sum af lagtykkelser fra Sektion C)</v>
       </c>
-      <c r="E52" s="154"/>
-      <c r="F52" s="154"/>
-      <c r="G52" s="154"/>
-      <c r="H52" s="154"/>
-      <c r="I52" s="154"/>
-      <c r="J52" s="154"/>
+      <c r="E52" s="148"/>
+      <c r="F52" s="148"/>
+      <c r="G52" s="148"/>
+      <c r="H52" s="148"/>
+      <c r="I52" s="148"/>
+      <c r="J52" s="148"/>
     </row>
     <row r="53" spans="2:10" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B53" s="23" t="s">
@@ -7375,16 +7375,16 @@
         <f ca="1">IF($C$21="Lagtykkelser",IFERROR($C$52-$C$46,""),"")</f>
         <v>-500</v>
       </c>
-      <c r="D53" s="148" t="str">
+      <c r="D53" s="154" t="str">
         <f ca="1">IF($C$21&lt;&gt;"Lagtykkelser","",IFERROR(IF($C$52&gt;=$C$46,"✓ Planlagt opbygning har TILSTRÆKKELIG tykkelse uden armering ("&amp;TEXT($C$52-$C$46,"+0;-0")&amp;" mm i forhold til krav på "&amp;TEXT($C$46,"0")&amp;" mm)","⚠ Planlagt opbygning har UTILSTRÆKKELIG tykkelse uden armering ("&amp;TEXT($C$52-$C$46,"+0;-0")&amp;" mm i forhold til krav på "&amp;TEXT($C$46,"0")&amp;" mm)"),""))</f>
         <v>⚠ Planlagt opbygning har UTILSTRÆKKELIG tykkelse uden armering (-500 mm i forhold til krav på 1100 mm)</v>
       </c>
-      <c r="E53" s="148"/>
-      <c r="F53" s="148"/>
-      <c r="G53" s="148"/>
-      <c r="H53" s="148"/>
-      <c r="I53" s="148"/>
-      <c r="J53" s="148"/>
+      <c r="E53" s="154"/>
+      <c r="F53" s="154"/>
+      <c r="G53" s="154"/>
+      <c r="H53" s="154"/>
+      <c r="I53" s="154"/>
+      <c r="J53" s="154"/>
     </row>
     <row r="54" spans="2:10" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B54" s="23" t="s">
@@ -7394,16 +7394,16 @@
         <f ca="1">IF($C$21="Lagtykkelser",IFERROR($C$52-$C$47,""),"")</f>
         <v>33.050000000000068</v>
       </c>
-      <c r="D54" s="148" t="str">
+      <c r="D54" s="154" t="str">
         <f ca="1">IF($C$21&lt;&gt;"Lagtykkelser","",IFERROR(IF($C$52&gt;=$C$47,"✓ Planlagt opbygning har TILSTRÆKKELIG tykkelse med armering ("&amp;TEXT($C$52-$C$47,"+0;-0")&amp;" mm i forhold til krav på "&amp;TEXT($C$47,"0")&amp;" mm)","❌ Planlagt opbygning har UTILSTRÆKKELIG tykkelse selv med armering ("&amp;TEXT($C$52-$C$47,"+0;-0")&amp;" mm i forhold til krav på "&amp;TEXT($C$47,"0")&amp;" mm) — forøg lagtykkelserne"),""))</f>
         <v>✓ Planlagt opbygning har TILSTRÆKKELIG tykkelse med armering (+33 mm i forhold til krav på 567 mm)</v>
       </c>
-      <c r="E54" s="148"/>
-      <c r="F54" s="148"/>
-      <c r="G54" s="148"/>
-      <c r="H54" s="148"/>
-      <c r="I54" s="148"/>
-      <c r="J54" s="148"/>
+      <c r="E54" s="154"/>
+      <c r="F54" s="154"/>
+      <c r="G54" s="154"/>
+      <c r="H54" s="154"/>
+      <c r="I54" s="154"/>
+      <c r="J54" s="154"/>
     </row>
     <row r="55" spans="2:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B55" s="23" t="s">
@@ -7413,214 +7413,214 @@
         <f ca="1">IF($C$21="Lagtykkelser",IFERROR(MAX(0,$C$52-$C$47),""),"")</f>
         <v>33.050000000000068</v>
       </c>
-      <c r="D55" s="162" t="str">
+      <c r="D55" s="166" t="str">
         <f>IF($C$21="Lagtykkelser","← se Sektion H for reduktionsstrategi","")</f>
         <v>← se Sektion H for reduktionsstrategi</v>
       </c>
-      <c r="E55" s="162"/>
-      <c r="F55" s="162"/>
-      <c r="G55" s="162"/>
-      <c r="H55" s="162"/>
-      <c r="I55" s="162"/>
-      <c r="J55" s="162"/>
+      <c r="E55" s="166"/>
+      <c r="F55" s="166"/>
+      <c r="G55" s="166"/>
+      <c r="H55" s="166"/>
+      <c r="I55" s="166"/>
+      <c r="J55" s="166"/>
     </row>
     <row r="57" spans="2:10" ht="21.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B57" s="149" t="s">
+      <c r="B57" s="151" t="s">
         <v>164</v>
       </c>
-      <c r="C57" s="149"/>
-      <c r="D57" s="149"/>
-      <c r="E57" s="149"/>
-      <c r="F57" s="149"/>
-      <c r="G57" s="149"/>
-      <c r="H57" s="149"/>
-      <c r="I57" s="149"/>
-      <c r="J57" s="149"/>
+      <c r="C57" s="151"/>
+      <c r="D57" s="151"/>
+      <c r="E57" s="151"/>
+      <c r="F57" s="151"/>
+      <c r="G57" s="151"/>
+      <c r="H57" s="151"/>
+      <c r="I57" s="151"/>
+      <c r="J57" s="151"/>
     </row>
     <row r="58" spans="2:10" ht="24" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B58" s="23" t="s">
         <v>165</v>
       </c>
-      <c r="C58" s="158" t="str">
+      <c r="C58" s="159" t="str">
         <f>IF(NOT(ISNUMBER($N$5)),"⚠ Indtast Eu eller Cv i Sektion A",IF($N$5&lt;3,"❌ FEJL: Eu &lt; 3 MPa er udenfor diagrammets gyldighedsområde (3-45 MPa). Kontakt Byggros.",IF($N$5&gt;45,"❌ FEJL: Eu &gt; 45 MPa er udenfor diagrammets gyldighedsområde (3-45 MPa). Kontakt Byggros.","")))</f>
         <v/>
       </c>
-      <c r="D58" s="158"/>
-      <c r="E58" s="158"/>
-      <c r="F58" s="158"/>
-      <c r="G58" s="158"/>
-      <c r="H58" s="158"/>
-      <c r="I58" s="158"/>
-      <c r="J58" s="158"/>
+      <c r="D58" s="159"/>
+      <c r="E58" s="159"/>
+      <c r="F58" s="159"/>
+      <c r="G58" s="159"/>
+      <c r="H58" s="159"/>
+      <c r="I58" s="159"/>
+      <c r="J58" s="159"/>
     </row>
     <row r="59" spans="2:10" ht="24" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B59" s="23" t="s">
         <v>166</v>
       </c>
-      <c r="C59" s="158" t="str">
+      <c r="C59" s="159" t="str">
         <f>IF(NOT(ISNUMBER($N$6)),"⚠ Vælg belastningsklasse i Sektion B",IF($N$6&lt;30,"❌ FEJL: Eo &lt; 30 MPa er udenfor gyldighedsområde (30-150 MPa).",IF($N$6&gt;150,"❌ FEJL: Eo &gt; 150 MPa er udenfor gyldighedsområde (30-150 MPa).","")))</f>
         <v/>
       </c>
-      <c r="D59" s="158"/>
-      <c r="E59" s="158"/>
-      <c r="F59" s="158"/>
-      <c r="G59" s="158"/>
-      <c r="H59" s="158"/>
-      <c r="I59" s="158"/>
-      <c r="J59" s="158"/>
+      <c r="D59" s="159"/>
+      <c r="E59" s="159"/>
+      <c r="F59" s="159"/>
+      <c r="G59" s="159"/>
+      <c r="H59" s="159"/>
+      <c r="I59" s="159"/>
+      <c r="J59" s="159"/>
     </row>
     <row r="60" spans="2:10" ht="24" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B60" s="23" t="s">
         <v>167</v>
       </c>
-      <c r="C60" s="158" t="str">
+      <c r="C60" s="159" t="str">
         <f>IF(NOT(ISNUMBER($N$7)),"",IF($N$7&lt;35,"⚠ φ &lt; 35° — værktøjet forudsætter friktionsmateriale med φ ≥ 35°. Resultat kan være for optimistisk.",IF($N$7&gt;50,"⚠ φ &gt; 50° — usædvanlig høj værdi, dobbelttjek materialevalget.","")))</f>
         <v/>
       </c>
-      <c r="D60" s="158"/>
-      <c r="E60" s="158"/>
-      <c r="F60" s="158"/>
-      <c r="G60" s="158"/>
-      <c r="H60" s="158"/>
-      <c r="I60" s="158"/>
-      <c r="J60" s="158"/>
+      <c r="D60" s="159"/>
+      <c r="E60" s="159"/>
+      <c r="F60" s="159"/>
+      <c r="G60" s="159"/>
+      <c r="H60" s="159"/>
+      <c r="I60" s="159"/>
+      <c r="J60" s="159"/>
     </row>
     <row r="61" spans="2:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B61" s="23" t="s">
         <v>168</v>
       </c>
-      <c r="C61" s="157" t="str">
+      <c r="C61" s="165" t="str">
         <f>IF(AND($C$26&gt;0,ABS($C$26-1)&gt;0.001),"⚠ Summen af materialeandele er ikke 100%. Justér i Sektion C.","")</f>
         <v/>
       </c>
-      <c r="D61" s="157"/>
-      <c r="E61" s="157"/>
-      <c r="F61" s="157"/>
-      <c r="G61" s="157"/>
-      <c r="H61" s="157"/>
-      <c r="I61" s="157"/>
-      <c r="J61" s="157"/>
+      <c r="D61" s="165"/>
+      <c r="E61" s="165"/>
+      <c r="F61" s="165"/>
+      <c r="G61" s="165"/>
+      <c r="H61" s="165"/>
+      <c r="I61" s="165"/>
+      <c r="J61" s="165"/>
     </row>
     <row r="62" spans="2:10" ht="24" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B62" s="23" t="s">
         <v>169</v>
       </c>
-      <c r="C62" s="158" t="str">
+      <c r="C62" s="159" t="str">
         <f ca="1">IF(AND($N$8&lt;&gt;"Uarmeret",NOT(ISNUMBER($N$17))),"⚠ Den valgte lagopbygning er ikke understøttet for denne Eu/Eo-kombination. Prøv en anden konfiguration.","")</f>
         <v/>
       </c>
-      <c r="D62" s="158"/>
-      <c r="E62" s="158"/>
-      <c r="F62" s="158"/>
-      <c r="G62" s="158"/>
-      <c r="H62" s="158"/>
-      <c r="I62" s="158"/>
-      <c r="J62" s="158"/>
+      <c r="D62" s="159"/>
+      <c r="E62" s="159"/>
+      <c r="F62" s="159"/>
+      <c r="G62" s="159"/>
+      <c r="H62" s="159"/>
+      <c r="I62" s="159"/>
+      <c r="J62" s="159"/>
     </row>
     <row r="63" spans="2:10" ht="24" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B63" s="23" t="s">
         <v>170</v>
       </c>
-      <c r="C63" s="158" t="str">
+      <c r="C63" s="159" t="str">
         <f>IFERROR(IF(AND(ISNUMBER(IFERROR(VLOOKUP($C$36,'6. DB Geonet'!$B$6:$J$25,6,FALSE()),"")),(MAX(IFERROR(VLOOKUP(B23,'5. DB Materialer'!$B$6:$F$18,3,FALSE()),0),IFERROR(VLOOKUP(B24,'5. DB Materialer'!$B$6:$F$18,3,FALSE()),0),IFERROR(VLOOKUP(B25,'5. DB Materialer'!$B$6:$F$18,3,FALSE()),0)))&gt;IFERROR(VLOOKUP($C$36,'6. DB Geonet'!$B$6:$J$25,6,FALSE()),"")),"⚠ Bærelagets max korn (" &amp; (MAX(IFERROR(VLOOKUP(B23,'5. DB Materialer'!$B$6:$F$18,3,FALSE()),0),IFERROR(VLOOKUP(B24,'5. DB Materialer'!$B$6:$F$18,3,FALSE()),0),IFERROR(VLOOKUP(B25,'5. DB Materialer'!$B$6:$F$18,3,FALSE()),0))) &amp; " mm) overstiger nettets anbefalede max korn (" &amp; IFERROR(VLOOKUP($C$36,'6. DB Geonet'!$B$6:$J$25,6,FALSE()),"") &amp; " mm). Overvej net med større maske.",""),"")</f>
         <v/>
       </c>
-      <c r="D63" s="158"/>
-      <c r="E63" s="158"/>
-      <c r="F63" s="158"/>
-      <c r="G63" s="158"/>
-      <c r="H63" s="158"/>
-      <c r="I63" s="158"/>
-      <c r="J63" s="158"/>
+      <c r="D63" s="159"/>
+      <c r="E63" s="159"/>
+      <c r="F63" s="159"/>
+      <c r="G63" s="159"/>
+      <c r="H63" s="159"/>
+      <c r="I63" s="159"/>
+      <c r="J63" s="159"/>
     </row>
     <row r="64" spans="2:10" ht="24" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B64" s="23" t="s">
         <v>171</v>
       </c>
-      <c r="C64" s="158" t="str">
+      <c r="C64" s="159" t="str">
         <f ca="1">IFERROR(IF(AND(ISNUMBER($C$47),ISNUMBER(IFERROR(VLOOKUP($C$36,'6. DB Geonet'!$B$6:$J$25,7,FALSE()),"")),$C$47&lt;IFERROR(VLOOKUP($C$36,'6. DB Geonet'!$B$6:$J$25,7,FALSE()),"")*10),"⚠ Dimensioneret tykkelse er mindre end nettets minimum dæklag (" &amp; IFERROR(VLOOKUP($C$36,'6. DB Geonet'!$B$6:$J$25,7,FALSE()),"") &amp; " cm). Vælg et tyndere net eller flere lag.",""),"")</f>
         <v/>
       </c>
-      <c r="D64" s="158"/>
-      <c r="E64" s="158"/>
-      <c r="F64" s="158"/>
-      <c r="G64" s="158"/>
-      <c r="H64" s="158"/>
-      <c r="I64" s="158"/>
-      <c r="J64" s="158"/>
+      <c r="D64" s="159"/>
+      <c r="E64" s="159"/>
+      <c r="F64" s="159"/>
+      <c r="G64" s="159"/>
+      <c r="H64" s="159"/>
+      <c r="I64" s="159"/>
+      <c r="J64" s="159"/>
     </row>
     <row r="65" spans="2:10" ht="24" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B65" s="23" t="s">
         <v>172</v>
       </c>
-      <c r="C65" s="163" t="str">
+      <c r="C65" s="164" t="str">
         <f ca="1">IF(AND(ISNUMBER($C$47),$N$8="1 lag",$C$47&gt;500),"💡 Total tykkelse &gt; 500 mm — overvej 2 lag for yderligere reduktion.",IF(AND(ISNUMBER($C$47),$N$8="2 lag/flere lag",$C$47&lt;400),"💡 Total tykkelse &lt; 400 mm — 1 lag er typisk tilstrækkeligt og mere økonomisk.",""))</f>
         <v/>
       </c>
-      <c r="D65" s="163"/>
-      <c r="E65" s="163"/>
-      <c r="F65" s="163"/>
-      <c r="G65" s="163"/>
-      <c r="H65" s="163"/>
-      <c r="I65" s="163"/>
-      <c r="J65" s="163"/>
+      <c r="D65" s="164"/>
+      <c r="E65" s="164"/>
+      <c r="F65" s="164"/>
+      <c r="G65" s="164"/>
+      <c r="H65" s="164"/>
+      <c r="I65" s="164"/>
+      <c r="J65" s="164"/>
     </row>
     <row r="67" spans="2:10" ht="21.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B67" s="149" t="s">
-        <v>541</v>
-      </c>
-      <c r="C67" s="149"/>
-      <c r="D67" s="149"/>
-      <c r="E67" s="149"/>
-      <c r="F67" s="149"/>
-      <c r="G67" s="149"/>
-      <c r="H67" s="149"/>
-      <c r="I67" s="149"/>
-      <c r="J67" s="149"/>
+      <c r="B67" s="151" t="s">
+        <v>540</v>
+      </c>
+      <c r="C67" s="151"/>
+      <c r="D67" s="151"/>
+      <c r="E67" s="151"/>
+      <c r="F67" s="151"/>
+      <c r="G67" s="151"/>
+      <c r="H67" s="151"/>
+      <c r="I67" s="151"/>
+      <c r="J67" s="151"/>
     </row>
     <row r="68" spans="2:10" ht="45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B68" s="137" t="s">
+      <c r="B68" s="138" t="s">
         <v>173</v>
       </c>
-      <c r="C68" s="137"/>
-      <c r="D68" s="137"/>
-      <c r="E68" s="137"/>
-      <c r="F68" s="137"/>
-      <c r="G68" s="137"/>
-      <c r="H68" s="137"/>
-      <c r="I68" s="137"/>
-      <c r="J68" s="137"/>
+      <c r="C68" s="138"/>
+      <c r="D68" s="138"/>
+      <c r="E68" s="138"/>
+      <c r="F68" s="138"/>
+      <c r="G68" s="138"/>
+      <c r="H68" s="138"/>
+      <c r="I68" s="138"/>
+      <c r="J68" s="138"/>
     </row>
     <row r="69" spans="2:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B69" s="164" t="str">
+      <c r="B69" s="161" t="str">
         <f>IF($C$21&lt;&gt;"Lagtykkelser","ⓘ Sektionen er ikke aktiv — skift indtastningsmetode til ""Lagtykkelser"" i Sektion C for at bruge den.","")</f>
         <v/>
       </c>
-      <c r="C69" s="164"/>
-      <c r="D69" s="164"/>
-      <c r="E69" s="164"/>
-      <c r="F69" s="164"/>
-      <c r="G69" s="164"/>
-      <c r="H69" s="164"/>
-      <c r="I69" s="164"/>
-      <c r="J69" s="164"/>
+      <c r="C69" s="161"/>
+      <c r="D69" s="161"/>
+      <c r="E69" s="161"/>
+      <c r="F69" s="161"/>
+      <c r="G69" s="161"/>
+      <c r="H69" s="161"/>
+      <c r="I69" s="161"/>
+      <c r="J69" s="161"/>
     </row>
     <row r="71" spans="2:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B71" s="23" t="s">
         <v>174</v>
       </c>
-      <c r="C71" s="156" t="s">
-        <v>546</v>
-      </c>
-      <c r="D71" s="156"/>
-      <c r="E71" s="154" t="s">
+      <c r="C71" s="162" t="s">
+        <v>545</v>
+      </c>
+      <c r="D71" s="162"/>
+      <c r="E71" s="148" t="s">
         <v>175</v>
       </c>
-      <c r="F71" s="154"/>
-      <c r="G71" s="154"/>
-      <c r="H71" s="154"/>
-      <c r="I71" s="154"/>
-      <c r="J71" s="154"/>
+      <c r="F71" s="148"/>
+      <c r="G71" s="148"/>
+      <c r="H71" s="148"/>
+      <c r="I71" s="148"/>
+      <c r="J71" s="148"/>
     </row>
     <row r="73" spans="2:10" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B73" s="33" t="s">
@@ -7724,10 +7724,10 @@
       </c>
     </row>
     <row r="77" spans="2:10" ht="24" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B77" s="165" t="s">
+      <c r="B77" s="163" t="s">
         <v>184</v>
       </c>
-      <c r="C77" s="165"/>
+      <c r="C77" s="163"/>
       <c r="D77" s="56">
         <f>SUM(D74:D76)</f>
         <v>600</v>
@@ -7750,16 +7750,16 @@
         <f ca="1">IF($C$21&lt;&gt;"Lagtykkelser","",IFERROR($G$77-$C$47,""))</f>
         <v>33.050000000000068</v>
       </c>
-      <c r="D79" s="148" t="str">
+      <c r="D79" s="154" t="str">
         <f ca="1">IF($C$21&lt;&gt;"Lagtykkelser","",IFERROR(IF($G$77&gt;=$C$47,"✓ Foreslået opbygning er tilstrækkelig","⚠ Foreslået opbygning er TYNDERE end krævet armeret ("&amp;TEXT($C$47,"0")&amp;" mm) — bæreevnen kan være utilstrækkelig"),""))</f>
         <v>✓ Foreslået opbygning er tilstrækkelig</v>
       </c>
-      <c r="E79" s="148"/>
-      <c r="F79" s="148"/>
-      <c r="G79" s="148"/>
-      <c r="H79" s="148"/>
-      <c r="I79" s="148"/>
-      <c r="J79" s="148"/>
+      <c r="E79" s="154"/>
+      <c r="F79" s="154"/>
+      <c r="G79" s="154"/>
+      <c r="H79" s="154"/>
+      <c r="I79" s="154"/>
+      <c r="J79" s="154"/>
     </row>
     <row r="80" spans="2:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B80" s="23" t="s">
@@ -7769,118 +7769,118 @@
         <f>IF($C$21&lt;&gt;"Lagtykkelser","",IFERROR($N$36-$G$77,""))</f>
         <v>0</v>
       </c>
-      <c r="D80" s="154" t="s">
+      <c r="D80" s="148" t="s">
         <v>187</v>
       </c>
-      <c r="E80" s="154"/>
-      <c r="F80" s="154"/>
-      <c r="G80" s="154"/>
-      <c r="H80" s="154"/>
-      <c r="I80" s="154"/>
-      <c r="J80" s="154"/>
+      <c r="E80" s="148"/>
+      <c r="F80" s="148"/>
+      <c r="G80" s="148"/>
+      <c r="H80" s="148"/>
+      <c r="I80" s="148"/>
+      <c r="J80" s="148"/>
     </row>
     <row r="82" spans="2:10" ht="36" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B82" s="23" t="s">
         <v>188</v>
       </c>
-      <c r="C82" s="148" t="str">
+      <c r="C82" s="154" t="str">
         <f>IF($C$21&lt;&gt;"Lagtykkelser","",IF($C$43="1 lag",IF(COUNTIF(F23:F25,"Bærelag")&gt;=1,"1 net placeres ved laggrænsen mellem nederste bærelag og bundsikring (eller i bunden af nederste bærelag)","1 net placeres ved bunden af bærelaget"),"2 net: ét ved laggrænsen mellem bærelag og bundsikring, og ét ved bunden mod råjordsplanum"))</f>
         <v>2 net: ét ved laggrænsen mellem bærelag og bundsikring, og ét ved bunden mod råjordsplanum</v>
       </c>
-      <c r="D82" s="148"/>
-      <c r="E82" s="148"/>
-      <c r="F82" s="148"/>
-      <c r="G82" s="148"/>
-      <c r="H82" s="148"/>
-      <c r="I82" s="148"/>
-      <c r="J82" s="148"/>
+      <c r="D82" s="154"/>
+      <c r="E82" s="154"/>
+      <c r="F82" s="154"/>
+      <c r="G82" s="154"/>
+      <c r="H82" s="154"/>
+      <c r="I82" s="154"/>
+      <c r="J82" s="154"/>
     </row>
     <row r="84" spans="2:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B84" s="166" t="s">
+      <c r="B84" s="160" t="s">
         <v>189</v>
       </c>
-      <c r="C84" s="166"/>
-      <c r="D84" s="166"/>
-      <c r="E84" s="166"/>
-      <c r="F84" s="166"/>
-      <c r="G84" s="166"/>
-      <c r="H84" s="166"/>
-      <c r="I84" s="166"/>
-      <c r="J84" s="166"/>
+      <c r="C84" s="160"/>
+      <c r="D84" s="160"/>
+      <c r="E84" s="160"/>
+      <c r="F84" s="160"/>
+      <c r="G84" s="160"/>
+      <c r="H84" s="160"/>
+      <c r="I84" s="160"/>
+      <c r="J84" s="160"/>
     </row>
     <row r="85" spans="2:10" ht="36" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B85" s="60" t="s">
         <v>190</v>
       </c>
-      <c r="C85" s="158" t="str">
+      <c r="C85" s="159" t="str">
         <f>IF($C$21&lt;&gt;"Lagtykkelser","",IF(OR(AND(G74&lt;&gt;"",G74&gt;0,G74&lt;200),AND(G75&lt;&gt;"",G75&gt;0,G75&lt;200),AND(G76&lt;&gt;"",G76&gt;0,G76&lt;200)),"⚠ Et eller flere lag er under 200 mm — geonet kræver normalt min. 200 mm dæklag for at opnå armeringseffekt. Vurder om opbygningen er praktisk anvendelig.",""))</f>
         <v/>
       </c>
-      <c r="D85" s="158"/>
-      <c r="E85" s="158"/>
-      <c r="F85" s="158"/>
-      <c r="G85" s="158"/>
-      <c r="H85" s="158"/>
-      <c r="I85" s="158"/>
-      <c r="J85" s="158"/>
+      <c r="D85" s="159"/>
+      <c r="E85" s="159"/>
+      <c r="F85" s="159"/>
+      <c r="G85" s="159"/>
+      <c r="H85" s="159"/>
+      <c r="I85" s="159"/>
+      <c r="J85" s="159"/>
     </row>
     <row r="86" spans="2:10" ht="48" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B86" s="60" t="s">
         <v>191</v>
       </c>
-      <c r="C86" s="158" t="str">
+      <c r="C86" s="159" t="str">
         <f ca="1">IF($C$21&lt;&gt;"Lagtykkelser","",IFERROR(IF($G$77&lt;$C$47,"⚠ Total foreslået opbygning ("&amp;TEXT($G$77,"0")&amp;" mm) er tyndere end den dimensionerende anbefaling ("&amp;TEXT($C$47,"0")&amp;" mm). Du kan have legitime grunde til at gå tyndere — men vær opmærksom på risiko for utilstrækkelig bæreevne.",""),""))</f>
         <v/>
       </c>
-      <c r="D86" s="158"/>
-      <c r="E86" s="158"/>
-      <c r="F86" s="158"/>
-      <c r="G86" s="158"/>
-      <c r="H86" s="158"/>
-      <c r="I86" s="158"/>
-      <c r="J86" s="158"/>
+      <c r="D86" s="159"/>
+      <c r="E86" s="159"/>
+      <c r="F86" s="159"/>
+      <c r="G86" s="159"/>
+      <c r="H86" s="159"/>
+      <c r="I86" s="159"/>
+      <c r="J86" s="159"/>
     </row>
     <row r="87" spans="2:10" ht="36" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B87" s="60" t="s">
         <v>192</v>
       </c>
-      <c r="C87" s="158" t="str">
+      <c r="C87" s="159" t="str">
         <f>IF($C$21&lt;&gt;"Lagtykkelser","",IF(AND($C$71="Reducer bærelag",$N$34=0),"⚠ Du har valgt ""Reducer bærelag"" men der er ingen bærelag i din opbygning. Vælg en anden strategi.",IF(AND($C$71="Reducer bundsikring",$N$35=0),"⚠ Du har valgt ""Reducer bundsikring"" men der er ingen bundsikring i din opbygning. Vælg en anden strategi.","")))</f>
         <v/>
       </c>
-      <c r="D87" s="158"/>
-      <c r="E87" s="158"/>
-      <c r="F87" s="158"/>
-      <c r="G87" s="158"/>
-      <c r="H87" s="158"/>
-      <c r="I87" s="158"/>
-      <c r="J87" s="158"/>
+      <c r="D87" s="159"/>
+      <c r="E87" s="159"/>
+      <c r="F87" s="159"/>
+      <c r="G87" s="159"/>
+      <c r="H87" s="159"/>
+      <c r="I87" s="159"/>
+      <c r="J87" s="159"/>
     </row>
     <row r="89" spans="2:10" ht="18.75" x14ac:dyDescent="0.25">
-      <c r="B89" s="149" t="s">
-        <v>551</v>
-      </c>
-      <c r="C89" s="149"/>
-      <c r="D89" s="149"/>
-      <c r="E89" s="149"/>
-      <c r="F89" s="149"/>
-      <c r="G89" s="149"/>
-      <c r="H89" s="149"/>
-      <c r="I89" s="149"/>
-      <c r="J89" s="149"/>
+      <c r="B89" s="151" t="s">
+        <v>550</v>
+      </c>
+      <c r="C89" s="151"/>
+      <c r="D89" s="151"/>
+      <c r="E89" s="151"/>
+      <c r="F89" s="151"/>
+      <c r="G89" s="151"/>
+      <c r="H89" s="151"/>
+      <c r="I89" s="151"/>
+      <c r="J89" s="151"/>
     </row>
     <row r="90" spans="2:10" x14ac:dyDescent="0.25">
-      <c r="B90" s="167" t="s">
-        <v>508</v>
-      </c>
-      <c r="C90" s="167"/>
-      <c r="D90" s="167"/>
-      <c r="E90" s="167"/>
-      <c r="F90" s="167"/>
-      <c r="G90" s="167"/>
-      <c r="H90" s="167"/>
-      <c r="I90" s="167"/>
-      <c r="J90" s="167"/>
+      <c r="B90" s="158" t="s">
+        <v>507</v>
+      </c>
+      <c r="C90" s="158"/>
+      <c r="D90" s="158"/>
+      <c r="E90" s="158"/>
+      <c r="F90" s="158"/>
+      <c r="G90" s="158"/>
+      <c r="H90" s="158"/>
+      <c r="I90" s="158"/>
+      <c r="J90" s="158"/>
     </row>
     <row r="92" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B92" s="63" t="s">
@@ -7892,17 +7892,17 @@
       </c>
     </row>
     <row r="94" spans="2:10" x14ac:dyDescent="0.25">
-      <c r="B94" s="168" t="s">
+      <c r="B94" s="157" t="s">
         <v>195</v>
       </c>
-      <c r="C94" s="168"/>
-      <c r="D94" s="168"/>
-      <c r="E94" s="168"/>
-      <c r="F94" s="168"/>
-      <c r="G94" s="168"/>
-      <c r="H94" s="168"/>
-      <c r="I94" s="168"/>
-      <c r="J94" s="168"/>
+      <c r="C94" s="157"/>
+      <c r="D94" s="157"/>
+      <c r="E94" s="157"/>
+      <c r="F94" s="157"/>
+      <c r="G94" s="157"/>
+      <c r="H94" s="157"/>
+      <c r="I94" s="157"/>
+      <c r="J94" s="157"/>
     </row>
     <row r="95" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B95" s="63" t="s">
@@ -7912,15 +7912,15 @@
         <f>IFERROR(VLOOKUP($C$36,'6. DB Geonet'!$B$6:$K$25,5,FALSE()),"Verificeres")</f>
         <v>pitch 80 mm</v>
       </c>
-      <c r="D95" s="169" t="s">
+      <c r="D95" s="156" t="s">
         <v>197</v>
       </c>
-      <c r="E95" s="169"/>
-      <c r="F95" s="169"/>
-      <c r="G95" s="169"/>
-      <c r="H95" s="169"/>
-      <c r="I95" s="169"/>
-      <c r="J95" s="169"/>
+      <c r="E95" s="156"/>
+      <c r="F95" s="156"/>
+      <c r="G95" s="156"/>
+      <c r="H95" s="156"/>
+      <c r="I95" s="156"/>
+      <c r="J95" s="156"/>
     </row>
     <row r="96" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B96" s="63" t="s">
@@ -7930,15 +7930,15 @@
         <f>IFERROR(IF(ISNUMBER(VLOOKUP($C$36,'6. DB Geonet'!$B$6:$K$25,6,FALSE())),VLOOKUP($C$36,'6. DB Geonet'!$B$6:$K$25,6,FALSE())&amp;" mm",VLOOKUP($C$36,'6. DB Geonet'!$B$6:$K$25,6,FALSE())),"Verificeres")</f>
         <v>150 mm</v>
       </c>
-      <c r="D96" s="169" t="s">
+      <c r="D96" s="156" t="s">
         <v>199</v>
       </c>
-      <c r="E96" s="169"/>
-      <c r="F96" s="169"/>
-      <c r="G96" s="169"/>
-      <c r="H96" s="169"/>
-      <c r="I96" s="169"/>
-      <c r="J96" s="169"/>
+      <c r="E96" s="156"/>
+      <c r="F96" s="156"/>
+      <c r="G96" s="156"/>
+      <c r="H96" s="156"/>
+      <c r="I96" s="156"/>
+      <c r="J96" s="156"/>
     </row>
     <row r="97" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B97" s="63" t="s">
@@ -7948,15 +7948,15 @@
         <f>IFERROR(IF(ISNUMBER(VLOOKUP($C$36,'6. DB Geonet'!$B$6:$K$25,10,FALSE())),VLOOKUP($C$36,'6. DB Geonet'!$B$6:$K$25,10,FALSE())&amp;" mm",VLOOKUP($C$36,'6. DB Geonet'!$B$6:$K$25,10,FALSE())),"Verificeres")</f>
         <v>Ej oplyst</v>
       </c>
-      <c r="D97" s="169" t="s">
+      <c r="D97" s="156" t="s">
         <v>201</v>
       </c>
-      <c r="E97" s="169"/>
-      <c r="F97" s="169"/>
-      <c r="G97" s="169"/>
-      <c r="H97" s="169"/>
-      <c r="I97" s="169"/>
-      <c r="J97" s="169"/>
+      <c r="E97" s="156"/>
+      <c r="F97" s="156"/>
+      <c r="G97" s="156"/>
+      <c r="H97" s="156"/>
+      <c r="I97" s="156"/>
+      <c r="J97" s="156"/>
     </row>
     <row r="98" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B98" s="63" t="s">
@@ -7966,15 +7966,15 @@
         <f>IFERROR(IF(ISNUMBER(VLOOKUP($C$36,'6. DB Geonet'!$B$6:$K$25,7,FALSE())),VLOOKUP($C$36,'6. DB Geonet'!$B$6:$K$25,7,FALSE())&amp;" cm",VLOOKUP($C$36,'6. DB Geonet'!$B$6:$K$25,7,FALSE())),"Verificeres")</f>
         <v>20 cm</v>
       </c>
-      <c r="D98" s="169" t="s">
+      <c r="D98" s="156" t="s">
         <v>203</v>
       </c>
-      <c r="E98" s="169"/>
-      <c r="F98" s="169"/>
-      <c r="G98" s="169"/>
-      <c r="H98" s="169"/>
-      <c r="I98" s="169"/>
-      <c r="J98" s="169"/>
+      <c r="E98" s="156"/>
+      <c r="F98" s="156"/>
+      <c r="G98" s="156"/>
+      <c r="H98" s="156"/>
+      <c r="I98" s="156"/>
+      <c r="J98" s="156"/>
     </row>
     <row r="99" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B99" s="63" t="s">
@@ -7983,28 +7983,28 @@
       <c r="C99" s="64" t="s">
         <v>205</v>
       </c>
-      <c r="D99" s="169" t="s">
+      <c r="D99" s="156" t="s">
         <v>206</v>
       </c>
-      <c r="E99" s="169"/>
-      <c r="F99" s="169"/>
-      <c r="G99" s="169"/>
-      <c r="H99" s="169"/>
-      <c r="I99" s="169"/>
-      <c r="J99" s="169"/>
+      <c r="E99" s="156"/>
+      <c r="F99" s="156"/>
+      <c r="G99" s="156"/>
+      <c r="H99" s="156"/>
+      <c r="I99" s="156"/>
+      <c r="J99" s="156"/>
     </row>
     <row r="101" spans="2:10" x14ac:dyDescent="0.25">
-      <c r="B101" s="168" t="s">
+      <c r="B101" s="157" t="s">
         <v>207</v>
       </c>
-      <c r="C101" s="168"/>
-      <c r="D101" s="168"/>
-      <c r="E101" s="168"/>
-      <c r="F101" s="168"/>
-      <c r="G101" s="168"/>
-      <c r="H101" s="168"/>
-      <c r="I101" s="168"/>
-      <c r="J101" s="168"/>
+      <c r="C101" s="157"/>
+      <c r="D101" s="157"/>
+      <c r="E101" s="157"/>
+      <c r="F101" s="157"/>
+      <c r="G101" s="157"/>
+      <c r="H101" s="157"/>
+      <c r="I101" s="157"/>
+      <c r="J101" s="157"/>
     </row>
     <row r="102" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B102" s="63" t="s">
@@ -8014,15 +8014,15 @@
         <f>IF(NOT(ISNUMBER($C$11)),"n/a",IF($C$11&gt;=5,"min. 30 cm","min. 40 cm"))</f>
         <v>min. 30 cm</v>
       </c>
-      <c r="D102" s="169" t="s">
+      <c r="D102" s="156" t="s">
         <v>209</v>
       </c>
-      <c r="E102" s="169"/>
-      <c r="F102" s="169"/>
-      <c r="G102" s="169"/>
-      <c r="H102" s="169"/>
-      <c r="I102" s="169"/>
-      <c r="J102" s="169"/>
+      <c r="E102" s="156"/>
+      <c r="F102" s="156"/>
+      <c r="G102" s="156"/>
+      <c r="H102" s="156"/>
+      <c r="I102" s="156"/>
+      <c r="J102" s="156"/>
     </row>
     <row r="103" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B103" s="63" t="s">
@@ -8032,15 +8032,15 @@
         <f>IF(OR($N$8="Uarmeret",$N$8="1 lag"),"n/a",IF(IFERROR(VLOOKUP($C$36,'6. DB Geonet'!$B$6:$K$25,2,FALSE()),"")="Tensar","20-40 cm","20-50 cm"))</f>
         <v>20-50 cm</v>
       </c>
-      <c r="D103" s="169" t="s">
+      <c r="D103" s="156" t="s">
         <v>211</v>
       </c>
-      <c r="E103" s="169"/>
-      <c r="F103" s="169"/>
-      <c r="G103" s="169"/>
-      <c r="H103" s="169"/>
-      <c r="I103" s="169"/>
-      <c r="J103" s="169"/>
+      <c r="E103" s="156"/>
+      <c r="F103" s="156"/>
+      <c r="G103" s="156"/>
+      <c r="H103" s="156"/>
+      <c r="I103" s="156"/>
+      <c r="J103" s="156"/>
     </row>
     <row r="104" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B104" s="63" t="s">
@@ -8050,15 +8050,15 @@
         <f>IF(OR($N$8="Uarmeret",$N$8="1 lag"),"n/a","min. 20 cm under overflade af bærelag")</f>
         <v>min. 20 cm under overflade af bærelag</v>
       </c>
-      <c r="D104" s="169" t="s">
+      <c r="D104" s="156" t="s">
         <v>213</v>
       </c>
-      <c r="E104" s="169"/>
-      <c r="F104" s="169"/>
-      <c r="G104" s="169"/>
-      <c r="H104" s="169"/>
-      <c r="I104" s="169"/>
-      <c r="J104" s="169"/>
+      <c r="E104" s="156"/>
+      <c r="F104" s="156"/>
+      <c r="G104" s="156"/>
+      <c r="H104" s="156"/>
+      <c r="I104" s="156"/>
+      <c r="J104" s="156"/>
     </row>
     <row r="105" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B105" s="63" t="s">
@@ -8067,15 +8067,15 @@
       <c r="C105" s="64" t="s">
         <v>215</v>
       </c>
-      <c r="D105" s="169" t="s">
+      <c r="D105" s="156" t="s">
         <v>216</v>
       </c>
-      <c r="E105" s="169"/>
-      <c r="F105" s="169"/>
-      <c r="G105" s="169"/>
-      <c r="H105" s="169"/>
-      <c r="I105" s="169"/>
-      <c r="J105" s="169"/>
+      <c r="E105" s="156"/>
+      <c r="F105" s="156"/>
+      <c r="G105" s="156"/>
+      <c r="H105" s="156"/>
+      <c r="I105" s="156"/>
+      <c r="J105" s="156"/>
     </row>
     <row r="106" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B106" s="63" t="s">
@@ -8084,18 +8084,80 @@
       <c r="C106" s="64" t="s">
         <v>218</v>
       </c>
-      <c r="D106" s="169" t="s">
+      <c r="D106" s="156" t="s">
         <v>219</v>
       </c>
-      <c r="E106" s="169"/>
-      <c r="F106" s="169"/>
-      <c r="G106" s="169"/>
-      <c r="H106" s="169"/>
-      <c r="I106" s="169"/>
-      <c r="J106" s="169"/>
+      <c r="E106" s="156"/>
+      <c r="F106" s="156"/>
+      <c r="G106" s="156"/>
+      <c r="H106" s="156"/>
+      <c r="I106" s="156"/>
+      <c r="J106" s="156"/>
     </row>
   </sheetData>
   <mergeCells count="71">
+    <mergeCell ref="B1:J1"/>
+    <mergeCell ref="B3:J3"/>
+    <mergeCell ref="M3:N3"/>
+    <mergeCell ref="B5:J5"/>
+    <mergeCell ref="B6:J6"/>
+    <mergeCell ref="D8:J8"/>
+    <mergeCell ref="D9:J9"/>
+    <mergeCell ref="B13:J13"/>
+    <mergeCell ref="B14:J14"/>
+    <mergeCell ref="C15:D15"/>
+    <mergeCell ref="D16:J16"/>
+    <mergeCell ref="B19:J19"/>
+    <mergeCell ref="B20:J20"/>
+    <mergeCell ref="C21:D21"/>
+    <mergeCell ref="E21:J21"/>
+    <mergeCell ref="E26:J26"/>
+    <mergeCell ref="C27:J27"/>
+    <mergeCell ref="D29:J29"/>
+    <mergeCell ref="B32:J32"/>
+    <mergeCell ref="B34:J34"/>
+    <mergeCell ref="B35:J35"/>
+    <mergeCell ref="C36:D36"/>
+    <mergeCell ref="E36:J36"/>
+    <mergeCell ref="D38:J38"/>
+    <mergeCell ref="B41:J41"/>
+    <mergeCell ref="B42:J42"/>
+    <mergeCell ref="B45:J45"/>
+    <mergeCell ref="D46:J46"/>
+    <mergeCell ref="D47:J47"/>
+    <mergeCell ref="F49:J49"/>
+    <mergeCell ref="B51:J51"/>
+    <mergeCell ref="D52:J52"/>
+    <mergeCell ref="D53:J53"/>
+    <mergeCell ref="D54:J54"/>
+    <mergeCell ref="D55:J55"/>
+    <mergeCell ref="B57:J57"/>
+    <mergeCell ref="C58:J58"/>
+    <mergeCell ref="C59:J59"/>
+    <mergeCell ref="C60:J60"/>
+    <mergeCell ref="C61:J61"/>
+    <mergeCell ref="C62:J62"/>
+    <mergeCell ref="C63:J63"/>
+    <mergeCell ref="C64:J64"/>
+    <mergeCell ref="C65:J65"/>
+    <mergeCell ref="B67:J67"/>
+    <mergeCell ref="B68:J68"/>
+    <mergeCell ref="B69:J69"/>
+    <mergeCell ref="C71:D71"/>
+    <mergeCell ref="E71:J71"/>
+    <mergeCell ref="B77:C77"/>
+    <mergeCell ref="C86:J86"/>
+    <mergeCell ref="C87:J87"/>
+    <mergeCell ref="D79:J79"/>
+    <mergeCell ref="D80:J80"/>
+    <mergeCell ref="C82:J82"/>
+    <mergeCell ref="B84:J84"/>
+    <mergeCell ref="C85:J85"/>
+    <mergeCell ref="B89:J89"/>
+    <mergeCell ref="B90:J90"/>
+    <mergeCell ref="B94:J94"/>
+    <mergeCell ref="D95:J95"/>
+    <mergeCell ref="D96:J96"/>
     <mergeCell ref="D103:J103"/>
     <mergeCell ref="D104:J104"/>
     <mergeCell ref="D105:J105"/>
@@ -8105,68 +8167,6 @@
     <mergeCell ref="D99:J99"/>
     <mergeCell ref="B101:J101"/>
     <mergeCell ref="D102:J102"/>
-    <mergeCell ref="B89:J89"/>
-    <mergeCell ref="B90:J90"/>
-    <mergeCell ref="B94:J94"/>
-    <mergeCell ref="D95:J95"/>
-    <mergeCell ref="D96:J96"/>
-    <mergeCell ref="C86:J86"/>
-    <mergeCell ref="C87:J87"/>
-    <mergeCell ref="D79:J79"/>
-    <mergeCell ref="D80:J80"/>
-    <mergeCell ref="C82:J82"/>
-    <mergeCell ref="B84:J84"/>
-    <mergeCell ref="C85:J85"/>
-    <mergeCell ref="B68:J68"/>
-    <mergeCell ref="B69:J69"/>
-    <mergeCell ref="C71:D71"/>
-    <mergeCell ref="E71:J71"/>
-    <mergeCell ref="B77:C77"/>
-    <mergeCell ref="C62:J62"/>
-    <mergeCell ref="C63:J63"/>
-    <mergeCell ref="C64:J64"/>
-    <mergeCell ref="C65:J65"/>
-    <mergeCell ref="B67:J67"/>
-    <mergeCell ref="B57:J57"/>
-    <mergeCell ref="C58:J58"/>
-    <mergeCell ref="C59:J59"/>
-    <mergeCell ref="C60:J60"/>
-    <mergeCell ref="C61:J61"/>
-    <mergeCell ref="B51:J51"/>
-    <mergeCell ref="D52:J52"/>
-    <mergeCell ref="D53:J53"/>
-    <mergeCell ref="D54:J54"/>
-    <mergeCell ref="D55:J55"/>
-    <mergeCell ref="B42:J42"/>
-    <mergeCell ref="B45:J45"/>
-    <mergeCell ref="D46:J46"/>
-    <mergeCell ref="D47:J47"/>
-    <mergeCell ref="F49:J49"/>
-    <mergeCell ref="B35:J35"/>
-    <mergeCell ref="C36:D36"/>
-    <mergeCell ref="E36:J36"/>
-    <mergeCell ref="D38:J38"/>
-    <mergeCell ref="B41:J41"/>
-    <mergeCell ref="E26:J26"/>
-    <mergeCell ref="C27:J27"/>
-    <mergeCell ref="D29:J29"/>
-    <mergeCell ref="B32:J32"/>
-    <mergeCell ref="B34:J34"/>
-    <mergeCell ref="D16:J16"/>
-    <mergeCell ref="B19:J19"/>
-    <mergeCell ref="B20:J20"/>
-    <mergeCell ref="C21:D21"/>
-    <mergeCell ref="E21:J21"/>
-    <mergeCell ref="D8:J8"/>
-    <mergeCell ref="D9:J9"/>
-    <mergeCell ref="B13:J13"/>
-    <mergeCell ref="B14:J14"/>
-    <mergeCell ref="C15:D15"/>
-    <mergeCell ref="B1:J1"/>
-    <mergeCell ref="B3:J3"/>
-    <mergeCell ref="M3:N3"/>
-    <mergeCell ref="B5:J5"/>
-    <mergeCell ref="B6:J6"/>
   </mergeCells>
   <conditionalFormatting sqref="C53">
     <cfRule type="expression" dxfId="17" priority="8">
@@ -8294,33 +8294,33 @@
   </cols>
   <sheetData>
     <row r="1" spans="2:8" ht="27.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B1" s="135" t="s">
+      <c r="B1" s="144" t="s">
         <v>220</v>
       </c>
-      <c r="C1" s="135"/>
-      <c r="D1" s="135"/>
+      <c r="C1" s="144"/>
+      <c r="D1" s="144"/>
     </row>
     <row r="3" spans="2:8" ht="45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B3" s="137" t="s">
+      <c r="B3" s="138" t="s">
         <v>221</v>
       </c>
-      <c r="C3" s="137"/>
-      <c r="D3" s="137"/>
+      <c r="C3" s="138"/>
+      <c r="D3" s="138"/>
     </row>
     <row r="5" spans="2:8" ht="21.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B5" s="149" t="s">
+      <c r="B5" s="151" t="s">
         <v>222</v>
       </c>
-      <c r="C5" s="149"/>
-      <c r="D5" s="149"/>
+      <c r="C5" s="151"/>
+      <c r="D5" s="151"/>
     </row>
     <row r="6" spans="2:8" ht="60" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B6" s="148" t="str">
+      <c r="B6" s="154" t="str">
         <f>"Vi starter med at fastlægge underbundens E-modul (Eu). Du har indtastet "&amp;IF('2. Dimensionering'!$C$7="Direkte (Eu)","Eu direkte: "&amp;TEXT('2. Dimensionering'!$C$11,"0")&amp;" MPa.","vingestyrke, og denne er omsat til Eu via opslag i konverteringstabellen (fane 7.4): Eu = "&amp;TEXT('2. Dimensionering'!$C$11,"0")&amp;" MPa.")</f>
         <v>Vi starter med at fastlægge underbundens E-modul (Eu). Du har indtastet Eu direkte: 10 MPa.</v>
       </c>
-      <c r="C6" s="148"/>
-      <c r="D6" s="148"/>
+      <c r="C6" s="154"/>
+      <c r="D6" s="154"/>
     </row>
     <row r="7" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B7" s="23" t="s">
@@ -8332,19 +8332,19 @@
       </c>
     </row>
     <row r="9" spans="2:8" ht="21.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B9" s="149" t="s">
+      <c r="B9" s="151" t="s">
         <v>224</v>
       </c>
-      <c r="C9" s="149"/>
-      <c r="D9" s="149"/>
+      <c r="C9" s="151"/>
+      <c r="D9" s="151"/>
     </row>
     <row r="10" spans="2:8" ht="45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B10" s="148" t="str">
+      <c r="B10" s="154" t="str">
         <f>"Det krævede E-modul på toppen af bærelaget (Eo) er fastlagt ud fra belastningsklassen. "&amp;"Du har valgt Eo = "&amp;TEXT('2. Dimensionering'!$C$17,"0")&amp;" MPa, som svarer til en standard belastningsklasse jf. GS-GRID Designmanual fig. 5."</f>
         <v>Det krævede E-modul på toppen af bærelaget (Eo) er fastlagt ud fra belastningsklassen. Du har valgt Eo = 150 MPa, som svarer til en standard belastningsklasse jf. GS-GRID Designmanual fig. 5.</v>
       </c>
-      <c r="C10" s="148"/>
-      <c r="D10" s="148"/>
+      <c r="C10" s="154"/>
+      <c r="D10" s="154"/>
     </row>
     <row r="11" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B11" s="23" t="s">
@@ -8359,19 +8359,19 @@
       </c>
     </row>
     <row r="13" spans="2:8" ht="21.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B13" s="149" t="s">
+      <c r="B13" s="151" t="s">
         <v>227</v>
       </c>
-      <c r="C13" s="149"/>
-      <c r="D13" s="149"/>
+      <c r="C13" s="151"/>
+      <c r="D13" s="151"/>
     </row>
     <row r="14" spans="2:8" ht="75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B14" s="148" t="str">
+      <c r="B14" s="154" t="str">
         <f>"Bærelagets friktionsvinkel (φ) er afgørende for hvor effektivt materialet kan fordele lasten. Værktøjet bruger φ = "&amp;TEXT('2. Dimensionering'!$C$30,"0,0")&amp;"°. "&amp;IF('2. Dimensionering'!$C$21="Lagtykkelser","I LAGTYKKELSE-MODE er φ vægtet efter de konkrete lagtykkelser: Σ(tykkelse_i × φ_i) / Σ(tykkelse_i). ","I PROCENT-MODE er φ vægtet efter de procentvise andele af materialerne. ")&amp;IF('2. Dimensionering'!$C$30&lt;=35,"Dette er minimum for friktionsmaterialer.","Da φ &gt; 35° giver dette en gunstig korrektion på bærelagstykkelsen (se trin 5).")</f>
         <v>Bærelagets friktionsvinkel (φ) er afgørende for hvor effektivt materialet kan fordele lasten. Værktøjet bruger φ = 37,5°. I LAGTYKKELSE-MODE er φ vægtet efter de konkrete lagtykkelser: Σ(tykkelse_i × φ_i) / Σ(tykkelse_i). Da φ &gt; 35° giver dette en gunstig korrektion på bærelagstykkelsen (se trin 5).</v>
       </c>
-      <c r="C14" s="148"/>
-      <c r="D14" s="148"/>
+      <c r="C14" s="154"/>
+      <c r="D14" s="154"/>
     </row>
     <row r="15" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B15" s="23" t="s">
@@ -8383,19 +8383,19 @@
       </c>
     </row>
     <row r="17" spans="2:4" ht="21.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B17" s="149" t="s">
+      <c r="B17" s="151" t="s">
         <v>229</v>
       </c>
-      <c r="C17" s="149"/>
-      <c r="D17" s="149"/>
+      <c r="C17" s="151"/>
+      <c r="D17" s="151"/>
     </row>
     <row r="18" spans="2:4" ht="75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B18" s="148" t="str">
+      <c r="B18" s="154" t="str">
         <f>"Vi slår nu op i designdiagrammet for Eo = "&amp;TEXT('2. Dimensionering'!$C$17,"0")&amp;" MPa (fane 7.1). Vi vælger kurven for "&amp;'2. Dimensionering'!$C$43&amp;" og finder bærelagstykkelsen ved Eu = "&amp;TEXT('2. Dimensionering'!$C$11,"0")&amp;" MPa. Da valgt/beregnet Eu kan ligge mellem to af tabellens værdier (I dette tilfælde "&amp;TEXT('2. Dimensionering'!$N$13,"0")&amp;" og "&amp;TEXT('2. Dimensionering'!$N$14,"0")&amp;" MPa), interpoleres lineært. Hvis Eu ligger på et punkt i tabellen, aflæses tabelværdien bare direkte"</f>
         <v>Vi slår nu op i designdiagrammet for Eo = 150 MPa (fane 7.1). Vi vælger kurven for 2 lag/flere lag og finder bærelagstykkelsen ved Eu = 10 MPa. Da valgt/beregnet Eu kan ligge mellem to af tabellens værdier (I dette tilfælde 10 og 12 MPa), interpoleres lineært. Hvis Eu ligger på et punkt i tabellen, aflæses tabelværdien bare direkte</v>
       </c>
-      <c r="C18" s="148"/>
-      <c r="D18" s="148"/>
+      <c r="C18" s="154"/>
+      <c r="D18" s="154"/>
     </row>
     <row r="19" spans="2:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B19" s="15" t="s">
@@ -8425,7 +8425,7 @@
     </row>
     <row r="21" spans="2:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B21" s="23" t="s">
-        <v>577</v>
+        <v>576</v>
       </c>
       <c r="C21" s="67">
         <f ca="1">'2. Dimensionering'!$N$18</f>
@@ -8433,19 +8433,19 @@
       </c>
     </row>
     <row r="23" spans="2:4" ht="21.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B23" s="149" t="s">
+      <c r="B23" s="151" t="s">
         <v>232</v>
       </c>
-      <c r="C23" s="149"/>
-      <c r="D23" s="149"/>
+      <c r="C23" s="151"/>
+      <c r="D23" s="151"/>
     </row>
     <row r="24" spans="2:4" ht="90" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B24" s="148" t="str">
+      <c r="B24" s="154" t="str">
         <f>"Designdiagrammet er baseret på et standard friktionsmateriale med φ ≈ 35°. Hvis dit materiale har en højere φ, kan bærelaget gøres tilsvarende tyndere. Korrektionen er −2 % per grad over 35° (fra Excel-arket AKK 2016). For φ = "&amp;TEXT('2. Dimensionering'!$C$30,"0,0")&amp;"° giver dette en korrektion på "&amp;TEXT('2. Dimensionering'!$N$20,"+0,0%;-0,0%")&amp;"."</f>
         <v>Designdiagrammet er baseret på et standard friktionsmateriale med φ ≈ 35°. Hvis dit materiale har en højere φ, kan bærelaget gøres tilsvarende tyndere. Korrektionen er −2 % per grad over 35° (fra Excel-arket AKK 2016). For φ = 37,5° giver dette en korrektion på -5,0%.</v>
       </c>
-      <c r="C24" s="148"/>
-      <c r="D24" s="148"/>
+      <c r="C24" s="154"/>
+      <c r="D24" s="154"/>
     </row>
     <row r="25" spans="2:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B25" s="23" t="s">
@@ -8457,19 +8457,19 @@
       </c>
     </row>
     <row r="27" spans="2:4" ht="21.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B27" s="149" t="s">
+      <c r="B27" s="151" t="s">
         <v>233</v>
       </c>
-      <c r="C27" s="149"/>
-      <c r="D27" s="149"/>
+      <c r="C27" s="151"/>
+      <c r="D27" s="151"/>
     </row>
     <row r="28" spans="2:4" ht="105" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B28" s="148" t="str">
+      <c r="B28" s="154" t="str">
         <f>"Designdiagrammet bruger GS-GRID SX160 / E'GRID T6 (eller TriAx TX160) som reference-armering (effektindeks 100). Hvis du har valgt en anden armering, skaleres tykkelsen op eller ned. Du har valgt: "&amp;'2. Dimensionering'!$C$36&amp;". Det giver en korrektion på "&amp;TEXT('2. Dimensionering'!$C$39,"+0,0%;-0,0%")&amp;". Bemærk: positiv = tykkere bærelag (mindre effektiv armering), negativ = tyndere bærelag (mere effektiv armering)."</f>
         <v>Designdiagrammet bruger GS-GRID SX160 / E'GRID T6 (eller TriAx TX160) som reference-armering (effektindeks 100). Hvis du har valgt en anden armering, skaleres tykkelsen op eller ned. Du har valgt: GS-GRID SX170. Det giver en korrektion på -10,0%. Bemærk: positiv = tykkere bærelag (mindre effektiv armering), negativ = tyndere bærelag (mere effektiv armering).</v>
       </c>
-      <c r="C28" s="148"/>
-      <c r="D28" s="148"/>
+      <c r="C28" s="154"/>
+      <c r="D28" s="154"/>
     </row>
     <row r="29" spans="2:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B29" s="23" t="s">
@@ -8481,26 +8481,26 @@
       </c>
     </row>
     <row r="31" spans="2:4" ht="21.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B31" s="149" t="s">
+      <c r="B31" s="151" t="s">
         <v>235</v>
       </c>
-      <c r="C31" s="149"/>
-      <c r="D31" s="149"/>
+      <c r="C31" s="151"/>
+      <c r="D31" s="151"/>
     </row>
     <row r="32" spans="2:4" ht="60" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B32" s="148" t="s">
+      <c r="B32" s="154" t="s">
         <v>236</v>
       </c>
-      <c r="C32" s="148"/>
-      <c r="D32" s="148"/>
+      <c r="C32" s="154"/>
+      <c r="D32" s="154"/>
     </row>
     <row r="33" spans="2:4" ht="34.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B33" s="148" t="str">
+      <c r="B33" s="154" t="str">
         <f ca="1">CONCATENATE("T_armeret = T_basis × (1 + φ-korr + net-korr) = ",TEXT('2. Dimensionering'!$N$18,"0")," mm × ",TEXT('2. Dimensionering'!$N$22,"0.000")," = ",TEXT('2. Dimensionering'!$C$47,"0")," mm")</f>
         <v>T_armeret = T_basis × (1 + φ-korr + net-korr) = 667 mm × 0.001 = 567 mm</v>
       </c>
-      <c r="C33" s="148"/>
-      <c r="D33" s="148"/>
+      <c r="C33" s="154"/>
+      <c r="D33" s="154"/>
     </row>
     <row r="34" spans="2:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B34" s="23" t="s">
@@ -8512,38 +8512,38 @@
       </c>
     </row>
     <row r="36" spans="2:4" ht="21.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B36" s="149"/>
-      <c r="C36" s="149"/>
-      <c r="D36" s="149"/>
+      <c r="B36" s="151"/>
+      <c r="C36" s="151"/>
+      <c r="D36" s="151"/>
     </row>
     <row r="37" spans="2:4" ht="75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B37" s="148"/>
-      <c r="C37" s="148"/>
-      <c r="D37" s="148"/>
+      <c r="B37" s="154"/>
+      <c r="C37" s="154"/>
+      <c r="D37" s="154"/>
     </row>
     <row r="38" spans="2:4" ht="30" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B38" s="148"/>
-      <c r="C38" s="148"/>
-      <c r="D38" s="148"/>
+      <c r="B38" s="154"/>
+      <c r="C38" s="154"/>
+      <c r="D38" s="154"/>
     </row>
     <row r="39" spans="2:4" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B39" s="23"/>
       <c r="C39" s="59"/>
     </row>
     <row r="41" spans="2:4" ht="21.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B41" s="149" t="s">
+      <c r="B41" s="151" t="s">
         <v>238</v>
       </c>
-      <c r="C41" s="149"/>
-      <c r="D41" s="149"/>
+      <c r="C41" s="151"/>
+      <c r="D41" s="151"/>
     </row>
     <row r="42" spans="2:4" ht="90" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B42" s="148" t="str">
+      <c r="B42" s="154" t="str">
         <f ca="1">IFERROR("Hvis vi havde lavet samme opbygning UDEN armering, ville bærelaget skulle være "&amp;TEXT('2. Dimensionering'!$C$46,"0")&amp;" mm tykt. Med din valgte armering reduceres tykkelsen til "&amp;TEXT('2. Dimensionering'!$C$47,"0")&amp;" mm. Det er en reduktion på "&amp;TEXT('2. Dimensionering'!$C$46-'2. Dimensionering'!$C$47,"0")&amp;" mm svarende til "&amp;TEXT(('2. Dimensionering'!$C$46-'2. Dimensionering'!$C$47)/'2. Dimensionering'!$C$46,"0%")&amp;" — den væsentligste fordel ved at bruge geonet i denne opbygning.","(Beregning ikke mulig — tjek input på fane 2)")</f>
         <v>Hvis vi havde lavet samme opbygning UDEN armering, ville bærelaget skulle være 1100 mm tykt. Med din valgte armering reduceres tykkelsen til 567 mm. Det er en reduktion på 533 mm svarende til 48% — den væsentligste fordel ved at bruge geonet i denne opbygning.</v>
       </c>
-      <c r="C42" s="148"/>
-      <c r="D42" s="148"/>
+      <c r="C42" s="154"/>
+      <c r="D42" s="154"/>
     </row>
     <row r="44" spans="2:4" ht="27.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B44" s="69" t="s">
@@ -8553,12 +8553,12 @@
       <c r="D44" s="70"/>
     </row>
     <row r="45" spans="2:4" ht="90" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B45" s="170" t="str">
+      <c r="B45" s="172" t="str">
         <f ca="1">IF('2. Dimensionering'!$C$21&lt;&gt;"Lagtykkelser","ⓘ Dette trin er kun aktivt i lagtykkelse-mode. Skift indtastningsmetode i Sektion C på fane 2 for at se forklaringen.","I lagtykkelse-mode har du indtastet konkrete tykkelser for hvert lag, og værktøjet kan derfor sammenligne din planlagte opbygning med både uarmeret og armeret krav. Din planlagte total er "&amp;TEXT('2. Dimensionering'!$C$52,"0")&amp;" mm. Sammenlignet med det uarmerede krav på "&amp;TEXT('2. Dimensionering'!$C$46,"0")&amp;" mm har din plan "&amp;IF('2. Dimensionering'!$C$53&gt;=0,"+"&amp;TEXT('2. Dimensionering'!$C$53,"0")&amp;" mm slæk (tilstrækkelig).",TEXT('2. Dimensionering'!$C$53,"0")&amp;" mm — utilstrækkelig uden armering.")&amp;" Sammenlignet med det armerede krav på "&amp;TEXT('2. Dimensionering'!$C$47,"0")&amp;" mm har din plan "&amp;IF('2. Dimensionering'!$C$54&gt;=0,"+"&amp;TEXT('2. Dimensionering'!$C$54,"0")&amp;" mm slæk (tilstrækkelig med armering).",TEXT('2. Dimensionering'!$C$54,"0")&amp;" mm — utilstrækkelig selv med armering.")&amp;" Den mulige besparelse fra din plan ved armering er dermed "&amp;TEXT('2. Dimensionering'!$C$55,"0")&amp;" mm.")</f>
         <v>I lagtykkelse-mode har du indtastet konkrete tykkelser for hvert lag, og værktøjet kan derfor sammenligne din planlagte opbygning med både uarmeret og armeret krav. Din planlagte total er 600 mm. Sammenlignet med det uarmerede krav på 1100 mm har din plan -500 mm — utilstrækkelig uden armering. Sammenlignet med det armerede krav på 567 mm har din plan +33 mm slæk (tilstrækkelig med armering). Den mulige besparelse fra din plan ved armering er dermed 33 mm.</v>
       </c>
-      <c r="C45" s="170"/>
-      <c r="D45" s="170"/>
+      <c r="C45" s="172"/>
+      <c r="D45" s="172"/>
     </row>
     <row r="46" spans="2:4" ht="6" customHeight="1" x14ac:dyDescent="0.25"/>
     <row r="47" spans="2:4" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
@@ -8603,19 +8603,19 @@
     </row>
     <row r="51" spans="2:5" ht="7.5" customHeight="1" x14ac:dyDescent="0.25"/>
     <row r="52" spans="2:5" ht="27.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B52" s="171" t="s">
+      <c r="B52" s="173" t="s">
         <v>244</v>
       </c>
-      <c r="C52" s="171"/>
-      <c r="D52" s="171"/>
+      <c r="C52" s="173"/>
+      <c r="D52" s="173"/>
     </row>
     <row r="53" spans="2:5" ht="72" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B53" s="170" t="str">
+      <c r="B53" s="172" t="str">
         <f>IF('2. Dimensionering'!$C$21&lt;&gt;"Lagtykkelser","ⓘ Dette trin er kun aktivt i lagtykkelse-mode.","Når armeringen tillader at du reducerer opbygningen, skal de sparede millimeter tages et eller flere steder. Du har valgt strategien """&amp;'2. Dimensionering'!$C$71&amp;""". "&amp;IF('2. Dimensionering'!$C$71="Reducer bærelag",_xlfn._LONGTEXT("Denne strategi reducerer udelukkende bærelaget/bærelagene (typisk stabilgrus eller knust beton). Hvis du har flere bærelag fordeles reduktionen proportionalt mellem dem. Bundsikringen bevares uændret. Vær opmærksom: hvis bærelaget bliver meget tyndt, kan ","dæklags-kravet på 200 mm være underskredet."),IF('2. Dimensionering'!$C$71="Reducer bundsikring",_xlfn._LONGTEXT("Denne strategi reducerer udelukkende bundsikringen, og bevarer bærelaget i sin oprindelige tykkelse. Det er ofte det praktisk mest meningsfulde valg, fordi bærelaget (stabilgrus) er det dyre kvalitetsmateriale du gerne vil beholde i fuld tykkelse for kørs","elsoverflade. Bundsikringen er det billigere drænende lag der reduceres."),IF('2. Dimensionering'!$C$71="Reducer alle proportionalt","Denne strategi reducerer alle lag med samme procent. Forholdet mellem bærelag og bundsikring bevares præcis. Det er en god strategi hvis du har specifikationer der kræver et bestemt forhold mellem lagene.","Denne strategi giver dig fuld kontrol — du indtaster selv de ønskede lagtykkelser i kolonnen ""Manuel (mm)"" på fane 2. Værktøjet validerer at den samlede tykkelse opfylder armeret krav."))))</f>
         <v>Når armeringen tillader at du reducerer opbygningen, skal de sparede millimeter tages et eller flere steder. Du har valgt strategien "Manuel justering". Denne strategi giver dig fuld kontrol — du indtaster selv de ønskede lagtykkelser i kolonnen "Manuel (mm)" på fane 2. Værktøjet validerer at den samlede tykkelse opfylder armeret krav.</v>
       </c>
-      <c r="C53" s="170"/>
-      <c r="D53" s="170"/>
+      <c r="C53" s="172"/>
+      <c r="D53" s="172"/>
     </row>
     <row r="54" spans="2:5" ht="6" customHeight="1" x14ac:dyDescent="0.25"/>
     <row r="55" spans="2:5" ht="21.75" customHeight="1" x14ac:dyDescent="0.25">
@@ -8699,12 +8699,12 @@
     </row>
     <row r="60" spans="2:5" ht="6" customHeight="1" x14ac:dyDescent="0.25"/>
     <row r="61" spans="2:5" ht="36" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B61" s="170" t="str">
+      <c r="B61" s="172" t="str">
         <f>IF('2. Dimensionering'!$C$21&lt;&gt;"Lagtykkelser","",IF(ISNUMBER('2. Dimensionering'!$C$80),"Med denne strategi sparer du "&amp;TEXT('2. Dimensionering'!$C$80,"0")&amp;" mm i forhold til din oprindelige plan. Det svarer til "&amp;TEXT(IFERROR('2. Dimensionering'!$C$80/'2. Dimensionering'!$C$52,0),"0%")&amp;" reduktion af den samlede opbygning.",""))</f>
         <v>Med denne strategi sparer du 0 mm i forhold til din oprindelige plan. Det svarer til 0% reduktion af den samlede opbygning.</v>
       </c>
-      <c r="C61" s="170"/>
-      <c r="D61" s="170"/>
+      <c r="C61" s="172"/>
+      <c r="D61" s="172"/>
     </row>
     <row r="62" spans="2:5" ht="7.5" customHeight="1" x14ac:dyDescent="0.25"/>
     <row r="63" spans="2:5" ht="27.75" customHeight="1" x14ac:dyDescent="0.3">
@@ -8715,86 +8715,86 @@
       <c r="D63" s="70"/>
     </row>
     <row r="64" spans="2:5" ht="90" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B64" s="170" t="str">
+      <c r="B64" s="172" t="str">
         <f>IF('2. Dimensionering'!$C$21&lt;&gt;"Lagtykkelser","ⓘ Dette trin er kun aktivt i lagtykkelse-mode.","Geonettets placering afhænger af antallet af lag og opbygningens struktur. For din aktuelle opbygning: "&amp;'2. Dimensionering'!$C$82&amp;_xlfn._LONGTEXT(". Reglen er at geonettet altid placeres i laggrænsen mellem to materialer (når der er flere lag) eller i bunden af et homogent lag. Geonettet skal have minimum 200 mm dæklag af bærelagsmateriale over sig for at opnå armeringseffekt — det er en praktisk gr","ænse fra designmanualerne. Hvis dit foreslåede design har et lag tyndere end 200 mm, vil værktøjet vise en advarsel i Sektion H."))</f>
         <v>Geonettets placering afhænger af antallet af lag og opbygningens struktur. For din aktuelle opbygning: 2 net: ét ved laggrænsen mellem bærelag og bundsikring, og ét ved bunden mod råjordsplanum. Reglen er at geonettet altid placeres i laggrænsen mellem to materialer (når der er flere lag) eller i bunden af et homogent lag. Geonettet skal have minimum 200 mm dæklag af bærelagsmateriale over sig for at opnå armeringseffekt — det er en praktisk grænse fra designmanualerne. Hvis dit foreslåede design har et lag tyndere end 200 mm, vil værktøjet vise en advarsel i Sektion H.</v>
       </c>
-      <c r="C64" s="170"/>
-      <c r="D64" s="170"/>
+      <c r="C64" s="172"/>
+      <c r="D64" s="172"/>
     </row>
     <row r="65" spans="2:4" ht="7.5" customHeight="1" x14ac:dyDescent="0.25"/>
     <row r="66" spans="2:4" ht="21.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B66" s="149" t="s">
+      <c r="B66" s="151" t="s">
         <v>247</v>
       </c>
-      <c r="C66" s="149"/>
-      <c r="D66" s="149"/>
+      <c r="C66" s="151"/>
+      <c r="D66" s="151"/>
     </row>
     <row r="67" spans="2:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B67" s="172" t="s">
+      <c r="B67" s="171" t="s">
         <v>248</v>
       </c>
-      <c r="C67" s="172"/>
-      <c r="D67" s="172"/>
+      <c r="C67" s="171"/>
+      <c r="D67" s="171"/>
     </row>
     <row r="68" spans="2:4" ht="45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B68" s="148" t="s">
+      <c r="B68" s="154" t="s">
         <v>249</v>
       </c>
-      <c r="C68" s="148"/>
-      <c r="D68" s="148"/>
+      <c r="C68" s="154"/>
+      <c r="D68" s="154"/>
     </row>
     <row r="69" spans="2:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B69" s="172" t="s">
+      <c r="B69" s="171" t="s">
         <v>250</v>
       </c>
-      <c r="C69" s="172"/>
-      <c r="D69" s="172"/>
+      <c r="C69" s="171"/>
+      <c r="D69" s="171"/>
     </row>
     <row r="70" spans="2:4" ht="45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B70" s="148" t="s">
+      <c r="B70" s="154" t="s">
         <v>251</v>
       </c>
-      <c r="C70" s="148"/>
-      <c r="D70" s="148"/>
+      <c r="C70" s="154"/>
+      <c r="D70" s="154"/>
     </row>
     <row r="71" spans="2:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B71" s="172" t="s">
+      <c r="B71" s="171" t="s">
         <v>252</v>
       </c>
-      <c r="C71" s="172"/>
-      <c r="D71" s="172"/>
+      <c r="C71" s="171"/>
+      <c r="D71" s="171"/>
     </row>
     <row r="72" spans="2:4" ht="45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B72" s="148" t="s">
+      <c r="B72" s="154" t="s">
         <v>253</v>
       </c>
-      <c r="C72" s="148"/>
-      <c r="D72" s="148"/>
+      <c r="C72" s="154"/>
+      <c r="D72" s="154"/>
     </row>
     <row r="73" spans="2:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B73" s="172"/>
-      <c r="C73" s="172"/>
-      <c r="D73" s="172"/>
+      <c r="B73" s="171"/>
+      <c r="C73" s="171"/>
+      <c r="D73" s="171"/>
     </row>
     <row r="74" spans="2:4" ht="45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B74" s="148"/>
-      <c r="C74" s="148"/>
-      <c r="D74" s="148"/>
+      <c r="B74" s="154"/>
+      <c r="C74" s="154"/>
+      <c r="D74" s="154"/>
     </row>
     <row r="75" spans="2:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B75" s="172" t="s">
+      <c r="B75" s="171" t="s">
         <v>254</v>
       </c>
-      <c r="C75" s="172"/>
-      <c r="D75" s="172"/>
+      <c r="C75" s="171"/>
+      <c r="D75" s="171"/>
     </row>
     <row r="76" spans="2:4" ht="45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B76" s="148" t="s">
+      <c r="B76" s="154" t="s">
         <v>255</v>
       </c>
-      <c r="C76" s="148"/>
-      <c r="D76" s="148"/>
+      <c r="C76" s="154"/>
+      <c r="D76" s="154"/>
     </row>
     <row r="77" spans="2:4" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B77" s="82" t="s">
@@ -8802,14 +8802,44 @@
       </c>
     </row>
     <row r="78" spans="2:4" ht="60" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B78" s="170" t="s">
+      <c r="B78" s="172" t="s">
         <v>257</v>
       </c>
-      <c r="C78" s="170"/>
-      <c r="D78" s="170"/>
+      <c r="C78" s="172"/>
+      <c r="D78" s="172"/>
     </row>
   </sheetData>
   <mergeCells count="39">
+    <mergeCell ref="B1:D1"/>
+    <mergeCell ref="B3:D3"/>
+    <mergeCell ref="B5:D5"/>
+    <mergeCell ref="B6:D6"/>
+    <mergeCell ref="B9:D9"/>
+    <mergeCell ref="B10:D10"/>
+    <mergeCell ref="B13:D13"/>
+    <mergeCell ref="B14:D14"/>
+    <mergeCell ref="B17:D17"/>
+    <mergeCell ref="B18:D18"/>
+    <mergeCell ref="B23:D23"/>
+    <mergeCell ref="B24:D24"/>
+    <mergeCell ref="B27:D27"/>
+    <mergeCell ref="B28:D28"/>
+    <mergeCell ref="B31:D31"/>
+    <mergeCell ref="B32:D32"/>
+    <mergeCell ref="B33:D33"/>
+    <mergeCell ref="B36:D36"/>
+    <mergeCell ref="B37:D37"/>
+    <mergeCell ref="B38:D38"/>
+    <mergeCell ref="B41:D41"/>
+    <mergeCell ref="B42:D42"/>
+    <mergeCell ref="B45:D45"/>
+    <mergeCell ref="B52:D52"/>
+    <mergeCell ref="B53:D53"/>
+    <mergeCell ref="B61:D61"/>
+    <mergeCell ref="B64:D64"/>
+    <mergeCell ref="B66:D66"/>
+    <mergeCell ref="B67:D67"/>
+    <mergeCell ref="B68:D68"/>
     <mergeCell ref="B74:D74"/>
     <mergeCell ref="B75:D75"/>
     <mergeCell ref="B76:D76"/>
@@ -8819,36 +8849,6 @@
     <mergeCell ref="B71:D71"/>
     <mergeCell ref="B72:D72"/>
     <mergeCell ref="B73:D73"/>
-    <mergeCell ref="B61:D61"/>
-    <mergeCell ref="B64:D64"/>
-    <mergeCell ref="B66:D66"/>
-    <mergeCell ref="B67:D67"/>
-    <mergeCell ref="B68:D68"/>
-    <mergeCell ref="B41:D41"/>
-    <mergeCell ref="B42:D42"/>
-    <mergeCell ref="B45:D45"/>
-    <mergeCell ref="B52:D52"/>
-    <mergeCell ref="B53:D53"/>
-    <mergeCell ref="B32:D32"/>
-    <mergeCell ref="B33:D33"/>
-    <mergeCell ref="B36:D36"/>
-    <mergeCell ref="B37:D37"/>
-    <mergeCell ref="B38:D38"/>
-    <mergeCell ref="B23:D23"/>
-    <mergeCell ref="B24:D24"/>
-    <mergeCell ref="B27:D27"/>
-    <mergeCell ref="B28:D28"/>
-    <mergeCell ref="B31:D31"/>
-    <mergeCell ref="B10:D10"/>
-    <mergeCell ref="B13:D13"/>
-    <mergeCell ref="B14:D14"/>
-    <mergeCell ref="B17:D17"/>
-    <mergeCell ref="B18:D18"/>
-    <mergeCell ref="B1:D1"/>
-    <mergeCell ref="B3:D3"/>
-    <mergeCell ref="B5:D5"/>
-    <mergeCell ref="B6:D6"/>
-    <mergeCell ref="B9:D9"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300"/>
@@ -8870,31 +8870,31 @@
   </cols>
   <sheetData>
     <row r="1" spans="2:6" ht="27.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B1" s="135" t="s">
+      <c r="B1" s="144" t="s">
         <v>258</v>
       </c>
-      <c r="C1" s="135"/>
-      <c r="D1" s="135"/>
-      <c r="E1" s="135"/>
-      <c r="F1" s="135"/>
+      <c r="C1" s="144"/>
+      <c r="D1" s="144"/>
+      <c r="E1" s="144"/>
+      <c r="F1" s="144"/>
     </row>
     <row r="3" spans="2:6" ht="60" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B3" s="137" t="s">
+      <c r="B3" s="138" t="s">
         <v>259</v>
       </c>
-      <c r="C3" s="137"/>
-      <c r="D3" s="137"/>
-      <c r="E3" s="137"/>
-      <c r="F3" s="137"/>
+      <c r="C3" s="138"/>
+      <c r="D3" s="138"/>
+      <c r="E3" s="138"/>
+      <c r="F3" s="138"/>
     </row>
     <row r="5" spans="2:6" ht="21.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B5" s="149" t="s">
+      <c r="B5" s="151" t="s">
         <v>260</v>
       </c>
-      <c r="C5" s="149"/>
-      <c r="D5" s="149"/>
-      <c r="E5" s="149"/>
-      <c r="F5" s="149"/>
+      <c r="C5" s="151"/>
+      <c r="D5" s="151"/>
+      <c r="E5" s="151"/>
+      <c r="F5" s="151"/>
     </row>
     <row r="6" spans="2:6" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B6" s="33" t="s">
@@ -8955,22 +8955,22 @@
       </c>
     </row>
     <row r="11" spans="2:6" ht="21.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B11" s="149" t="s">
+      <c r="B11" s="151" t="s">
         <v>271</v>
       </c>
-      <c r="C11" s="149"/>
-      <c r="D11" s="149"/>
-      <c r="E11" s="149"/>
-      <c r="F11" s="149"/>
+      <c r="C11" s="151"/>
+      <c r="D11" s="151"/>
+      <c r="E11" s="151"/>
+      <c r="F11" s="151"/>
     </row>
     <row r="12" spans="2:6" ht="56.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B12" s="137" t="s">
+      <c r="B12" s="138" t="s">
         <v>272</v>
       </c>
-      <c r="C12" s="137"/>
-      <c r="D12" s="137"/>
-      <c r="E12" s="137"/>
-      <c r="F12" s="137"/>
+      <c r="C12" s="138"/>
+      <c r="D12" s="138"/>
+      <c r="E12" s="138"/>
+      <c r="F12" s="138"/>
     </row>
     <row r="13" spans="2:6" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B13" s="33" t="s">
@@ -9304,22 +9304,22 @@
   </cols>
   <sheetData>
     <row r="1" spans="2:6" ht="27.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B1" s="135" t="s">
+      <c r="B1" s="144" t="s">
         <v>301</v>
       </c>
-      <c r="C1" s="135"/>
-      <c r="D1" s="135"/>
-      <c r="E1" s="135"/>
-      <c r="F1" s="135"/>
+      <c r="C1" s="144"/>
+      <c r="D1" s="144"/>
+      <c r="E1" s="144"/>
+      <c r="F1" s="144"/>
     </row>
     <row r="3" spans="2:6" ht="69.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B3" s="137" t="s">
+      <c r="B3" s="138" t="s">
         <v>302</v>
       </c>
-      <c r="C3" s="137"/>
-      <c r="D3" s="137"/>
-      <c r="E3" s="137"/>
-      <c r="F3" s="137"/>
+      <c r="C3" s="138"/>
+      <c r="D3" s="138"/>
+      <c r="E3" s="138"/>
+      <c r="F3" s="138"/>
     </row>
     <row r="5" spans="2:6" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B5" s="33" t="s">
@@ -9357,13 +9357,13 @@
     </row>
     <row r="7" spans="2:6" ht="21.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B7" s="92" t="s">
-        <v>307</v>
+        <v>590</v>
       </c>
       <c r="C7" s="93">
         <v>38</v>
       </c>
       <c r="D7" s="94">
-        <v>80</v>
+        <v>8</v>
       </c>
       <c r="E7" s="95" t="s">
         <v>305</v>
@@ -9374,7 +9374,7 @@
     </row>
     <row r="8" spans="2:6" ht="21.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B8" s="92" t="s">
-        <v>308</v>
+        <v>307</v>
       </c>
       <c r="C8" s="93">
         <v>40</v>
@@ -9383,10 +9383,10 @@
         <v>32</v>
       </c>
       <c r="E8" s="96" t="s">
+        <v>308</v>
+      </c>
+      <c r="F8" s="11" t="s">
         <v>309</v>
-      </c>
-      <c r="F8" s="11" t="s">
-        <v>310</v>
       </c>
     </row>
     <row r="9" spans="2:6" ht="21.75" customHeight="1" x14ac:dyDescent="0.25">
@@ -9400,15 +9400,15 @@
         <v>32</v>
       </c>
       <c r="E9" s="96" t="s">
-        <v>309</v>
+        <v>308</v>
       </c>
       <c r="F9" s="11" t="s">
-        <v>311</v>
+        <v>310</v>
       </c>
     </row>
     <row r="10" spans="2:6" ht="21.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B10" s="92" t="s">
-        <v>312</v>
+        <v>311</v>
       </c>
       <c r="C10" s="93">
         <v>40</v>
@@ -9417,15 +9417,15 @@
         <v>32</v>
       </c>
       <c r="E10" s="96" t="s">
-        <v>309</v>
+        <v>308</v>
       </c>
       <c r="F10" s="11" t="s">
-        <v>313</v>
+        <v>312</v>
       </c>
     </row>
     <row r="11" spans="2:6" ht="21.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B11" s="92" t="s">
-        <v>314</v>
+        <v>313</v>
       </c>
       <c r="C11" s="93">
         <v>45</v>
@@ -9434,15 +9434,15 @@
         <v>32</v>
       </c>
       <c r="E11" s="96" t="s">
-        <v>309</v>
+        <v>308</v>
       </c>
       <c r="F11" s="11" t="s">
-        <v>315</v>
+        <v>314</v>
       </c>
     </row>
     <row r="12" spans="2:6" ht="21.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B12" s="92" t="s">
-        <v>316</v>
+        <v>315</v>
       </c>
       <c r="C12" s="93">
         <v>45</v>
@@ -9451,15 +9451,15 @@
         <v>64</v>
       </c>
       <c r="E12" s="96" t="s">
-        <v>309</v>
+        <v>308</v>
       </c>
       <c r="F12" s="11" t="s">
-        <v>309</v>
+        <v>308</v>
       </c>
     </row>
     <row r="13" spans="2:6" ht="21.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B13" s="92" t="s">
-        <v>317</v>
+        <v>316</v>
       </c>
       <c r="C13" s="93">
         <v>45</v>
@@ -9468,15 +9468,15 @@
         <v>90</v>
       </c>
       <c r="E13" s="96" t="s">
-        <v>309</v>
+        <v>308</v>
       </c>
       <c r="F13" s="11" t="s">
-        <v>318</v>
+        <v>317</v>
       </c>
     </row>
     <row r="14" spans="2:6" ht="21.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B14" s="92" t="s">
-        <v>319</v>
+        <v>318</v>
       </c>
       <c r="C14" s="93">
         <v>45</v>
@@ -9493,7 +9493,7 @@
     </row>
     <row r="15" spans="2:6" ht="21.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B15" s="92" t="s">
-        <v>320</v>
+        <v>319</v>
       </c>
       <c r="C15" s="93">
         <v>45</v>
@@ -9505,12 +9505,12 @@
         <v>305</v>
       </c>
       <c r="F15" s="11" t="s">
-        <v>321</v>
+        <v>320</v>
       </c>
     </row>
     <row r="16" spans="2:6" ht="21.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B16" s="92" t="s">
-        <v>322</v>
+        <v>321</v>
       </c>
       <c r="C16" s="93">
         <v>45</v>
@@ -9522,12 +9522,12 @@
         <v>305</v>
       </c>
       <c r="F16" s="11" t="s">
-        <v>323</v>
+        <v>322</v>
       </c>
     </row>
     <row r="17" spans="2:6" ht="21.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B17" s="92" t="s">
-        <v>324</v>
+        <v>323</v>
       </c>
       <c r="C17" s="93">
         <v>45</v>
@@ -9539,42 +9539,42 @@
         <v>305</v>
       </c>
       <c r="F17" s="11" t="s">
-        <v>325</v>
+        <v>324</v>
       </c>
     </row>
     <row r="18" spans="2:6" ht="24" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B18" s="92" t="s">
-        <v>326</v>
+        <v>325</v>
       </c>
       <c r="C18" s="97"/>
       <c r="D18" s="97"/>
       <c r="E18" s="97"/>
       <c r="F18" s="98" t="s">
-        <v>327</v>
+        <v>326</v>
       </c>
     </row>
     <row r="20" spans="2:6" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B20" s="23" t="s">
-        <v>328</v>
+        <v>327</v>
       </c>
     </row>
     <row r="21" spans="2:6" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B21" s="61"/>
-      <c r="C21" s="154" t="s">
-        <v>329</v>
-      </c>
-      <c r="D21" s="154"/>
-      <c r="E21" s="154"/>
-      <c r="F21" s="154"/>
+      <c r="C21" s="148" t="s">
+        <v>328</v>
+      </c>
+      <c r="D21" s="148"/>
+      <c r="E21" s="148"/>
+      <c r="F21" s="148"/>
     </row>
     <row r="22" spans="2:6" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B22" s="62"/>
-      <c r="C22" s="154" t="s">
-        <v>330</v>
-      </c>
-      <c r="D22" s="154"/>
-      <c r="E22" s="154"/>
-      <c r="F22" s="154"/>
+      <c r="C22" s="148" t="s">
+        <v>329</v>
+      </c>
+      <c r="D22" s="148"/>
+      <c r="E22" s="148"/>
+      <c r="F22" s="148"/>
     </row>
   </sheetData>
   <mergeCells count="4">
@@ -9613,71 +9613,71 @@
   </cols>
   <sheetData>
     <row r="1" spans="2:17" ht="27.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B1" s="135" t="s">
+      <c r="B1" s="144" t="s">
+        <v>330</v>
+      </c>
+      <c r="C1" s="144"/>
+      <c r="D1" s="144"/>
+      <c r="E1" s="144"/>
+      <c r="F1" s="144"/>
+      <c r="G1" s="144"/>
+      <c r="H1" s="144"/>
+      <c r="I1" s="144"/>
+      <c r="J1" s="144"/>
+    </row>
+    <row r="3" spans="2:17" ht="42.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B3" s="138" t="s">
         <v>331</v>
       </c>
-      <c r="C1" s="135"/>
-      <c r="D1" s="135"/>
-      <c r="E1" s="135"/>
-      <c r="F1" s="135"/>
-      <c r="G1" s="135"/>
-      <c r="H1" s="135"/>
-      <c r="I1" s="135"/>
-      <c r="J1" s="135"/>
-    </row>
-    <row r="3" spans="2:17" ht="42.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B3" s="137" t="s">
-        <v>332</v>
-      </c>
-      <c r="C3" s="137"/>
-      <c r="D3" s="137"/>
-      <c r="E3" s="137"/>
-      <c r="F3" s="137"/>
-      <c r="G3" s="137"/>
-      <c r="H3" s="137"/>
-      <c r="I3" s="137"/>
-      <c r="J3" s="137"/>
+      <c r="C3" s="138"/>
+      <c r="D3" s="138"/>
+      <c r="E3" s="138"/>
+      <c r="F3" s="138"/>
+      <c r="G3" s="138"/>
+      <c r="H3" s="138"/>
+      <c r="I3" s="138"/>
+      <c r="J3" s="138"/>
     </row>
     <row r="4" spans="2:17" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="L4" s="143" t="s">
-        <v>567</v>
-      </c>
-      <c r="M4" s="173"/>
-      <c r="N4" s="173"/>
-      <c r="O4" s="173"/>
-      <c r="P4" s="173"/>
-      <c r="Q4" s="174"/>
+        <v>566</v>
+      </c>
+      <c r="M4" s="174"/>
+      <c r="N4" s="174"/>
+      <c r="O4" s="174"/>
+      <c r="P4" s="174"/>
+      <c r="Q4" s="175"/>
     </row>
     <row r="5" spans="2:17" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B5" s="33" t="s">
         <v>273</v>
       </c>
       <c r="C5" s="33" t="s">
+        <v>332</v>
+      </c>
+      <c r="D5" s="33" t="s">
         <v>333</v>
       </c>
-      <c r="D5" s="33" t="s">
+      <c r="E5" s="33" t="s">
         <v>334</v>
       </c>
-      <c r="E5" s="33" t="s">
+      <c r="F5" s="33" t="s">
         <v>335</v>
-      </c>
-      <c r="F5" s="33" t="s">
-        <v>336</v>
       </c>
       <c r="G5" s="33" t="s">
         <v>303</v>
       </c>
       <c r="H5" s="33" t="s">
+        <v>336</v>
+      </c>
+      <c r="I5" s="33" t="s">
         <v>337</v>
       </c>
-      <c r="I5" s="33" t="s">
+      <c r="J5" s="33" t="s">
         <v>338</v>
       </c>
-      <c r="J5" s="33" t="s">
+      <c r="K5" s="33" t="s">
         <v>339</v>
-      </c>
-      <c r="K5" s="33" t="s">
-        <v>340</v>
       </c>
       <c r="L5" s="33">
         <v>1</v>
@@ -9703,31 +9703,31 @@
         <v>274</v>
       </c>
       <c r="C6" s="12" t="s">
+        <v>340</v>
+      </c>
+      <c r="D6" s="12" t="s">
         <v>341</v>
-      </c>
-      <c r="D6" s="12" t="s">
-        <v>342</v>
       </c>
       <c r="E6" s="83">
         <v>0.1</v>
       </c>
       <c r="F6" s="12" t="s">
-        <v>568</v>
+        <v>567</v>
       </c>
       <c r="G6" s="12" t="s">
-        <v>568</v>
+        <v>567</v>
       </c>
       <c r="H6" s="12">
         <v>20</v>
       </c>
       <c r="I6" s="12" t="s">
-        <v>568</v>
+        <v>567</v>
       </c>
       <c r="J6" s="85" t="s">
         <v>275</v>
       </c>
       <c r="K6" s="12" t="s">
-        <v>568</v>
+        <v>567</v>
       </c>
       <c r="L6" s="12" t="str" cm="1">
         <f t="array" ref="L6">IF(OR($B6="Anden armering",$B6=""),"",IF(_xlfn.IFS(
@@ -9849,31 +9849,31 @@
         <v>276</v>
       </c>
       <c r="C7" s="12" t="s">
-        <v>341</v>
+        <v>340</v>
       </c>
       <c r="D7" s="12" t="s">
-        <v>343</v>
+        <v>342</v>
       </c>
       <c r="E7" s="83">
         <v>0.1</v>
       </c>
       <c r="F7" s="12" t="s">
-        <v>568</v>
+        <v>567</v>
       </c>
       <c r="G7" s="12" t="s">
-        <v>568</v>
+        <v>567</v>
       </c>
       <c r="H7" s="12">
         <v>20</v>
       </c>
       <c r="I7" s="12" t="s">
-        <v>568</v>
+        <v>567</v>
       </c>
       <c r="J7" s="85" t="s">
         <v>275</v>
       </c>
       <c r="K7" s="12" t="s">
-        <v>568</v>
+        <v>567</v>
       </c>
       <c r="L7" s="12" t="str" cm="1">
         <f t="array" ref="L7">IF(OR($B7="Anden armering",$B7=""),"",IF(_xlfn.IFS(
@@ -9995,31 +9995,31 @@
         <v>277</v>
       </c>
       <c r="C8" s="12" t="s">
-        <v>341</v>
+        <v>340</v>
       </c>
       <c r="D8" s="12" t="s">
-        <v>344</v>
+        <v>343</v>
       </c>
       <c r="E8" s="83">
         <v>0.05</v>
       </c>
       <c r="F8" s="12" t="s">
-        <v>568</v>
+        <v>567</v>
       </c>
       <c r="G8" s="12" t="s">
-        <v>568</v>
+        <v>567</v>
       </c>
       <c r="H8" s="12">
         <v>20</v>
       </c>
       <c r="I8" s="12" t="s">
-        <v>568</v>
+        <v>567</v>
       </c>
       <c r="J8" s="85" t="s">
         <v>278</v>
       </c>
       <c r="K8" s="12" t="s">
-        <v>568</v>
+        <v>567</v>
       </c>
       <c r="L8" s="12" t="str" cm="1">
         <f t="array" ref="L8">IF(OR($B8="Anden armering",$B8=""),"",IF(_xlfn.IFS(
@@ -10141,16 +10141,16 @@
         <v>279</v>
       </c>
       <c r="C9" s="100" t="s">
-        <v>341</v>
+        <v>340</v>
       </c>
       <c r="D9" s="100" t="s">
-        <v>343</v>
+        <v>342</v>
       </c>
       <c r="E9" s="101">
         <v>0</v>
       </c>
       <c r="F9" s="100" t="s">
-        <v>345</v>
+        <v>344</v>
       </c>
       <c r="G9" s="100">
         <v>80</v>
@@ -10160,7 +10160,7 @@
       </c>
       <c r="I9" s="100"/>
       <c r="J9" s="102" t="s">
-        <v>346</v>
+        <v>345</v>
       </c>
       <c r="K9" s="13">
         <v>80</v>
@@ -10285,31 +10285,31 @@
         <v>281</v>
       </c>
       <c r="C10" s="12" t="s">
-        <v>341</v>
+        <v>340</v>
       </c>
       <c r="D10" s="12" t="s">
-        <v>344</v>
+        <v>343</v>
       </c>
       <c r="E10" s="83">
         <v>-0.05</v>
       </c>
       <c r="F10" s="12" t="s">
-        <v>568</v>
+        <v>567</v>
       </c>
       <c r="G10" s="12" t="s">
-        <v>568</v>
+        <v>567</v>
       </c>
       <c r="H10" s="12">
         <v>20</v>
       </c>
       <c r="I10" s="12" t="s">
-        <v>568</v>
+        <v>567</v>
       </c>
       <c r="J10" s="85" t="s">
         <v>282</v>
       </c>
       <c r="K10" s="12" t="s">
-        <v>568</v>
+        <v>567</v>
       </c>
       <c r="L10" s="12" t="str" cm="1">
         <f t="array" ref="L10">IF(OR($B10="Anden armering",$B10=""),"",IF(_xlfn.IFS(
@@ -10431,31 +10431,31 @@
         <v>142</v>
       </c>
       <c r="C11" s="12" t="s">
-        <v>341</v>
+        <v>340</v>
       </c>
       <c r="D11" s="12" t="s">
-        <v>344</v>
+        <v>343</v>
       </c>
       <c r="E11" s="83">
         <v>-0.1</v>
       </c>
       <c r="F11" s="12" t="s">
-        <v>568</v>
+        <v>567</v>
       </c>
       <c r="G11" s="12" t="s">
-        <v>568</v>
+        <v>567</v>
       </c>
       <c r="H11" s="12">
         <v>20</v>
       </c>
       <c r="I11" s="12" t="s">
-        <v>568</v>
+        <v>567</v>
       </c>
       <c r="J11" s="85" t="s">
         <v>283</v>
       </c>
       <c r="K11" s="12" t="s">
-        <v>568</v>
+        <v>567</v>
       </c>
       <c r="L11" s="12" t="str" cm="1">
         <f t="array" ref="L11">IF(OR($B11="Anden armering",$B11=""),"",IF(_xlfn.IFS(
@@ -10577,31 +10577,31 @@
         <v>284</v>
       </c>
       <c r="C12" s="12" t="s">
-        <v>341</v>
+        <v>340</v>
       </c>
       <c r="D12" s="12" t="s">
-        <v>344</v>
+        <v>343</v>
       </c>
       <c r="E12" s="83">
         <v>-0.15</v>
       </c>
       <c r="F12" s="12" t="s">
-        <v>568</v>
+        <v>567</v>
       </c>
       <c r="G12" s="12" t="s">
-        <v>568</v>
+        <v>567</v>
       </c>
       <c r="H12" s="12">
         <v>20</v>
       </c>
       <c r="I12" s="12" t="s">
-        <v>568</v>
+        <v>567</v>
       </c>
       <c r="J12" s="85" t="s">
         <v>285</v>
       </c>
       <c r="K12" s="12" t="s">
-        <v>568</v>
+        <v>567</v>
       </c>
       <c r="L12" s="12" t="str" cm="1">
         <f t="array" ref="L12">IF(OR($B12="Anden armering",$B12=""),"",IF(_xlfn.IFS(
@@ -10723,16 +10723,16 @@
         <v>286</v>
       </c>
       <c r="C13" s="12" t="s">
-        <v>347</v>
+        <v>346</v>
       </c>
       <c r="D13" s="12" t="s">
-        <v>342</v>
+        <v>341</v>
       </c>
       <c r="E13" s="83">
         <v>0.2</v>
       </c>
       <c r="F13" s="12" t="s">
-        <v>348</v>
+        <v>347</v>
       </c>
       <c r="G13" s="12">
         <v>64</v>
@@ -10867,29 +10867,29 @@
         <v>287</v>
       </c>
       <c r="C14" s="12" t="s">
-        <v>347</v>
+        <v>346</v>
       </c>
       <c r="D14" s="12" t="s">
-        <v>342</v>
+        <v>341</v>
       </c>
       <c r="E14" s="83">
         <v>0.2</v>
       </c>
       <c r="F14" s="12" t="s">
-        <v>568</v>
+        <v>567</v>
       </c>
       <c r="G14" s="12" t="s">
-        <v>568</v>
+        <v>567</v>
       </c>
       <c r="H14" s="12">
         <v>20</v>
       </c>
       <c r="I14" s="12" t="s">
-        <v>568</v>
+        <v>567</v>
       </c>
       <c r="J14" s="85"/>
       <c r="K14" s="12" t="s">
-        <v>568</v>
+        <v>567</v>
       </c>
       <c r="L14" s="12" t="str" cm="1">
         <f t="array" ref="L14">IF(OR($B14="Anden armering",$B14=""),"",IF(_xlfn.IFS(
@@ -11011,16 +11011,16 @@
         <v>288</v>
       </c>
       <c r="C15" s="12" t="s">
-        <v>347</v>
+        <v>346</v>
       </c>
       <c r="D15" s="12" t="s">
-        <v>342</v>
+        <v>341</v>
       </c>
       <c r="E15" s="83">
         <v>0.1</v>
       </c>
       <c r="F15" s="12" t="s">
-        <v>349</v>
+        <v>348</v>
       </c>
       <c r="G15" s="12">
         <v>64</v>
@@ -11155,16 +11155,16 @@
         <v>289</v>
       </c>
       <c r="C16" s="12" t="s">
-        <v>347</v>
+        <v>346</v>
       </c>
       <c r="D16" s="12" t="s">
-        <v>342</v>
+        <v>341</v>
       </c>
       <c r="E16" s="83">
         <v>0.1</v>
       </c>
       <c r="F16" s="12" t="s">
-        <v>350</v>
+        <v>349</v>
       </c>
       <c r="G16" s="12">
         <v>120</v>
@@ -11299,16 +11299,16 @@
         <v>290</v>
       </c>
       <c r="C17" s="12" t="s">
-        <v>347</v>
+        <v>346</v>
       </c>
       <c r="D17" s="12" t="s">
-        <v>342</v>
+        <v>341</v>
       </c>
       <c r="E17" s="83">
         <v>0.1</v>
       </c>
       <c r="F17" s="12" t="s">
-        <v>351</v>
+        <v>350</v>
       </c>
       <c r="G17" s="12">
         <v>200</v>
@@ -11443,16 +11443,16 @@
         <v>291</v>
       </c>
       <c r="C18" s="12" t="s">
-        <v>347</v>
+        <v>346</v>
       </c>
       <c r="D18" s="12" t="s">
-        <v>342</v>
+        <v>341</v>
       </c>
       <c r="E18" s="83">
         <v>0</v>
       </c>
       <c r="F18" s="12" t="s">
-        <v>352</v>
+        <v>351</v>
       </c>
       <c r="G18" s="12">
         <v>64</v>
@@ -11587,16 +11587,16 @@
         <v>292</v>
       </c>
       <c r="C19" s="12" t="s">
-        <v>347</v>
+        <v>346</v>
       </c>
       <c r="D19" s="12" t="s">
-        <v>342</v>
+        <v>341</v>
       </c>
       <c r="E19" s="83">
         <v>0</v>
       </c>
       <c r="F19" s="12" t="s">
-        <v>350</v>
+        <v>349</v>
       </c>
       <c r="G19" s="12">
         <v>120</v>
@@ -11731,16 +11731,16 @@
         <v>293</v>
       </c>
       <c r="C20" s="100" t="s">
-        <v>347</v>
+        <v>346</v>
       </c>
       <c r="D20" s="100" t="s">
-        <v>344</v>
+        <v>343</v>
       </c>
       <c r="E20" s="101">
         <v>0</v>
       </c>
       <c r="F20" s="100" t="s">
-        <v>353</v>
+        <v>352</v>
       </c>
       <c r="G20" s="100">
         <v>80</v>
@@ -11877,16 +11877,16 @@
         <v>295</v>
       </c>
       <c r="C21" s="12" t="s">
-        <v>347</v>
+        <v>346</v>
       </c>
       <c r="D21" s="12" t="s">
-        <v>344</v>
+        <v>343</v>
       </c>
       <c r="E21" s="83">
         <v>-0.1</v>
       </c>
       <c r="F21" s="12" t="s">
-        <v>353</v>
+        <v>352</v>
       </c>
       <c r="G21" s="12">
         <v>150</v>
@@ -11899,7 +11899,7 @@
       </c>
       <c r="J21" s="85"/>
       <c r="K21" s="12" t="s">
-        <v>568</v>
+        <v>567</v>
       </c>
       <c r="L21" s="12" t="str" cm="1">
         <f t="array" ref="L21">IF(OR($B21="Anden armering",$B21=""),"",IF(_xlfn.IFS(
@@ -12021,16 +12021,16 @@
         <v>296</v>
       </c>
       <c r="C22" s="12" t="s">
-        <v>354</v>
+        <v>353</v>
       </c>
       <c r="D22" s="12" t="s">
-        <v>344</v>
+        <v>343</v>
       </c>
       <c r="E22" s="83">
         <v>0</v>
       </c>
       <c r="F22" s="12" t="s">
-        <v>353</v>
+        <v>352</v>
       </c>
       <c r="G22" s="12">
         <v>80</v>
@@ -12167,16 +12167,16 @@
         <v>298</v>
       </c>
       <c r="C23" s="12" t="s">
-        <v>354</v>
+        <v>353</v>
       </c>
       <c r="D23" s="12" t="s">
-        <v>344</v>
+        <v>343</v>
       </c>
       <c r="E23" s="83">
         <v>-0.1</v>
       </c>
       <c r="F23" s="12" t="s">
-        <v>353</v>
+        <v>352</v>
       </c>
       <c r="G23" s="12">
         <v>80</v>
@@ -12191,7 +12191,7 @@
         <v>299</v>
       </c>
       <c r="K23" s="12" t="s">
-        <v>568</v>
+        <v>567</v>
       </c>
       <c r="L23" s="12" t="str" cm="1">
         <f t="array" ref="L23">IF(OR($B23="Anden armering",$B23=""),"",IF(_xlfn.IFS(
@@ -12313,16 +12313,16 @@
         <v>300</v>
       </c>
       <c r="C24" s="12" t="s">
-        <v>354</v>
+        <v>353</v>
       </c>
       <c r="D24" s="12" t="s">
-        <v>344</v>
+        <v>343</v>
       </c>
       <c r="E24" s="83">
         <v>-0.1</v>
       </c>
       <c r="F24" s="12" t="s">
-        <v>355</v>
+        <v>354</v>
       </c>
       <c r="G24" s="12">
         <v>150</v>
@@ -12454,10 +12454,10 @@
     </row>
     <row r="25" spans="2:17" ht="21.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B25" s="92" t="s">
+        <v>355</v>
+      </c>
+      <c r="C25" s="12" t="s">
         <v>356</v>
-      </c>
-      <c r="C25" s="12" t="s">
-        <v>357</v>
       </c>
       <c r="D25" s="12"/>
       <c r="E25" s="83">
@@ -12468,7 +12468,7 @@
       <c r="H25" s="12"/>
       <c r="I25" s="12"/>
       <c r="J25" s="85" t="s">
-        <v>358</v>
+        <v>357</v>
       </c>
       <c r="K25" s="12"/>
       <c r="L25" s="128" t="str" cm="1">
@@ -12587,17 +12587,17 @@
       </c>
     </row>
     <row r="27" spans="2:17" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B27" s="137" t="s">
-        <v>359</v>
-      </c>
-      <c r="C27" s="137"/>
-      <c r="D27" s="137"/>
-      <c r="E27" s="137"/>
-      <c r="F27" s="137"/>
-      <c r="G27" s="137"/>
-      <c r="H27" s="137"/>
-      <c r="I27" s="137"/>
-      <c r="J27" s="137"/>
+      <c r="B27" s="138" t="s">
+        <v>358</v>
+      </c>
+      <c r="C27" s="138"/>
+      <c r="D27" s="138"/>
+      <c r="E27" s="138"/>
+      <c r="F27" s="138"/>
+      <c r="G27" s="138"/>
+      <c r="H27" s="138"/>
+      <c r="I27" s="138"/>
+      <c r="J27" s="138"/>
     </row>
   </sheetData>
   <mergeCells count="4">
@@ -12654,187 +12654,187 @@
   </cols>
   <sheetData>
     <row r="1" spans="2:71" ht="24" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B1" s="135" t="s">
+      <c r="B1" s="144" t="s">
+        <v>359</v>
+      </c>
+      <c r="C1" s="144"/>
+      <c r="D1" s="144"/>
+      <c r="E1" s="144"/>
+      <c r="F1" s="144"/>
+      <c r="G1" s="144"/>
+      <c r="H1" s="144"/>
+      <c r="I1" s="144"/>
+      <c r="J1" s="144"/>
+      <c r="K1" s="144"/>
+      <c r="L1" s="144"/>
+      <c r="M1" s="144"/>
+      <c r="N1" s="144"/>
+      <c r="O1" s="144"/>
+      <c r="P1" s="144"/>
+      <c r="Q1" s="144"/>
+      <c r="R1" s="144"/>
+      <c r="S1" s="144"/>
+      <c r="T1" s="144"/>
+      <c r="AA1" s="145" t="s">
         <v>360</v>
       </c>
-      <c r="C1" s="135"/>
-      <c r="D1" s="135"/>
-      <c r="E1" s="135"/>
-      <c r="F1" s="135"/>
-      <c r="G1" s="135"/>
-      <c r="H1" s="135"/>
-      <c r="I1" s="135"/>
-      <c r="J1" s="135"/>
-      <c r="K1" s="135"/>
-      <c r="L1" s="135"/>
-      <c r="M1" s="135"/>
-      <c r="N1" s="135"/>
-      <c r="O1" s="135"/>
-      <c r="P1" s="135"/>
-      <c r="Q1" s="135"/>
-      <c r="R1" s="135"/>
-      <c r="S1" s="135"/>
-      <c r="T1" s="135"/>
-      <c r="AA1" s="136" t="s">
+      <c r="AB1" s="145"/>
+      <c r="AC1" s="145"/>
+      <c r="AD1" s="145"/>
+      <c r="AE1" s="145"/>
+      <c r="AF1" s="145"/>
+      <c r="AG1" s="145"/>
+      <c r="AH1" s="145"/>
+      <c r="AI1" s="145"/>
+      <c r="AJ1" s="145"/>
+      <c r="AK1" s="145"/>
+      <c r="AL1" s="145"/>
+      <c r="AM1" s="145"/>
+      <c r="AN1" s="145"/>
+      <c r="AO1" s="145"/>
+      <c r="AP1" s="145"/>
+      <c r="AQ1" s="145"/>
+      <c r="AR1" s="145"/>
+      <c r="AS1" s="145"/>
+      <c r="AT1" s="145"/>
+      <c r="AU1" s="145"/>
+      <c r="AV1" s="145"/>
+      <c r="AW1" s="145"/>
+      <c r="AX1" s="145"/>
+      <c r="AY1" s="145"/>
+      <c r="AZ1" s="145"/>
+      <c r="BA1" s="145"/>
+    </row>
+    <row r="2" spans="2:71" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B2" s="138" t="s">
         <v>361</v>
       </c>
-      <c r="AB1" s="136"/>
-      <c r="AC1" s="136"/>
-      <c r="AD1" s="136"/>
-      <c r="AE1" s="136"/>
-      <c r="AF1" s="136"/>
-      <c r="AG1" s="136"/>
-      <c r="AH1" s="136"/>
-      <c r="AI1" s="136"/>
-      <c r="AJ1" s="136"/>
-      <c r="AK1" s="136"/>
-      <c r="AL1" s="136"/>
-      <c r="AM1" s="136"/>
-      <c r="AN1" s="136"/>
-      <c r="AO1" s="136"/>
-      <c r="AP1" s="136"/>
-      <c r="AQ1" s="136"/>
-      <c r="AR1" s="136"/>
-      <c r="AS1" s="136"/>
-      <c r="AT1" s="136"/>
-      <c r="AU1" s="136"/>
-      <c r="AV1" s="136"/>
-      <c r="AW1" s="136"/>
-      <c r="AX1" s="136"/>
-      <c r="AY1" s="136"/>
-      <c r="AZ1" s="136"/>
-      <c r="BA1" s="136"/>
-    </row>
-    <row r="2" spans="2:71" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B2" s="137" t="s">
-        <v>362</v>
-      </c>
-      <c r="C2" s="137"/>
-      <c r="D2" s="137"/>
-      <c r="E2" s="137"/>
-      <c r="F2" s="137"/>
-      <c r="G2" s="137"/>
-      <c r="H2" s="137"/>
-      <c r="I2" s="137"/>
-      <c r="J2" s="137"/>
-      <c r="K2" s="137"/>
-      <c r="L2" s="137"/>
-      <c r="M2" s="137"/>
-      <c r="N2" s="137"/>
-      <c r="O2" s="137"/>
-      <c r="P2" s="137"/>
-      <c r="Q2" s="137"/>
-      <c r="R2" s="137"/>
-      <c r="S2" s="137"/>
-      <c r="T2" s="137"/>
+      <c r="C2" s="138"/>
+      <c r="D2" s="138"/>
+      <c r="E2" s="138"/>
+      <c r="F2" s="138"/>
+      <c r="G2" s="138"/>
+      <c r="H2" s="138"/>
+      <c r="I2" s="138"/>
+      <c r="J2" s="138"/>
+      <c r="K2" s="138"/>
+      <c r="L2" s="138"/>
+      <c r="M2" s="138"/>
+      <c r="N2" s="138"/>
+      <c r="O2" s="138"/>
+      <c r="P2" s="138"/>
+      <c r="Q2" s="138"/>
+      <c r="R2" s="138"/>
+      <c r="S2" s="138"/>
+      <c r="T2" s="138"/>
       <c r="U2" s="104"/>
       <c r="V2" s="104"/>
       <c r="W2" s="104"/>
       <c r="X2" s="104"/>
       <c r="Y2" s="104"/>
-      <c r="AA2" s="138" t="s">
-        <v>363</v>
-      </c>
-      <c r="AB2" s="138"/>
-      <c r="AC2" s="138"/>
-      <c r="AD2" s="138"/>
-      <c r="AE2" s="138"/>
-      <c r="AF2" s="138"/>
-      <c r="AG2" s="138"/>
-      <c r="AH2" s="138"/>
-      <c r="AI2" s="138"/>
-      <c r="AJ2" s="138"/>
-      <c r="AK2" s="138"/>
-      <c r="AL2" s="138"/>
-      <c r="AM2" s="138"/>
-      <c r="AN2" s="138"/>
-      <c r="AO2" s="138"/>
-      <c r="AP2" s="138"/>
-      <c r="AQ2" s="138"/>
-      <c r="AR2" s="138"/>
-      <c r="AS2" s="138"/>
-      <c r="AT2" s="138"/>
-      <c r="AU2" s="138"/>
-      <c r="AV2" s="138"/>
-      <c r="AW2" s="138"/>
-      <c r="AX2" s="138"/>
-      <c r="AY2" s="138"/>
-      <c r="AZ2" s="138"/>
-      <c r="BA2" s="138"/>
+      <c r="AA2" s="146" t="s">
+        <v>362</v>
+      </c>
+      <c r="AB2" s="146"/>
+      <c r="AC2" s="146"/>
+      <c r="AD2" s="146"/>
+      <c r="AE2" s="146"/>
+      <c r="AF2" s="146"/>
+      <c r="AG2" s="146"/>
+      <c r="AH2" s="146"/>
+      <c r="AI2" s="146"/>
+      <c r="AJ2" s="146"/>
+      <c r="AK2" s="146"/>
+      <c r="AL2" s="146"/>
+      <c r="AM2" s="146"/>
+      <c r="AN2" s="146"/>
+      <c r="AO2" s="146"/>
+      <c r="AP2" s="146"/>
+      <c r="AQ2" s="146"/>
+      <c r="AR2" s="146"/>
+      <c r="AS2" s="146"/>
+      <c r="AT2" s="146"/>
+      <c r="AU2" s="146"/>
+      <c r="AV2" s="146"/>
+      <c r="AW2" s="146"/>
+      <c r="AX2" s="146"/>
+      <c r="AY2" s="146"/>
+      <c r="AZ2" s="146"/>
+      <c r="BA2" s="146"/>
     </row>
     <row r="3" spans="2:71" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B3" s="137"/>
-      <c r="C3" s="137"/>
-      <c r="D3" s="137"/>
-      <c r="E3" s="137"/>
-      <c r="F3" s="137"/>
-      <c r="G3" s="137"/>
-      <c r="H3" s="137"/>
-      <c r="I3" s="137"/>
-      <c r="J3" s="137"/>
-      <c r="K3" s="137"/>
-      <c r="L3" s="137"/>
-      <c r="M3" s="137"/>
-      <c r="N3" s="137"/>
-      <c r="O3" s="137"/>
-      <c r="P3" s="137"/>
-      <c r="Q3" s="137"/>
-      <c r="R3" s="137"/>
-      <c r="S3" s="137"/>
-      <c r="T3" s="137"/>
+      <c r="B3" s="138"/>
+      <c r="C3" s="138"/>
+      <c r="D3" s="138"/>
+      <c r="E3" s="138"/>
+      <c r="F3" s="138"/>
+      <c r="G3" s="138"/>
+      <c r="H3" s="138"/>
+      <c r="I3" s="138"/>
+      <c r="J3" s="138"/>
+      <c r="K3" s="138"/>
+      <c r="L3" s="138"/>
+      <c r="M3" s="138"/>
+      <c r="N3" s="138"/>
+      <c r="O3" s="138"/>
+      <c r="P3" s="138"/>
+      <c r="Q3" s="138"/>
+      <c r="R3" s="138"/>
+      <c r="S3" s="138"/>
+      <c r="T3" s="138"/>
       <c r="U3" s="104"/>
       <c r="V3" s="104"/>
       <c r="W3" s="104"/>
       <c r="X3" s="104"/>
       <c r="Y3" s="104"/>
-      <c r="AA3" s="138"/>
-      <c r="AB3" s="138"/>
-      <c r="AC3" s="138"/>
-      <c r="AD3" s="138"/>
-      <c r="AE3" s="138"/>
-      <c r="AF3" s="138"/>
-      <c r="AG3" s="138"/>
-      <c r="AH3" s="138"/>
-      <c r="AI3" s="138"/>
-      <c r="AJ3" s="138"/>
-      <c r="AK3" s="138"/>
-      <c r="AL3" s="138"/>
-      <c r="AM3" s="138"/>
-      <c r="AN3" s="138"/>
-      <c r="AO3" s="138"/>
-      <c r="AP3" s="138"/>
-      <c r="AQ3" s="138"/>
-      <c r="AR3" s="138"/>
-      <c r="AS3" s="138"/>
-      <c r="AT3" s="138"/>
-      <c r="AU3" s="138"/>
-      <c r="AV3" s="138"/>
-      <c r="AW3" s="138"/>
-      <c r="AX3" s="138"/>
-      <c r="AY3" s="138"/>
-      <c r="AZ3" s="138"/>
-      <c r="BA3" s="138"/>
+      <c r="AA3" s="146"/>
+      <c r="AB3" s="146"/>
+      <c r="AC3" s="146"/>
+      <c r="AD3" s="146"/>
+      <c r="AE3" s="146"/>
+      <c r="AF3" s="146"/>
+      <c r="AG3" s="146"/>
+      <c r="AH3" s="146"/>
+      <c r="AI3" s="146"/>
+      <c r="AJ3" s="146"/>
+      <c r="AK3" s="146"/>
+      <c r="AL3" s="146"/>
+      <c r="AM3" s="146"/>
+      <c r="AN3" s="146"/>
+      <c r="AO3" s="146"/>
+      <c r="AP3" s="146"/>
+      <c r="AQ3" s="146"/>
+      <c r="AR3" s="146"/>
+      <c r="AS3" s="146"/>
+      <c r="AT3" s="146"/>
+      <c r="AU3" s="146"/>
+      <c r="AV3" s="146"/>
+      <c r="AW3" s="146"/>
+      <c r="AX3" s="146"/>
+      <c r="AY3" s="146"/>
+      <c r="AZ3" s="146"/>
+      <c r="BA3" s="146"/>
     </row>
     <row r="4" spans="2:71" ht="27.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B4" s="137"/>
-      <c r="C4" s="137"/>
-      <c r="D4" s="137"/>
-      <c r="E4" s="137"/>
-      <c r="F4" s="137"/>
-      <c r="G4" s="137"/>
-      <c r="H4" s="137"/>
-      <c r="I4" s="137"/>
-      <c r="J4" s="137"/>
-      <c r="K4" s="137"/>
-      <c r="L4" s="137"/>
-      <c r="M4" s="137"/>
-      <c r="N4" s="137"/>
-      <c r="O4" s="137"/>
-      <c r="P4" s="137"/>
-      <c r="Q4" s="137"/>
-      <c r="R4" s="137"/>
-      <c r="S4" s="137"/>
-      <c r="T4" s="137"/>
+      <c r="B4" s="138"/>
+      <c r="C4" s="138"/>
+      <c r="D4" s="138"/>
+      <c r="E4" s="138"/>
+      <c r="F4" s="138"/>
+      <c r="G4" s="138"/>
+      <c r="H4" s="138"/>
+      <c r="I4" s="138"/>
+      <c r="J4" s="138"/>
+      <c r="K4" s="138"/>
+      <c r="L4" s="138"/>
+      <c r="M4" s="138"/>
+      <c r="N4" s="138"/>
+      <c r="O4" s="138"/>
+      <c r="P4" s="138"/>
+      <c r="Q4" s="138"/>
+      <c r="R4" s="138"/>
+      <c r="S4" s="138"/>
+      <c r="T4" s="138"/>
       <c r="AA4" s="4"/>
       <c r="AB4" s="4"/>
       <c r="AC4" s="4"/>
@@ -12844,7 +12844,7 @@
       <c r="AG4" s="4"/>
       <c r="AH4" s="4"/>
       <c r="AI4" s="103" t="s">
-        <v>364</v>
+        <v>363</v>
       </c>
       <c r="AJ4" s="103"/>
       <c r="AK4" s="103"/>
@@ -12866,110 +12866,110 @@
       <c r="BA4" s="103"/>
     </row>
     <row r="5" spans="2:71" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B5" s="139" t="s">
+      <c r="B5" s="137" t="s">
+        <v>364</v>
+      </c>
+      <c r="C5" s="137"/>
+      <c r="D5" s="137"/>
+      <c r="E5" s="137"/>
+      <c r="F5" s="137"/>
+      <c r="G5" s="137"/>
+      <c r="H5" s="137"/>
+      <c r="I5" s="137"/>
+      <c r="J5" s="137"/>
+      <c r="K5" s="137"/>
+      <c r="L5" s="137"/>
+      <c r="M5" s="137"/>
+      <c r="N5" s="137"/>
+      <c r="O5" s="137"/>
+      <c r="P5" s="137"/>
+      <c r="Q5" s="137"/>
+      <c r="R5" s="137"/>
+      <c r="S5" s="137"/>
+      <c r="T5" s="137"/>
+      <c r="V5" s="147"/>
+      <c r="W5" s="147"/>
+      <c r="X5" s="147"/>
+      <c r="Y5" s="147"/>
+      <c r="AA5" s="105" t="s">
         <v>365</v>
       </c>
-      <c r="C5" s="139"/>
-      <c r="D5" s="139"/>
-      <c r="E5" s="139"/>
-      <c r="F5" s="139"/>
-      <c r="G5" s="139"/>
-      <c r="H5" s="139"/>
-      <c r="I5" s="139"/>
-      <c r="J5" s="139"/>
-      <c r="K5" s="139"/>
-      <c r="L5" s="139"/>
-      <c r="M5" s="139"/>
-      <c r="N5" s="139"/>
-      <c r="O5" s="139"/>
-      <c r="P5" s="139"/>
-      <c r="Q5" s="139"/>
-      <c r="R5" s="139"/>
-      <c r="S5" s="139"/>
-      <c r="T5" s="139"/>
-      <c r="V5" s="140"/>
-      <c r="W5" s="140"/>
-      <c r="X5" s="140"/>
-      <c r="Y5" s="140"/>
-      <c r="AA5" s="105" t="s">
+      <c r="AB5" s="105" t="s">
         <v>366</v>
-      </c>
-      <c r="AB5" s="105" t="s">
-        <v>367</v>
       </c>
       <c r="AC5" s="105" t="s">
         <v>120</v>
       </c>
       <c r="AD5" s="105" t="s">
+        <v>367</v>
+      </c>
+      <c r="AE5" s="105" t="s">
         <v>368</v>
       </c>
-      <c r="AE5" s="105" t="s">
+      <c r="AF5" s="105" t="s">
         <v>369</v>
-      </c>
-      <c r="AF5" s="105" t="s">
-        <v>370</v>
       </c>
       <c r="AG5" s="4"/>
       <c r="AH5" s="4"/>
       <c r="AI5" s="105" t="s">
+        <v>370</v>
+      </c>
+      <c r="AJ5" s="105" t="s">
         <v>371</v>
       </c>
-      <c r="AJ5" s="105" t="s">
+      <c r="AK5" s="105" t="s">
         <v>372</v>
       </c>
-      <c r="AK5" s="105" t="s">
+      <c r="AL5" s="105" t="s">
         <v>373</v>
       </c>
-      <c r="AL5" s="105" t="s">
+      <c r="AM5" s="105" t="s">
         <v>374</v>
       </c>
-      <c r="AM5" s="105" t="s">
+      <c r="AN5" s="105" t="s">
         <v>375</v>
       </c>
-      <c r="AN5" s="105" t="s">
+      <c r="AO5" s="105" t="s">
         <v>376</v>
       </c>
-      <c r="AO5" s="105" t="s">
+      <c r="AP5" s="105" t="s">
         <v>377</v>
       </c>
-      <c r="AP5" s="105" t="s">
+      <c r="AQ5" s="105" t="s">
         <v>378</v>
       </c>
-      <c r="AQ5" s="105" t="s">
+      <c r="AR5" s="105" t="s">
         <v>379</v>
       </c>
-      <c r="AR5" s="105" t="s">
+      <c r="AS5" s="105" t="s">
         <v>380</v>
       </c>
-      <c r="AS5" s="105" t="s">
+      <c r="AT5" s="105" t="s">
         <v>381</v>
       </c>
-      <c r="AT5" s="105" t="s">
+      <c r="AU5" s="105" t="s">
         <v>382</v>
       </c>
-      <c r="AU5" s="105" t="s">
+      <c r="AV5" s="105" t="s">
         <v>383</v>
       </c>
-      <c r="AV5" s="105" t="s">
+      <c r="AW5" s="105" t="s">
         <v>384</v>
       </c>
-      <c r="AW5" s="105" t="s">
+      <c r="AX5" s="105" t="s">
         <v>385</v>
       </c>
-      <c r="AX5" s="105" t="s">
+      <c r="AY5" s="105" t="s">
         <v>386</v>
       </c>
-      <c r="AY5" s="105" t="s">
+      <c r="AZ5" s="105" t="s">
         <v>387</v>
       </c>
-      <c r="AZ5" s="105" t="s">
+      <c r="BA5" s="105" t="s">
         <v>388</v>
       </c>
-      <c r="BA5" s="105" t="s">
-        <v>389</v>
-      </c>
       <c r="BB5" s="132" t="s">
-        <v>569</v>
+        <v>568</v>
       </c>
       <c r="BC5"/>
       <c r="BD5"/>
@@ -12990,49 +12990,49 @@
       <c r="BS5"/>
     </row>
     <row r="6" spans="2:71" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B6" s="141" t="s">
-        <v>390</v>
-      </c>
-      <c r="C6" s="141"/>
-      <c r="D6" s="141"/>
-      <c r="E6" s="141"/>
-      <c r="F6" s="141"/>
-      <c r="G6" s="141"/>
-      <c r="H6" s="141"/>
-      <c r="I6" s="141"/>
-      <c r="J6" s="141"/>
-      <c r="K6" s="141"/>
-      <c r="L6" s="141"/>
-      <c r="M6" s="141"/>
-      <c r="N6" s="141"/>
-      <c r="O6" s="141"/>
-      <c r="P6" s="141"/>
-      <c r="Q6" s="141"/>
-      <c r="R6" s="141"/>
-      <c r="S6" s="141"/>
-      <c r="T6" s="141"/>
+      <c r="B6" s="142" t="s">
+        <v>389</v>
+      </c>
+      <c r="C6" s="142"/>
+      <c r="D6" s="142"/>
+      <c r="E6" s="142"/>
+      <c r="F6" s="142"/>
+      <c r="G6" s="142"/>
+      <c r="H6" s="142"/>
+      <c r="I6" s="142"/>
+      <c r="J6" s="142"/>
+      <c r="K6" s="142"/>
+      <c r="L6" s="142"/>
+      <c r="M6" s="142"/>
+      <c r="N6" s="142"/>
+      <c r="O6" s="142"/>
+      <c r="P6" s="142"/>
+      <c r="Q6" s="142"/>
+      <c r="R6" s="142"/>
+      <c r="S6" s="142"/>
+      <c r="T6" s="142"/>
       <c r="U6" s="104"/>
       <c r="V6"/>
       <c r="W6"/>
       <c r="X6"/>
       <c r="Y6"/>
       <c r="AA6" s="106" t="s">
-        <v>372</v>
+        <v>371</v>
       </c>
       <c r="AB6" s="106">
         <v>30</v>
       </c>
       <c r="AC6" s="106" t="s">
+        <v>390</v>
+      </c>
+      <c r="AD6" s="106" t="s">
         <v>391</v>
       </c>
-      <c r="AD6" s="106" t="s">
+      <c r="AE6" s="106" t="s">
         <v>392</v>
       </c>
-      <c r="AE6" s="106" t="s">
+      <c r="AF6" s="106" t="s">
         <v>393</v>
-      </c>
-      <c r="AF6" s="106" t="s">
-        <v>394</v>
       </c>
       <c r="AG6" s="4"/>
       <c r="AH6" s="4"/>
@@ -13113,7 +13113,7 @@
         <v>110</v>
       </c>
       <c r="BB6" t="s">
-        <v>570</v>
+        <v>569</v>
       </c>
       <c r="BC6"/>
       <c r="BD6"/>
@@ -13134,31 +13134,31 @@
       <c r="BS6"/>
     </row>
     <row r="7" spans="2:71" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B7" s="141"/>
-      <c r="C7" s="141"/>
-      <c r="D7" s="141"/>
-      <c r="E7" s="141"/>
-      <c r="F7" s="141"/>
-      <c r="G7" s="141"/>
-      <c r="H7" s="141"/>
-      <c r="I7" s="141"/>
-      <c r="J7" s="141"/>
-      <c r="K7" s="141"/>
-      <c r="L7" s="141"/>
-      <c r="M7" s="141"/>
-      <c r="N7" s="141"/>
-      <c r="O7" s="141"/>
-      <c r="P7" s="141"/>
-      <c r="Q7" s="141"/>
-      <c r="R7" s="141"/>
-      <c r="S7" s="141"/>
-      <c r="T7" s="141"/>
+      <c r="B7" s="142"/>
+      <c r="C7" s="142"/>
+      <c r="D7" s="142"/>
+      <c r="E7" s="142"/>
+      <c r="F7" s="142"/>
+      <c r="G7" s="142"/>
+      <c r="H7" s="142"/>
+      <c r="I7" s="142"/>
+      <c r="J7" s="142"/>
+      <c r="K7" s="142"/>
+      <c r="L7" s="142"/>
+      <c r="M7" s="142"/>
+      <c r="N7" s="142"/>
+      <c r="O7" s="142"/>
+      <c r="P7" s="142"/>
+      <c r="Q7" s="142"/>
+      <c r="R7" s="142"/>
+      <c r="S7" s="142"/>
+      <c r="T7" s="142"/>
       <c r="V7"/>
       <c r="W7"/>
       <c r="X7"/>
       <c r="Y7"/>
       <c r="AA7" s="106" t="s">
-        <v>373</v>
+        <v>372</v>
       </c>
       <c r="AB7" s="106">
         <v>30</v>
@@ -13167,13 +13167,13 @@
         <v>152</v>
       </c>
       <c r="AD7" s="106" t="s">
-        <v>392</v>
+        <v>391</v>
       </c>
       <c r="AE7" s="106" t="s">
-        <v>395</v>
+        <v>394</v>
       </c>
       <c r="AF7" s="106" t="s">
-        <v>394</v>
+        <v>393</v>
       </c>
       <c r="AG7" s="4"/>
       <c r="AH7" s="4"/>
@@ -13273,61 +13273,61 @@
       <c r="BS7"/>
     </row>
     <row r="8" spans="2:71" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B8" s="142" t="s">
-        <v>371</v>
+      <c r="B8" s="139" t="s">
+        <v>370</v>
       </c>
       <c r="C8" s="143" t="s">
-        <v>396</v>
+        <v>395</v>
       </c>
       <c r="D8" s="143"/>
       <c r="E8" s="143"/>
       <c r="F8" s="143" t="s">
-        <v>397</v>
+        <v>396</v>
       </c>
       <c r="G8" s="143"/>
       <c r="H8" s="143"/>
       <c r="I8" s="143" t="s">
-        <v>398</v>
+        <v>397</v>
       </c>
       <c r="J8" s="143"/>
       <c r="K8" s="143"/>
       <c r="L8" s="143" t="s">
-        <v>399</v>
+        <v>398</v>
       </c>
       <c r="M8" s="143"/>
       <c r="N8" s="143"/>
       <c r="O8" s="143" t="s">
-        <v>400</v>
+        <v>399</v>
       </c>
       <c r="P8" s="143"/>
       <c r="Q8" s="143"/>
       <c r="R8" s="143" t="s">
-        <v>401</v>
+        <v>400</v>
       </c>
       <c r="S8" s="143"/>
       <c r="T8" s="143"/>
       <c r="V8" s="130" t="s">
-        <v>574</v>
+        <v>573</v>
       </c>
       <c r="X8"/>
       <c r="Y8"/>
       <c r="AA8" s="106" t="s">
-        <v>374</v>
+        <v>373</v>
       </c>
       <c r="AB8" s="106">
         <v>30</v>
       </c>
       <c r="AC8" s="106" t="s">
+        <v>401</v>
+      </c>
+      <c r="AD8" s="106" t="s">
+        <v>391</v>
+      </c>
+      <c r="AE8" s="106" t="s">
         <v>402</v>
       </c>
-      <c r="AD8" s="106" t="s">
-        <v>392</v>
-      </c>
-      <c r="AE8" s="106" t="s">
-        <v>403</v>
-      </c>
       <c r="AF8" s="106" t="s">
-        <v>394</v>
+        <v>393</v>
       </c>
       <c r="AG8" s="4"/>
       <c r="AH8" s="4"/>
@@ -13427,81 +13427,81 @@
       <c r="BS8"/>
     </row>
     <row r="9" spans="2:71" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B9" s="142"/>
+      <c r="B9" s="139"/>
       <c r="C9" s="108" t="s">
-        <v>391</v>
+        <v>390</v>
       </c>
       <c r="D9" s="108" t="s">
         <v>152</v>
       </c>
       <c r="E9" s="108" t="s">
-        <v>402</v>
+        <v>401</v>
       </c>
       <c r="F9" s="108" t="s">
-        <v>391</v>
+        <v>390</v>
       </c>
       <c r="G9" s="108" t="s">
         <v>152</v>
       </c>
       <c r="H9" s="108" t="s">
-        <v>402</v>
+        <v>401</v>
       </c>
       <c r="I9" s="108" t="s">
-        <v>391</v>
+        <v>390</v>
       </c>
       <c r="J9" s="108" t="s">
         <v>152</v>
       </c>
       <c r="K9" s="108" t="s">
-        <v>402</v>
+        <v>401</v>
       </c>
       <c r="L9" s="108" t="s">
-        <v>391</v>
+        <v>390</v>
       </c>
       <c r="M9" s="108" t="s">
         <v>152</v>
       </c>
       <c r="N9" s="108" t="s">
-        <v>402</v>
+        <v>401</v>
       </c>
       <c r="O9" s="108" t="s">
-        <v>391</v>
+        <v>390</v>
       </c>
       <c r="P9" s="108" t="s">
         <v>152</v>
       </c>
       <c r="Q9" s="108" t="s">
-        <v>402</v>
+        <v>401</v>
       </c>
       <c r="R9" s="108" t="s">
-        <v>391</v>
+        <v>390</v>
       </c>
       <c r="S9" s="108" t="s">
         <v>152</v>
       </c>
       <c r="T9" s="108" t="s">
-        <v>402</v>
+        <v>401</v>
       </c>
       <c r="V9" s="131" t="s">
-        <v>575</v>
+        <v>574</v>
       </c>
       <c r="AA9" s="106" t="s">
-        <v>375</v>
+        <v>374</v>
       </c>
       <c r="AB9" s="106">
         <v>45</v>
       </c>
       <c r="AC9" s="106" t="s">
-        <v>391</v>
+        <v>390</v>
       </c>
       <c r="AD9" s="106" t="s">
+        <v>403</v>
+      </c>
+      <c r="AE9" s="106" t="s">
         <v>404</v>
       </c>
-      <c r="AE9" s="106" t="s">
+      <c r="AF9" s="106" t="s">
         <v>405</v>
-      </c>
-      <c r="AF9" s="106" t="s">
-        <v>406</v>
       </c>
       <c r="AG9" s="4"/>
       <c r="AH9" s="4"/>
@@ -13582,58 +13582,58 @@
         <v>87.5</v>
       </c>
       <c r="BB9" t="s">
+        <v>371</v>
+      </c>
+      <c r="BC9" t="s">
         <v>372</v>
       </c>
-      <c r="BC9" t="s">
+      <c r="BD9" t="s">
         <v>373</v>
       </c>
-      <c r="BD9" t="s">
+      <c r="BE9" t="s">
         <v>374</v>
       </c>
-      <c r="BE9" t="s">
+      <c r="BF9" t="s">
         <v>375</v>
       </c>
-      <c r="BF9" t="s">
+      <c r="BG9" t="s">
         <v>376</v>
       </c>
-      <c r="BG9" t="s">
+      <c r="BH9" t="s">
         <v>377</v>
       </c>
-      <c r="BH9" t="s">
+      <c r="BI9" t="s">
         <v>378</v>
       </c>
-      <c r="BI9" t="s">
+      <c r="BJ9" t="s">
         <v>379</v>
       </c>
-      <c r="BJ9" t="s">
+      <c r="BK9" t="s">
         <v>380</v>
       </c>
-      <c r="BK9" t="s">
+      <c r="BL9" t="s">
         <v>381</v>
       </c>
-      <c r="BL9" t="s">
+      <c r="BM9" t="s">
         <v>382</v>
       </c>
-      <c r="BM9" t="s">
+      <c r="BN9" t="s">
         <v>383</v>
       </c>
-      <c r="BN9" t="s">
+      <c r="BO9" t="s">
         <v>384</v>
       </c>
-      <c r="BO9" t="s">
+      <c r="BP9" t="s">
         <v>385</v>
       </c>
-      <c r="BP9" t="s">
+      <c r="BQ9" t="s">
         <v>386</v>
       </c>
-      <c r="BQ9" t="s">
+      <c r="BR9" t="s">
         <v>387</v>
       </c>
-      <c r="BR9" t="s">
+      <c r="BS9" t="s">
         <v>388</v>
-      </c>
-      <c r="BS9" t="s">
-        <v>389</v>
       </c>
     </row>
     <row r="10" spans="2:71" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
@@ -13713,10 +13713,10 @@
         <v>110</v>
       </c>
       <c r="V10" s="129" t="s">
-        <v>576</v>
+        <v>575</v>
       </c>
       <c r="AA10" s="106" t="s">
-        <v>376</v>
+        <v>375</v>
       </c>
       <c r="AB10" s="106">
         <v>45</v>
@@ -13725,13 +13725,13 @@
         <v>152</v>
       </c>
       <c r="AD10" s="106" t="s">
-        <v>404</v>
+        <v>403</v>
       </c>
       <c r="AE10" s="106" t="s">
-        <v>407</v>
+        <v>406</v>
       </c>
       <c r="AF10" s="106" t="s">
-        <v>406</v>
+        <v>405</v>
       </c>
       <c r="AG10" s="4"/>
       <c r="AH10" s="4"/>
@@ -13812,58 +13812,58 @@
         <v>82.5</v>
       </c>
       <c r="BB10" t="s">
+        <v>570</v>
+      </c>
+      <c r="BC10" t="s">
         <v>571</v>
       </c>
-      <c r="BC10" t="s">
+      <c r="BD10" t="s">
+        <v>570</v>
+      </c>
+      <c r="BE10" t="s">
+        <v>570</v>
+      </c>
+      <c r="BF10" t="s">
+        <v>571</v>
+      </c>
+      <c r="BG10" t="s">
+        <v>571</v>
+      </c>
+      <c r="BH10" t="s">
+        <v>570</v>
+      </c>
+      <c r="BI10" t="s">
         <v>572</v>
       </c>
-      <c r="BD10" t="s">
+      <c r="BJ10" t="s">
+        <v>572</v>
+      </c>
+      <c r="BK10" t="s">
+        <v>570</v>
+      </c>
+      <c r="BL10" t="s">
         <v>571</v>
       </c>
-      <c r="BE10" t="s">
+      <c r="BM10" t="s">
         <v>571</v>
       </c>
-      <c r="BF10" t="s">
+      <c r="BN10" t="s">
+        <v>570</v>
+      </c>
+      <c r="BO10" t="s">
+        <v>571</v>
+      </c>
+      <c r="BP10" t="s">
         <v>572</v>
       </c>
-      <c r="BG10" t="s">
+      <c r="BQ10" t="s">
+        <v>570</v>
+      </c>
+      <c r="BR10" t="s">
         <v>572</v>
       </c>
-      <c r="BH10" t="s">
+      <c r="BS10" t="s">
         <v>571</v>
-      </c>
-      <c r="BI10" t="s">
-        <v>573</v>
-      </c>
-      <c r="BJ10" t="s">
-        <v>573</v>
-      </c>
-      <c r="BK10" t="s">
-        <v>571</v>
-      </c>
-      <c r="BL10" t="s">
-        <v>572</v>
-      </c>
-      <c r="BM10" t="s">
-        <v>572</v>
-      </c>
-      <c r="BN10" t="s">
-        <v>571</v>
-      </c>
-      <c r="BO10" t="s">
-        <v>572</v>
-      </c>
-      <c r="BP10" t="s">
-        <v>573</v>
-      </c>
-      <c r="BQ10" t="s">
-        <v>571</v>
-      </c>
-      <c r="BR10" t="s">
-        <v>573</v>
-      </c>
-      <c r="BS10" t="s">
-        <v>572</v>
       </c>
     </row>
     <row r="11" spans="2:71" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
@@ -13943,22 +13943,22 @@
         <v>100</v>
       </c>
       <c r="AA11" s="106" t="s">
-        <v>377</v>
+        <v>376</v>
       </c>
       <c r="AB11" s="106">
         <v>45</v>
       </c>
       <c r="AC11" s="106" t="s">
-        <v>402</v>
+        <v>401</v>
       </c>
       <c r="AD11" s="106" t="s">
-        <v>404</v>
+        <v>403</v>
       </c>
       <c r="AE11" s="106" t="s">
-        <v>408</v>
+        <v>407</v>
       </c>
       <c r="AF11" s="106" t="s">
-        <v>406</v>
+        <v>405</v>
       </c>
       <c r="AG11" s="4"/>
       <c r="AH11" s="4"/>
@@ -14039,58 +14039,58 @@
         <v>78</v>
       </c>
       <c r="BB11" t="s">
+        <v>571</v>
+      </c>
+      <c r="BC11" t="s">
+        <v>571</v>
+      </c>
+      <c r="BD11" t="s">
+        <v>570</v>
+      </c>
+      <c r="BE11" t="s">
+        <v>571</v>
+      </c>
+      <c r="BF11" t="s">
         <v>572</v>
       </c>
-      <c r="BC11" t="s">
+      <c r="BG11" t="s">
+        <v>571</v>
+      </c>
+      <c r="BH11" t="s">
+        <v>571</v>
+      </c>
+      <c r="BI11" t="s">
+        <v>571</v>
+      </c>
+      <c r="BJ11" t="s">
+        <v>571</v>
+      </c>
+      <c r="BK11" t="s">
+        <v>571</v>
+      </c>
+      <c r="BL11" t="s">
+        <v>571</v>
+      </c>
+      <c r="BM11" t="s">
+        <v>571</v>
+      </c>
+      <c r="BN11" t="s">
+        <v>571</v>
+      </c>
+      <c r="BO11" t="s">
+        <v>571</v>
+      </c>
+      <c r="BP11" t="s">
+        <v>571</v>
+      </c>
+      <c r="BQ11" t="s">
+        <v>571</v>
+      </c>
+      <c r="BR11" t="s">
         <v>572</v>
       </c>
-      <c r="BD11" t="s">
+      <c r="BS11" t="s">
         <v>571</v>
-      </c>
-      <c r="BE11" t="s">
-        <v>572</v>
-      </c>
-      <c r="BF11" t="s">
-        <v>573</v>
-      </c>
-      <c r="BG11" t="s">
-        <v>572</v>
-      </c>
-      <c r="BH11" t="s">
-        <v>572</v>
-      </c>
-      <c r="BI11" t="s">
-        <v>572</v>
-      </c>
-      <c r="BJ11" t="s">
-        <v>572</v>
-      </c>
-      <c r="BK11" t="s">
-        <v>572</v>
-      </c>
-      <c r="BL11" t="s">
-        <v>572</v>
-      </c>
-      <c r="BM11" t="s">
-        <v>572</v>
-      </c>
-      <c r="BN11" t="s">
-        <v>572</v>
-      </c>
-      <c r="BO11" t="s">
-        <v>572</v>
-      </c>
-      <c r="BP11" t="s">
-        <v>572</v>
-      </c>
-      <c r="BQ11" t="s">
-        <v>572</v>
-      </c>
-      <c r="BR11" t="s">
-        <v>573</v>
-      </c>
-      <c r="BS11" t="s">
-        <v>572</v>
       </c>
     </row>
     <row r="12" spans="2:71" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
@@ -14170,22 +14170,22 @@
         <v>93.3</v>
       </c>
       <c r="AA12" s="106" t="s">
-        <v>378</v>
+        <v>377</v>
       </c>
       <c r="AB12" s="106">
         <v>60</v>
       </c>
       <c r="AC12" s="106" t="s">
-        <v>391</v>
+        <v>390</v>
       </c>
       <c r="AD12" s="106" t="s">
+        <v>408</v>
+      </c>
+      <c r="AE12" s="106" t="s">
         <v>409</v>
       </c>
-      <c r="AE12" s="106" t="s">
+      <c r="AF12" s="106" t="s">
         <v>410</v>
-      </c>
-      <c r="AF12" s="106" t="s">
-        <v>411</v>
       </c>
       <c r="AG12" s="4"/>
       <c r="AH12" s="4"/>
@@ -14266,58 +14266,58 @@
         <v>74</v>
       </c>
       <c r="BB12" t="s">
-        <v>573</v>
+        <v>572</v>
       </c>
       <c r="BC12" t="s">
-        <v>573</v>
+        <v>572</v>
       </c>
       <c r="BD12" t="s">
+        <v>570</v>
+      </c>
+      <c r="BE12" t="s">
+        <v>572</v>
+      </c>
+      <c r="BF12" t="s">
+        <v>572</v>
+      </c>
+      <c r="BG12" t="s">
+        <v>572</v>
+      </c>
+      <c r="BH12" t="s">
+        <v>572</v>
+      </c>
+      <c r="BI12" t="s">
+        <v>572</v>
+      </c>
+      <c r="BJ12" t="s">
+        <v>572</v>
+      </c>
+      <c r="BK12" t="s">
+        <v>572</v>
+      </c>
+      <c r="BL12" t="s">
+        <v>572</v>
+      </c>
+      <c r="BM12" t="s">
         <v>571</v>
       </c>
-      <c r="BE12" t="s">
-        <v>573</v>
-      </c>
-      <c r="BF12" t="s">
-        <v>573</v>
-      </c>
-      <c r="BG12" t="s">
-        <v>573</v>
-      </c>
-      <c r="BH12" t="s">
-        <v>573</v>
-      </c>
-      <c r="BI12" t="s">
-        <v>573</v>
-      </c>
-      <c r="BJ12" t="s">
-        <v>573</v>
-      </c>
-      <c r="BK12" t="s">
-        <v>573</v>
-      </c>
-      <c r="BL12" t="s">
-        <v>573</v>
-      </c>
-      <c r="BM12" t="s">
+      <c r="BN12" t="s">
         <v>572</v>
       </c>
-      <c r="BN12" t="s">
-        <v>573</v>
-      </c>
       <c r="BO12" t="s">
-        <v>573</v>
+        <v>572</v>
       </c>
       <c r="BP12" t="s">
+        <v>571</v>
+      </c>
+      <c r="BQ12" t="s">
         <v>572</v>
       </c>
-      <c r="BQ12" t="s">
-        <v>573</v>
-      </c>
       <c r="BR12" t="s">
-        <v>573</v>
+        <v>572</v>
       </c>
       <c r="BS12" t="s">
-        <v>573</v>
+        <v>572</v>
       </c>
     </row>
     <row r="13" spans="2:71" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
@@ -14397,7 +14397,7 @@
         <v>87.5</v>
       </c>
       <c r="AA13" s="106" t="s">
-        <v>379</v>
+        <v>378</v>
       </c>
       <c r="AB13" s="106">
         <v>60</v>
@@ -14406,13 +14406,13 @@
         <v>152</v>
       </c>
       <c r="AD13" s="106" t="s">
-        <v>409</v>
+        <v>408</v>
       </c>
       <c r="AE13" s="106" t="s">
-        <v>412</v>
+        <v>411</v>
       </c>
       <c r="AF13" s="106" t="s">
-        <v>411</v>
+        <v>410</v>
       </c>
       <c r="AG13" s="4"/>
       <c r="AH13" s="4"/>
@@ -14493,58 +14493,58 @@
         <v>66.7</v>
       </c>
       <c r="BB13" t="s">
+        <v>571</v>
+      </c>
+      <c r="BC13" t="s">
+        <v>571</v>
+      </c>
+      <c r="BD13" t="s">
+        <v>570</v>
+      </c>
+      <c r="BE13" t="s">
+        <v>571</v>
+      </c>
+      <c r="BF13" t="s">
         <v>572</v>
       </c>
-      <c r="BC13" t="s">
+      <c r="BG13" t="s">
         <v>572</v>
       </c>
-      <c r="BD13" t="s">
+      <c r="BH13" t="s">
         <v>571</v>
       </c>
-      <c r="BE13" t="s">
+      <c r="BI13" t="s">
         <v>572</v>
       </c>
-      <c r="BF13" t="s">
-        <v>573</v>
-      </c>
-      <c r="BG13" t="s">
-        <v>573</v>
-      </c>
-      <c r="BH13" t="s">
+      <c r="BJ13" t="s">
         <v>572</v>
       </c>
-      <c r="BI13" t="s">
-        <v>573</v>
-      </c>
-      <c r="BJ13" t="s">
-        <v>573</v>
-      </c>
       <c r="BK13" t="s">
-        <v>573</v>
+        <v>572</v>
       </c>
       <c r="BL13" t="s">
-        <v>573</v>
+        <v>572</v>
       </c>
       <c r="BM13" t="s">
-        <v>573</v>
+        <v>572</v>
       </c>
       <c r="BN13" t="s">
+        <v>571</v>
+      </c>
+      <c r="BO13" t="s">
         <v>572</v>
       </c>
-      <c r="BO13" t="s">
-        <v>573</v>
-      </c>
       <c r="BP13" t="s">
-        <v>573</v>
+        <v>572</v>
       </c>
       <c r="BQ13" t="s">
+        <v>571</v>
+      </c>
+      <c r="BR13" t="s">
+        <v>571</v>
+      </c>
+      <c r="BS13" t="s">
         <v>572</v>
-      </c>
-      <c r="BR13" t="s">
-        <v>572</v>
-      </c>
-      <c r="BS13" t="s">
-        <v>573</v>
       </c>
     </row>
     <row r="14" spans="2:71" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
@@ -14624,22 +14624,22 @@
         <v>82.5</v>
       </c>
       <c r="AA14" s="106" t="s">
-        <v>380</v>
+        <v>379</v>
       </c>
       <c r="AB14" s="106">
         <v>60</v>
       </c>
       <c r="AC14" s="106" t="s">
-        <v>402</v>
+        <v>401</v>
       </c>
       <c r="AD14" s="106" t="s">
-        <v>409</v>
+        <v>408</v>
       </c>
       <c r="AE14" s="106" t="s">
-        <v>413</v>
+        <v>412</v>
       </c>
       <c r="AF14" s="106" t="s">
-        <v>411</v>
+        <v>410</v>
       </c>
       <c r="AG14" s="4"/>
       <c r="AH14" s="4"/>
@@ -14720,58 +14720,58 @@
         <v>60</v>
       </c>
       <c r="BB14" t="s">
+        <v>571</v>
+      </c>
+      <c r="BC14" t="s">
         <v>572</v>
       </c>
-      <c r="BC14" t="s">
-        <v>573</v>
-      </c>
       <c r="BD14" t="s">
+        <v>570</v>
+      </c>
+      <c r="BE14" t="s">
         <v>571</v>
       </c>
-      <c r="BE14" t="s">
+      <c r="BF14" t="s">
+        <v>571</v>
+      </c>
+      <c r="BG14" t="s">
         <v>572</v>
       </c>
-      <c r="BF14" t="s">
+      <c r="BH14" t="s">
+        <v>571</v>
+      </c>
+      <c r="BI14" t="s">
         <v>572</v>
       </c>
-      <c r="BG14" t="s">
-        <v>573</v>
-      </c>
-      <c r="BH14" t="s">
+      <c r="BJ14" t="s">
         <v>572</v>
       </c>
-      <c r="BI14" t="s">
-        <v>573</v>
-      </c>
-      <c r="BJ14" t="s">
-        <v>573</v>
-      </c>
       <c r="BK14" t="s">
-        <v>573</v>
+        <v>572</v>
       </c>
       <c r="BL14" t="s">
-        <v>573</v>
+        <v>572</v>
       </c>
       <c r="BM14" t="s">
+        <v>571</v>
+      </c>
+      <c r="BN14" t="s">
+        <v>571</v>
+      </c>
+      <c r="BO14" t="s">
+        <v>571</v>
+      </c>
+      <c r="BP14" t="s">
         <v>572</v>
       </c>
-      <c r="BN14" t="s">
+      <c r="BQ14" t="s">
+        <v>571</v>
+      </c>
+      <c r="BR14" t="s">
+        <v>571</v>
+      </c>
+      <c r="BS14" t="s">
         <v>572</v>
-      </c>
-      <c r="BO14" t="s">
-        <v>572</v>
-      </c>
-      <c r="BP14" t="s">
-        <v>573</v>
-      </c>
-      <c r="BQ14" t="s">
-        <v>572</v>
-      </c>
-      <c r="BR14" t="s">
-        <v>572</v>
-      </c>
-      <c r="BS14" t="s">
-        <v>573</v>
       </c>
     </row>
     <row r="15" spans="2:71" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
@@ -14851,22 +14851,22 @@
         <v>78</v>
       </c>
       <c r="AA15" s="106" t="s">
-        <v>381</v>
+        <v>380</v>
       </c>
       <c r="AB15" s="106">
         <v>80</v>
       </c>
       <c r="AC15" s="106" t="s">
-        <v>391</v>
+        <v>390</v>
       </c>
       <c r="AD15" s="106" t="s">
+        <v>413</v>
+      </c>
+      <c r="AE15" s="106" t="s">
         <v>414</v>
       </c>
-      <c r="AE15" s="106" t="s">
+      <c r="AF15" s="106" t="s">
         <v>415</v>
-      </c>
-      <c r="AF15" s="106" t="s">
-        <v>416</v>
       </c>
       <c r="AG15" s="4"/>
       <c r="AH15" s="4"/>
@@ -14947,58 +14947,58 @@
         <v>55</v>
       </c>
       <c r="BB15" t="s">
-        <v>573</v>
+        <v>572</v>
       </c>
       <c r="BC15" t="s">
-        <v>573</v>
+        <v>572</v>
       </c>
       <c r="BD15" t="s">
-        <v>571</v>
+        <v>570</v>
       </c>
       <c r="BE15" t="s">
-        <v>573</v>
+        <v>572</v>
       </c>
       <c r="BF15" t="s">
-        <v>573</v>
+        <v>572</v>
       </c>
       <c r="BG15" t="s">
-        <v>571</v>
+        <v>570</v>
       </c>
       <c r="BH15" t="s">
-        <v>573</v>
+        <v>572</v>
       </c>
       <c r="BI15" t="s">
-        <v>573</v>
+        <v>572</v>
       </c>
       <c r="BJ15" t="s">
-        <v>573</v>
+        <v>572</v>
       </c>
       <c r="BK15" t="s">
-        <v>573</v>
+        <v>572</v>
       </c>
       <c r="BL15" t="s">
-        <v>573</v>
+        <v>572</v>
       </c>
       <c r="BM15" t="s">
-        <v>573</v>
+        <v>572</v>
       </c>
       <c r="BN15" t="s">
-        <v>573</v>
+        <v>572</v>
       </c>
       <c r="BO15" t="s">
-        <v>573</v>
+        <v>572</v>
       </c>
       <c r="BP15" t="s">
-        <v>573</v>
+        <v>572</v>
       </c>
       <c r="BQ15" t="s">
-        <v>573</v>
+        <v>572</v>
       </c>
       <c r="BR15" t="s">
-        <v>573</v>
+        <v>572</v>
       </c>
       <c r="BS15" t="s">
-        <v>573</v>
+        <v>572</v>
       </c>
     </row>
     <row r="16" spans="2:71" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
@@ -15078,7 +15078,7 @@
         <v>74</v>
       </c>
       <c r="AA16" s="106" t="s">
-        <v>382</v>
+        <v>381</v>
       </c>
       <c r="AB16" s="106">
         <v>80</v>
@@ -15087,13 +15087,13 @@
         <v>152</v>
       </c>
       <c r="AD16" s="106" t="s">
-        <v>414</v>
+        <v>413</v>
       </c>
       <c r="AE16" s="106" t="s">
-        <v>417</v>
+        <v>416</v>
       </c>
       <c r="AF16" s="106" t="s">
-        <v>416</v>
+        <v>415</v>
       </c>
       <c r="AG16" s="4"/>
       <c r="AH16" s="4"/>
@@ -15174,58 +15174,58 @@
         <v>50</v>
       </c>
       <c r="BB16" t="s">
+        <v>571</v>
+      </c>
+      <c r="BC16" t="s">
         <v>572</v>
       </c>
-      <c r="BC16" t="s">
-        <v>573</v>
-      </c>
       <c r="BD16" t="s">
+        <v>570</v>
+      </c>
+      <c r="BE16" t="s">
         <v>571</v>
       </c>
-      <c r="BE16" t="s">
+      <c r="BF16" t="s">
         <v>572</v>
       </c>
-      <c r="BF16" t="s">
-        <v>573</v>
-      </c>
       <c r="BG16" t="s">
+        <v>570</v>
+      </c>
+      <c r="BH16" t="s">
+        <v>572</v>
+      </c>
+      <c r="BI16" t="s">
+        <v>572</v>
+      </c>
+      <c r="BJ16" t="s">
+        <v>572</v>
+      </c>
+      <c r="BK16" t="s">
         <v>571</v>
       </c>
-      <c r="BH16" t="s">
-        <v>573</v>
-      </c>
-      <c r="BI16" t="s">
-        <v>573</v>
-      </c>
-      <c r="BJ16" t="s">
-        <v>573</v>
-      </c>
-      <c r="BK16" t="s">
+      <c r="BL16" t="s">
+        <v>571</v>
+      </c>
+      <c r="BM16" t="s">
+        <v>571</v>
+      </c>
+      <c r="BN16" t="s">
+        <v>571</v>
+      </c>
+      <c r="BO16" t="s">
+        <v>571</v>
+      </c>
+      <c r="BP16" t="s">
+        <v>571</v>
+      </c>
+      <c r="BQ16" t="s">
+        <v>571</v>
+      </c>
+      <c r="BR16" t="s">
         <v>572</v>
       </c>
-      <c r="BL16" t="s">
+      <c r="BS16" t="s">
         <v>572</v>
-      </c>
-      <c r="BM16" t="s">
-        <v>572</v>
-      </c>
-      <c r="BN16" t="s">
-        <v>572</v>
-      </c>
-      <c r="BO16" t="s">
-        <v>572</v>
-      </c>
-      <c r="BP16" t="s">
-        <v>572</v>
-      </c>
-      <c r="BQ16" t="s">
-        <v>572</v>
-      </c>
-      <c r="BR16" t="s">
-        <v>573</v>
-      </c>
-      <c r="BS16" t="s">
-        <v>573</v>
       </c>
     </row>
     <row r="17" spans="2:71" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
@@ -15305,22 +15305,22 @@
         <v>66.7</v>
       </c>
       <c r="AA17" s="106" t="s">
-        <v>383</v>
+        <v>382</v>
       </c>
       <c r="AB17" s="106">
         <v>80</v>
       </c>
       <c r="AC17" s="106" t="s">
-        <v>402</v>
+        <v>401</v>
       </c>
       <c r="AD17" s="106" t="s">
-        <v>414</v>
+        <v>413</v>
       </c>
       <c r="AE17" s="106" t="s">
-        <v>418</v>
+        <v>417</v>
       </c>
       <c r="AF17" s="106" t="s">
-        <v>416</v>
+        <v>415</v>
       </c>
       <c r="AG17" s="4"/>
       <c r="AH17" s="4"/>
@@ -15401,58 +15401,58 @@
         <v/>
       </c>
       <c r="BB17" t="s">
+        <v>571</v>
+      </c>
+      <c r="BC17" t="s">
         <v>572</v>
       </c>
-      <c r="BC17" t="s">
-        <v>573</v>
-      </c>
       <c r="BD17" t="s">
+        <v>570</v>
+      </c>
+      <c r="BE17" t="s">
         <v>571</v>
       </c>
-      <c r="BE17" t="s">
+      <c r="BF17" t="s">
         <v>572</v>
       </c>
-      <c r="BF17" t="s">
-        <v>573</v>
-      </c>
       <c r="BG17" t="s">
+        <v>570</v>
+      </c>
+      <c r="BH17" t="s">
         <v>571</v>
       </c>
-      <c r="BH17" t="s">
+      <c r="BI17" t="s">
         <v>572</v>
       </c>
-      <c r="BI17" t="s">
-        <v>573</v>
-      </c>
       <c r="BJ17" t="s">
+        <v>570</v>
+      </c>
+      <c r="BK17" t="s">
         <v>571</v>
       </c>
-      <c r="BK17" t="s">
+      <c r="BL17" t="s">
         <v>572</v>
       </c>
-      <c r="BL17" t="s">
-        <v>573</v>
-      </c>
       <c r="BM17" t="s">
+        <v>570</v>
+      </c>
+      <c r="BN17" t="s">
         <v>571</v>
       </c>
-      <c r="BN17" t="s">
+      <c r="BO17" t="s">
+        <v>571</v>
+      </c>
+      <c r="BP17" t="s">
+        <v>571</v>
+      </c>
+      <c r="BQ17" t="s">
+        <v>571</v>
+      </c>
+      <c r="BR17" t="s">
         <v>572</v>
       </c>
-      <c r="BO17" t="s">
+      <c r="BS17" t="s">
         <v>572</v>
-      </c>
-      <c r="BP17" t="s">
-        <v>572</v>
-      </c>
-      <c r="BQ17" t="s">
-        <v>572</v>
-      </c>
-      <c r="BR17" t="s">
-        <v>573</v>
-      </c>
-      <c r="BS17" t="s">
-        <v>573</v>
       </c>
     </row>
     <row r="18" spans="2:71" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
@@ -15532,22 +15532,22 @@
         <v>60</v>
       </c>
       <c r="AA18" s="106" t="s">
-        <v>384</v>
+        <v>383</v>
       </c>
       <c r="AB18" s="106">
         <v>120</v>
       </c>
       <c r="AC18" s="106" t="s">
-        <v>391</v>
+        <v>390</v>
       </c>
       <c r="AD18" s="106" t="s">
+        <v>418</v>
+      </c>
+      <c r="AE18" s="106" t="s">
         <v>419</v>
       </c>
-      <c r="AE18" s="106" t="s">
+      <c r="AF18" s="106" t="s">
         <v>420</v>
-      </c>
-      <c r="AF18" s="106" t="s">
-        <v>421</v>
       </c>
       <c r="AG18" s="4"/>
       <c r="AH18" s="4"/>
@@ -15628,58 +15628,58 @@
         <v/>
       </c>
       <c r="BB18" t="s">
+        <v>571</v>
+      </c>
+      <c r="BC18" t="s">
         <v>572</v>
       </c>
-      <c r="BC18" t="s">
-        <v>573</v>
-      </c>
       <c r="BD18" t="s">
+        <v>570</v>
+      </c>
+      <c r="BE18" t="s">
         <v>571</v>
       </c>
-      <c r="BE18" t="s">
+      <c r="BF18" t="s">
+        <v>571</v>
+      </c>
+      <c r="BG18" t="s">
+        <v>570</v>
+      </c>
+      <c r="BH18" t="s">
+        <v>571</v>
+      </c>
+      <c r="BI18" t="s">
+        <v>571</v>
+      </c>
+      <c r="BJ18" t="s">
+        <v>570</v>
+      </c>
+      <c r="BK18" t="s">
+        <v>571</v>
+      </c>
+      <c r="BL18" t="s">
         <v>572</v>
       </c>
-      <c r="BF18" t="s">
+      <c r="BM18" t="s">
+        <v>570</v>
+      </c>
+      <c r="BN18" t="s">
+        <v>571</v>
+      </c>
+      <c r="BO18" t="s">
         <v>572</v>
       </c>
-      <c r="BG18" t="s">
+      <c r="BP18" t="s">
+        <v>572</v>
+      </c>
+      <c r="BQ18" t="s">
         <v>571</v>
       </c>
-      <c r="BH18" t="s">
-        <v>572</v>
-      </c>
-      <c r="BI18" t="s">
-        <v>572</v>
-      </c>
-      <c r="BJ18" t="s">
+      <c r="BR18" t="s">
         <v>571</v>
       </c>
-      <c r="BK18" t="s">
-        <v>572</v>
-      </c>
-      <c r="BL18" t="s">
-        <v>573</v>
-      </c>
-      <c r="BM18" t="s">
+      <c r="BS18" t="s">
         <v>571</v>
-      </c>
-      <c r="BN18" t="s">
-        <v>572</v>
-      </c>
-      <c r="BO18" t="s">
-        <v>573</v>
-      </c>
-      <c r="BP18" t="s">
-        <v>573</v>
-      </c>
-      <c r="BQ18" t="s">
-        <v>572</v>
-      </c>
-      <c r="BR18" t="s">
-        <v>572</v>
-      </c>
-      <c r="BS18" t="s">
-        <v>572</v>
       </c>
     </row>
     <row r="19" spans="2:71" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
@@ -15759,7 +15759,7 @@
         <v>55</v>
       </c>
       <c r="AA19" s="106" t="s">
-        <v>385</v>
+        <v>384</v>
       </c>
       <c r="AB19" s="106">
         <v>120</v>
@@ -15768,13 +15768,13 @@
         <v>152</v>
       </c>
       <c r="AD19" s="106" t="s">
-        <v>419</v>
+        <v>418</v>
       </c>
       <c r="AE19" s="106" t="s">
-        <v>422</v>
+        <v>421</v>
       </c>
       <c r="AF19" s="106" t="s">
-        <v>421</v>
+        <v>420</v>
       </c>
       <c r="AG19" s="4"/>
       <c r="AH19" s="4"/>
@@ -15855,58 +15855,58 @@
         <v/>
       </c>
       <c r="BB19" t="s">
-        <v>573</v>
+        <v>572</v>
       </c>
       <c r="BC19" t="s">
+        <v>571</v>
+      </c>
+      <c r="BD19" t="s">
+        <v>570</v>
+      </c>
+      <c r="BE19" t="s">
+        <v>571</v>
+      </c>
+      <c r="BF19" t="s">
         <v>572</v>
       </c>
-      <c r="BD19" t="s">
+      <c r="BG19" t="s">
+        <v>570</v>
+      </c>
+      <c r="BH19" t="s">
         <v>571</v>
       </c>
-      <c r="BE19" t="s">
+      <c r="BI19" t="s">
         <v>572</v>
       </c>
-      <c r="BF19" t="s">
-        <v>573</v>
-      </c>
-      <c r="BG19" t="s">
+      <c r="BJ19" t="s">
+        <v>570</v>
+      </c>
+      <c r="BK19" t="s">
         <v>571</v>
       </c>
-      <c r="BH19" t="s">
+      <c r="BL19" t="s">
         <v>572</v>
       </c>
-      <c r="BI19" t="s">
-        <v>573</v>
-      </c>
-      <c r="BJ19" t="s">
+      <c r="BM19" t="s">
+        <v>570</v>
+      </c>
+      <c r="BN19" t="s">
         <v>571</v>
       </c>
-      <c r="BK19" t="s">
+      <c r="BO19" t="s">
         <v>572</v>
       </c>
-      <c r="BL19" t="s">
-        <v>573</v>
-      </c>
-      <c r="BM19" t="s">
+      <c r="BP19" t="s">
+        <v>570</v>
+      </c>
+      <c r="BQ19" t="s">
         <v>571</v>
       </c>
-      <c r="BN19" t="s">
+      <c r="BR19" t="s">
         <v>572</v>
       </c>
-      <c r="BO19" t="s">
-        <v>573</v>
-      </c>
-      <c r="BP19" t="s">
-        <v>571</v>
-      </c>
-      <c r="BQ19" t="s">
+      <c r="BS19" t="s">
         <v>572</v>
-      </c>
-      <c r="BR19" t="s">
-        <v>573</v>
-      </c>
-      <c r="BS19" t="s">
-        <v>573</v>
       </c>
     </row>
     <row r="20" spans="2:71" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
@@ -15986,22 +15986,22 @@
         <v>50</v>
       </c>
       <c r="AA20" s="106" t="s">
-        <v>386</v>
+        <v>385</v>
       </c>
       <c r="AB20" s="106">
         <v>120</v>
       </c>
       <c r="AC20" s="106" t="s">
-        <v>402</v>
+        <v>401</v>
       </c>
       <c r="AD20" s="106" t="s">
-        <v>419</v>
+        <v>418</v>
       </c>
       <c r="AE20" s="106" t="s">
-        <v>423</v>
+        <v>422</v>
       </c>
       <c r="AF20" s="106" t="s">
-        <v>421</v>
+        <v>420</v>
       </c>
       <c r="AG20" s="4"/>
       <c r="AH20" s="4"/>
@@ -16082,58 +16082,58 @@
         <v/>
       </c>
       <c r="BB20" t="s">
+        <v>571</v>
+      </c>
+      <c r="BC20" t="s">
+        <v>570</v>
+      </c>
+      <c r="BD20" t="s">
+        <v>570</v>
+      </c>
+      <c r="BE20" t="s">
+        <v>571</v>
+      </c>
+      <c r="BF20" t="s">
         <v>572</v>
       </c>
-      <c r="BC20" t="s">
+      <c r="BG20" t="s">
+        <v>570</v>
+      </c>
+      <c r="BH20" t="s">
+        <v>572</v>
+      </c>
+      <c r="BI20" t="s">
+        <v>572</v>
+      </c>
+      <c r="BJ20" t="s">
+        <v>570</v>
+      </c>
+      <c r="BK20" t="s">
+        <v>572</v>
+      </c>
+      <c r="BL20" t="s">
+        <v>572</v>
+      </c>
+      <c r="BM20" t="s">
+        <v>570</v>
+      </c>
+      <c r="BN20" t="s">
+        <v>572</v>
+      </c>
+      <c r="BO20" t="s">
+        <v>572</v>
+      </c>
+      <c r="BP20" t="s">
+        <v>570</v>
+      </c>
+      <c r="BQ20" t="s">
+        <v>572</v>
+      </c>
+      <c r="BR20" t="s">
+        <v>572</v>
+      </c>
+      <c r="BS20" t="s">
         <v>571</v>
-      </c>
-      <c r="BD20" t="s">
-        <v>571</v>
-      </c>
-      <c r="BE20" t="s">
-        <v>572</v>
-      </c>
-      <c r="BF20" t="s">
-        <v>573</v>
-      </c>
-      <c r="BG20" t="s">
-        <v>571</v>
-      </c>
-      <c r="BH20" t="s">
-        <v>573</v>
-      </c>
-      <c r="BI20" t="s">
-        <v>573</v>
-      </c>
-      <c r="BJ20" t="s">
-        <v>571</v>
-      </c>
-      <c r="BK20" t="s">
-        <v>573</v>
-      </c>
-      <c r="BL20" t="s">
-        <v>573</v>
-      </c>
-      <c r="BM20" t="s">
-        <v>571</v>
-      </c>
-      <c r="BN20" t="s">
-        <v>573</v>
-      </c>
-      <c r="BO20" t="s">
-        <v>573</v>
-      </c>
-      <c r="BP20" t="s">
-        <v>571</v>
-      </c>
-      <c r="BQ20" t="s">
-        <v>573</v>
-      </c>
-      <c r="BR20" t="s">
-        <v>573</v>
-      </c>
-      <c r="BS20" t="s">
-        <v>572</v>
       </c>
     </row>
     <row r="21" spans="2:71" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
@@ -16213,22 +16213,22 @@
         <v>—</v>
       </c>
       <c r="AA21" s="106" t="s">
-        <v>387</v>
+        <v>386</v>
       </c>
       <c r="AB21" s="106">
         <v>150</v>
       </c>
       <c r="AC21" s="106" t="s">
-        <v>391</v>
+        <v>390</v>
       </c>
       <c r="AD21" s="106" t="s">
+        <v>423</v>
+      </c>
+      <c r="AE21" s="106" t="s">
         <v>424</v>
       </c>
-      <c r="AE21" s="106" t="s">
+      <c r="AF21" s="106" t="s">
         <v>425</v>
-      </c>
-      <c r="AF21" s="106" t="s">
-        <v>426</v>
       </c>
       <c r="AG21" s="4"/>
       <c r="AH21" s="4"/>
@@ -16309,58 +16309,58 @@
         <v/>
       </c>
       <c r="BB21" t="s">
-        <v>573</v>
+        <v>572</v>
       </c>
       <c r="BC21" t="s">
+        <v>570</v>
+      </c>
+      <c r="BD21" t="s">
+        <v>570</v>
+      </c>
+      <c r="BE21" t="s">
+        <v>572</v>
+      </c>
+      <c r="BF21" t="s">
         <v>571</v>
       </c>
-      <c r="BD21" t="s">
+      <c r="BG21" t="s">
+        <v>570</v>
+      </c>
+      <c r="BH21" t="s">
+        <v>572</v>
+      </c>
+      <c r="BI21" t="s">
         <v>571</v>
       </c>
-      <c r="BE21" t="s">
-        <v>573</v>
-      </c>
-      <c r="BF21" t="s">
+      <c r="BJ21" t="s">
+        <v>570</v>
+      </c>
+      <c r="BK21" t="s">
         <v>572</v>
       </c>
-      <c r="BG21" t="s">
+      <c r="BL21" t="s">
         <v>571</v>
       </c>
-      <c r="BH21" t="s">
-        <v>573</v>
-      </c>
-      <c r="BI21" t="s">
+      <c r="BM21" t="s">
+        <v>570</v>
+      </c>
+      <c r="BN21" t="s">
         <v>572</v>
       </c>
-      <c r="BJ21" t="s">
-        <v>571</v>
-      </c>
-      <c r="BK21" t="s">
-        <v>573</v>
-      </c>
-      <c r="BL21" t="s">
+      <c r="BO21" t="s">
         <v>572</v>
       </c>
-      <c r="BM21" t="s">
-        <v>571</v>
-      </c>
-      <c r="BN21" t="s">
-        <v>573</v>
-      </c>
-      <c r="BO21" t="s">
-        <v>573</v>
-      </c>
       <c r="BP21" t="s">
-        <v>571</v>
+        <v>570</v>
       </c>
       <c r="BQ21" t="s">
-        <v>573</v>
+        <v>572</v>
       </c>
       <c r="BR21" t="s">
-        <v>573</v>
+        <v>572</v>
       </c>
       <c r="BS21" t="s">
-        <v>571</v>
+        <v>570</v>
       </c>
     </row>
     <row r="22" spans="2:71" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
@@ -16440,7 +16440,7 @@
         <v>—</v>
       </c>
       <c r="AA22" s="106" t="s">
-        <v>388</v>
+        <v>387</v>
       </c>
       <c r="AB22" s="106">
         <v>150</v>
@@ -16449,13 +16449,13 @@
         <v>152</v>
       </c>
       <c r="AD22" s="106" t="s">
-        <v>424</v>
+        <v>423</v>
       </c>
       <c r="AE22" s="106" t="s">
-        <v>427</v>
+        <v>426</v>
       </c>
       <c r="AF22" s="106" t="s">
-        <v>426</v>
+        <v>425</v>
       </c>
       <c r="AG22" s="4"/>
       <c r="AH22" s="4"/>
@@ -16536,58 +16536,58 @@
         <v/>
       </c>
       <c r="BB22" t="s">
+        <v>571</v>
+      </c>
+      <c r="BC22" t="s">
+        <v>570</v>
+      </c>
+      <c r="BD22" t="s">
+        <v>570</v>
+      </c>
+      <c r="BE22" t="s">
         <v>572</v>
       </c>
-      <c r="BC22" t="s">
+      <c r="BF22" t="s">
+        <v>570</v>
+      </c>
+      <c r="BG22" t="s">
+        <v>570</v>
+      </c>
+      <c r="BH22" t="s">
+        <v>572</v>
+      </c>
+      <c r="BI22" t="s">
+        <v>572</v>
+      </c>
+      <c r="BJ22" t="s">
+        <v>570</v>
+      </c>
+      <c r="BK22" t="s">
+        <v>572</v>
+      </c>
+      <c r="BL22" t="s">
+        <v>572</v>
+      </c>
+      <c r="BM22" t="s">
+        <v>570</v>
+      </c>
+      <c r="BN22" t="s">
+        <v>572</v>
+      </c>
+      <c r="BO22" t="s">
         <v>571</v>
       </c>
-      <c r="BD22" t="s">
-        <v>571</v>
-      </c>
-      <c r="BE22" t="s">
-        <v>573</v>
-      </c>
-      <c r="BF22" t="s">
-        <v>571</v>
-      </c>
-      <c r="BG22" t="s">
-        <v>571</v>
-      </c>
-      <c r="BH22" t="s">
-        <v>573</v>
-      </c>
-      <c r="BI22" t="s">
-        <v>573</v>
-      </c>
-      <c r="BJ22" t="s">
-        <v>571</v>
-      </c>
-      <c r="BK22" t="s">
-        <v>573</v>
-      </c>
-      <c r="BL22" t="s">
-        <v>573</v>
-      </c>
-      <c r="BM22" t="s">
-        <v>571</v>
-      </c>
-      <c r="BN22" t="s">
-        <v>573</v>
-      </c>
-      <c r="BO22" t="s">
+      <c r="BP22" t="s">
+        <v>570</v>
+      </c>
+      <c r="BQ22" t="s">
         <v>572</v>
       </c>
-      <c r="BP22" t="s">
-        <v>571</v>
-      </c>
-      <c r="BQ22" t="s">
-        <v>573</v>
-      </c>
       <c r="BR22" t="s">
-        <v>573</v>
+        <v>572</v>
       </c>
       <c r="BS22" t="s">
-        <v>571</v>
+        <v>570</v>
       </c>
     </row>
     <row r="23" spans="2:71" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
@@ -16667,22 +16667,22 @@
         <v>—</v>
       </c>
       <c r="AA23" s="106" t="s">
-        <v>389</v>
+        <v>388</v>
       </c>
       <c r="AB23" s="106">
         <v>150</v>
       </c>
       <c r="AC23" s="106" t="s">
-        <v>402</v>
+        <v>401</v>
       </c>
       <c r="AD23" s="106" t="s">
-        <v>424</v>
+        <v>423</v>
       </c>
       <c r="AE23" s="106" t="s">
-        <v>428</v>
+        <v>427</v>
       </c>
       <c r="AF23" s="106" t="s">
-        <v>426</v>
+        <v>425</v>
       </c>
       <c r="AG23" s="4"/>
       <c r="AH23" s="4"/>
@@ -16763,58 +16763,58 @@
         <v/>
       </c>
       <c r="BB23" t="s">
+        <v>571</v>
+      </c>
+      <c r="BC23" t="s">
+        <v>570</v>
+      </c>
+      <c r="BD23" t="s">
+        <v>570</v>
+      </c>
+      <c r="BE23" t="s">
         <v>572</v>
       </c>
-      <c r="BC23" t="s">
-        <v>571</v>
-      </c>
-      <c r="BD23" t="s">
-        <v>571</v>
-      </c>
-      <c r="BE23" t="s">
-        <v>573</v>
-      </c>
       <c r="BF23" t="s">
-        <v>571</v>
+        <v>570</v>
       </c>
       <c r="BG23" t="s">
-        <v>571</v>
+        <v>570</v>
       </c>
       <c r="BH23" t="s">
-        <v>573</v>
+        <v>572</v>
       </c>
       <c r="BI23" t="s">
-        <v>571</v>
+        <v>570</v>
       </c>
       <c r="BJ23" t="s">
-        <v>571</v>
+        <v>570</v>
       </c>
       <c r="BK23" t="s">
-        <v>573</v>
+        <v>572</v>
       </c>
       <c r="BL23" t="s">
-        <v>573</v>
+        <v>572</v>
       </c>
       <c r="BM23" t="s">
-        <v>571</v>
+        <v>570</v>
       </c>
       <c r="BN23" t="s">
-        <v>573</v>
+        <v>572</v>
       </c>
       <c r="BO23" t="s">
-        <v>573</v>
+        <v>572</v>
       </c>
       <c r="BP23" t="s">
-        <v>571</v>
+        <v>570</v>
       </c>
       <c r="BQ23" t="s">
-        <v>573</v>
+        <v>572</v>
       </c>
       <c r="BR23" t="s">
-        <v>573</v>
+        <v>572</v>
       </c>
       <c r="BS23" t="s">
-        <v>571</v>
+        <v>570</v>
       </c>
     </row>
     <row r="24" spans="2:71" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
@@ -17126,78 +17126,78 @@
       </c>
     </row>
     <row r="29" spans="2:71" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B29" s="137" t="s">
+      <c r="B29" s="138" t="s">
+        <v>428</v>
+      </c>
+      <c r="C29" s="138"/>
+      <c r="D29" s="138"/>
+      <c r="E29" s="138"/>
+      <c r="F29" s="138"/>
+      <c r="G29" s="138"/>
+      <c r="H29" s="138"/>
+      <c r="I29" s="138"/>
+      <c r="J29" s="138"/>
+      <c r="K29" s="138"/>
+      <c r="L29" s="138"/>
+      <c r="M29" s="138"/>
+      <c r="N29" s="138"/>
+      <c r="O29" s="138"/>
+      <c r="P29" s="138"/>
+      <c r="Q29" s="138"/>
+      <c r="R29" s="138"/>
+      <c r="S29" s="138"/>
+      <c r="T29" s="138"/>
+      <c r="U29" s="138"/>
+      <c r="V29" s="138"/>
+      <c r="W29" s="138"/>
+      <c r="X29" s="138"/>
+      <c r="Y29" s="138"/>
+    </row>
+    <row r="32" spans="2:71" ht="21.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B32" s="137" t="s">
         <v>429</v>
       </c>
-      <c r="C29" s="137"/>
-      <c r="D29" s="137"/>
-      <c r="E29" s="137"/>
-      <c r="F29" s="137"/>
-      <c r="G29" s="137"/>
-      <c r="H29" s="137"/>
-      <c r="I29" s="137"/>
-      <c r="J29" s="137"/>
-      <c r="K29" s="137"/>
-      <c r="L29" s="137"/>
-      <c r="M29" s="137"/>
-      <c r="N29" s="137"/>
-      <c r="O29" s="137"/>
-      <c r="P29" s="137"/>
-      <c r="Q29" s="137"/>
-      <c r="R29" s="137"/>
-      <c r="S29" s="137"/>
-      <c r="T29" s="137"/>
-      <c r="U29" s="137"/>
-      <c r="V29" s="137"/>
-      <c r="W29" s="137"/>
-      <c r="X29" s="137"/>
-      <c r="Y29" s="137"/>
-    </row>
-    <row r="32" spans="2:71" ht="21.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B32" s="139" t="s">
+      <c r="C32" s="137"/>
+      <c r="D32" s="137"/>
+      <c r="E32" s="137"/>
+      <c r="F32" s="137"/>
+      <c r="G32" s="137"/>
+      <c r="H32" s="137"/>
+      <c r="I32" s="137"/>
+      <c r="J32" s="137"/>
+      <c r="K32" s="137"/>
+      <c r="L32" s="137"/>
+      <c r="M32" s="137"/>
+      <c r="N32" s="137"/>
+      <c r="O32" s="137"/>
+      <c r="P32" s="137"/>
+      <c r="Q32" s="137"/>
+      <c r="R32" s="137"/>
+      <c r="S32" s="137"/>
+      <c r="T32" s="137"/>
+    </row>
+    <row r="33" spans="2:25" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B33" s="138" t="s">
         <v>430</v>
       </c>
-      <c r="C32" s="139"/>
-      <c r="D32" s="139"/>
-      <c r="E32" s="139"/>
-      <c r="F32" s="139"/>
-      <c r="G32" s="139"/>
-      <c r="H32" s="139"/>
-      <c r="I32" s="139"/>
-      <c r="J32" s="139"/>
-      <c r="K32" s="139"/>
-      <c r="L32" s="139"/>
-      <c r="M32" s="139"/>
-      <c r="N32" s="139"/>
-      <c r="O32" s="139"/>
-      <c r="P32" s="139"/>
-      <c r="Q32" s="139"/>
-      <c r="R32" s="139"/>
-      <c r="S32" s="139"/>
-      <c r="T32" s="139"/>
-    </row>
-    <row r="33" spans="2:25" ht="30" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B33" s="137" t="s">
-        <v>431</v>
-      </c>
-      <c r="C33" s="137"/>
-      <c r="D33" s="137"/>
-      <c r="E33" s="137"/>
-      <c r="F33" s="137"/>
-      <c r="G33" s="137"/>
-      <c r="H33" s="137"/>
-      <c r="I33" s="137"/>
-      <c r="J33" s="137"/>
-      <c r="K33" s="137"/>
-      <c r="L33" s="137"/>
-      <c r="M33" s="137"/>
-      <c r="N33" s="137"/>
-      <c r="O33" s="137"/>
-      <c r="P33" s="137"/>
-      <c r="Q33" s="137"/>
-      <c r="R33" s="137"/>
-      <c r="S33" s="137"/>
-      <c r="T33" s="137"/>
+      <c r="C33" s="138"/>
+      <c r="D33" s="138"/>
+      <c r="E33" s="138"/>
+      <c r="F33" s="138"/>
+      <c r="G33" s="138"/>
+      <c r="H33" s="138"/>
+      <c r="I33" s="138"/>
+      <c r="J33" s="138"/>
+      <c r="K33" s="138"/>
+      <c r="L33" s="138"/>
+      <c r="M33" s="138"/>
+      <c r="N33" s="138"/>
+      <c r="O33" s="138"/>
+      <c r="P33" s="138"/>
+      <c r="Q33" s="138"/>
+      <c r="R33" s="138"/>
+      <c r="S33" s="138"/>
+      <c r="T33" s="138"/>
       <c r="U33" s="104"/>
       <c r="V33" s="104"/>
       <c r="W33" s="104"/>
@@ -17205,43 +17205,43 @@
       <c r="Y33" s="104"/>
     </row>
     <row r="35" spans="2:25" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B35" s="144" t="s">
+      <c r="B35" s="141" t="s">
+        <v>431</v>
+      </c>
+      <c r="C35" s="141"/>
+      <c r="D35" s="141"/>
+      <c r="E35" s="141"/>
+      <c r="I35" s="141" t="s">
         <v>432</v>
       </c>
-      <c r="C35" s="144"/>
-      <c r="D35" s="144"/>
-      <c r="E35" s="144"/>
-      <c r="I35" s="144" t="s">
-        <v>433</v>
-      </c>
-      <c r="J35" s="144"/>
-      <c r="K35" s="144"/>
-      <c r="L35" s="144"/>
+      <c r="J35" s="141"/>
+      <c r="K35" s="141"/>
+      <c r="L35" s="141"/>
     </row>
     <row r="36" spans="2:25" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B36" s="111" t="s">
+        <v>433</v>
+      </c>
+      <c r="C36" s="111" t="s">
         <v>434</v>
       </c>
-      <c r="C36" s="111" t="s">
+      <c r="D36" s="111" t="s">
         <v>435</v>
       </c>
-      <c r="D36" s="111" t="s">
-        <v>436</v>
-      </c>
       <c r="E36" s="111" t="s">
-        <v>590</v>
+        <v>589</v>
       </c>
       <c r="I36" s="111" t="s">
+        <v>433</v>
+      </c>
+      <c r="J36" s="111" t="s">
         <v>434</v>
       </c>
-      <c r="J36" s="111" t="s">
+      <c r="K36" s="111" t="s">
         <v>435</v>
       </c>
-      <c r="K36" s="111" t="s">
-        <v>436</v>
-      </c>
       <c r="L36" s="111" t="s">
-        <v>590</v>
+        <v>589</v>
       </c>
     </row>
     <row r="37" spans="2:25" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -17525,43 +17525,43 @@
       <c r="L50" s="112"/>
     </row>
     <row r="53" spans="2:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B53" s="144" t="s">
+      <c r="B53" s="141" t="s">
+        <v>436</v>
+      </c>
+      <c r="C53" s="141"/>
+      <c r="D53" s="141"/>
+      <c r="E53" s="141"/>
+      <c r="I53" s="141" t="s">
         <v>437</v>
       </c>
-      <c r="C53" s="144"/>
-      <c r="D53" s="144"/>
-      <c r="E53" s="144"/>
-      <c r="I53" s="144" t="s">
-        <v>438</v>
-      </c>
-      <c r="J53" s="144"/>
-      <c r="K53" s="144"/>
-      <c r="L53" s="144"/>
+      <c r="J53" s="141"/>
+      <c r="K53" s="141"/>
+      <c r="L53" s="141"/>
     </row>
     <row r="54" spans="2:12" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B54" s="111" t="s">
+        <v>433</v>
+      </c>
+      <c r="C54" s="111" t="s">
         <v>434</v>
       </c>
-      <c r="C54" s="111" t="s">
+      <c r="D54" s="111" t="s">
         <v>435</v>
       </c>
-      <c r="D54" s="111" t="s">
-        <v>436</v>
-      </c>
       <c r="E54" s="111" t="s">
-        <v>590</v>
+        <v>589</v>
       </c>
       <c r="I54" s="111" t="s">
+        <v>433</v>
+      </c>
+      <c r="J54" s="111" t="s">
         <v>434</v>
       </c>
-      <c r="J54" s="111" t="s">
+      <c r="K54" s="111" t="s">
         <v>435</v>
       </c>
-      <c r="K54" s="111" t="s">
-        <v>436</v>
-      </c>
       <c r="L54" s="111" t="s">
-        <v>590</v>
+        <v>589</v>
       </c>
     </row>
     <row r="55" spans="2:12" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -17901,10 +17901,10 @@
       <c r="L69" s="112"/>
     </row>
     <row r="70" spans="2:12" x14ac:dyDescent="0.25">
-      <c r="B70" s="180"/>
-      <c r="C70" s="180"/>
-      <c r="D70" s="180"/>
-      <c r="E70" s="180"/>
+      <c r="B70" s="135"/>
+      <c r="C70" s="135"/>
+      <c r="D70" s="135"/>
+      <c r="E70" s="135"/>
       <c r="I70" s="112">
         <v>170</v>
       </c>
@@ -17915,43 +17915,43 @@
       <c r="L70" s="112"/>
     </row>
     <row r="72" spans="2:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B72" s="144" t="s">
+      <c r="B72" s="141" t="s">
+        <v>438</v>
+      </c>
+      <c r="C72" s="141"/>
+      <c r="D72" s="141"/>
+      <c r="E72" s="141"/>
+      <c r="I72" s="141" t="s">
         <v>439</v>
       </c>
-      <c r="C72" s="144"/>
-      <c r="D72" s="144"/>
-      <c r="E72" s="144"/>
-      <c r="I72" s="144" t="s">
-        <v>440</v>
-      </c>
-      <c r="J72" s="144"/>
-      <c r="K72" s="144"/>
-      <c r="L72" s="144"/>
+      <c r="J72" s="141"/>
+      <c r="K72" s="141"/>
+      <c r="L72" s="141"/>
     </row>
     <row r="73" spans="2:12" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B73" s="111" t="s">
+        <v>433</v>
+      </c>
+      <c r="C73" s="111" t="s">
         <v>434</v>
       </c>
-      <c r="C73" s="111" t="s">
+      <c r="D73" s="111" t="s">
         <v>435</v>
       </c>
-      <c r="D73" s="111" t="s">
-        <v>436</v>
-      </c>
       <c r="E73" s="111" t="s">
-        <v>590</v>
+        <v>589</v>
       </c>
       <c r="I73" s="111" t="s">
+        <v>433</v>
+      </c>
+      <c r="J73" s="111" t="s">
         <v>434</v>
       </c>
-      <c r="J73" s="111" t="s">
+      <c r="K73" s="111" t="s">
         <v>435</v>
       </c>
-      <c r="K73" s="111" t="s">
-        <v>436</v>
-      </c>
       <c r="L73" s="111" t="s">
-        <v>590</v>
+        <v>589</v>
       </c>
     </row>
     <row r="74" spans="2:12" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -18283,96 +18283,96 @@
       <c r="L87" s="112"/>
     </row>
     <row r="92" spans="2:20" ht="21.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B92" s="139" t="s">
+      <c r="B92" s="137" t="s">
+        <v>440</v>
+      </c>
+      <c r="C92" s="137"/>
+      <c r="D92" s="137"/>
+      <c r="E92" s="137"/>
+      <c r="F92" s="137"/>
+      <c r="G92" s="137"/>
+      <c r="H92" s="137"/>
+      <c r="I92" s="137"/>
+      <c r="J92" s="137"/>
+      <c r="K92" s="137"/>
+      <c r="L92" s="137"/>
+      <c r="M92" s="137"/>
+      <c r="N92" s="137"/>
+      <c r="O92" s="137"/>
+      <c r="P92" s="137"/>
+      <c r="Q92" s="137"/>
+      <c r="R92" s="137"/>
+      <c r="S92" s="137"/>
+      <c r="T92" s="137"/>
+    </row>
+    <row r="93" spans="2:20" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B93" s="138" t="s">
         <v>441</v>
       </c>
-      <c r="C92" s="139"/>
-      <c r="D92" s="139"/>
-      <c r="E92" s="139"/>
-      <c r="F92" s="139"/>
-      <c r="G92" s="139"/>
-      <c r="H92" s="139"/>
-      <c r="I92" s="139"/>
-      <c r="J92" s="139"/>
-      <c r="K92" s="139"/>
-      <c r="L92" s="139"/>
-      <c r="M92" s="139"/>
-      <c r="N92" s="139"/>
-      <c r="O92" s="139"/>
-      <c r="P92" s="139"/>
-      <c r="Q92" s="139"/>
-      <c r="R92" s="139"/>
-      <c r="S92" s="139"/>
-      <c r="T92" s="139"/>
-    </row>
-    <row r="93" spans="2:20" ht="30" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B93" s="137" t="s">
-        <v>442</v>
-      </c>
-      <c r="C93" s="137"/>
-      <c r="D93" s="137"/>
-      <c r="E93" s="137"/>
-      <c r="F93" s="137"/>
-      <c r="G93" s="137"/>
-      <c r="H93" s="137"/>
-      <c r="I93" s="137"/>
-      <c r="J93" s="137"/>
-      <c r="K93" s="137"/>
-      <c r="L93" s="137"/>
-      <c r="M93" s="137"/>
-      <c r="N93" s="137"/>
-      <c r="O93" s="137"/>
-      <c r="P93" s="137"/>
-      <c r="Q93" s="137"/>
-      <c r="R93" s="137"/>
-      <c r="S93" s="137"/>
-      <c r="T93" s="137"/>
+      <c r="C93" s="138"/>
+      <c r="D93" s="138"/>
+      <c r="E93" s="138"/>
+      <c r="F93" s="138"/>
+      <c r="G93" s="138"/>
+      <c r="H93" s="138"/>
+      <c r="I93" s="138"/>
+      <c r="J93" s="138"/>
+      <c r="K93" s="138"/>
+      <c r="L93" s="138"/>
+      <c r="M93" s="138"/>
+      <c r="N93" s="138"/>
+      <c r="O93" s="138"/>
+      <c r="P93" s="138"/>
+      <c r="Q93" s="138"/>
+      <c r="R93" s="138"/>
+      <c r="S93" s="138"/>
+      <c r="T93" s="138"/>
     </row>
     <row r="94" spans="2:20" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B94" s="137"/>
-      <c r="C94" s="137"/>
-      <c r="D94" s="137"/>
-      <c r="E94" s="137"/>
-      <c r="F94" s="137"/>
-      <c r="G94" s="137"/>
-      <c r="H94" s="137"/>
-      <c r="I94" s="137"/>
-      <c r="J94" s="137"/>
-      <c r="K94" s="137"/>
-      <c r="L94" s="137"/>
-      <c r="M94" s="137"/>
-      <c r="N94" s="137"/>
-      <c r="O94" s="137"/>
-      <c r="P94" s="137"/>
-      <c r="Q94" s="137"/>
-      <c r="R94" s="137"/>
-      <c r="S94" s="137"/>
-      <c r="T94" s="137"/>
+      <c r="B94" s="138"/>
+      <c r="C94" s="138"/>
+      <c r="D94" s="138"/>
+      <c r="E94" s="138"/>
+      <c r="F94" s="138"/>
+      <c r="G94" s="138"/>
+      <c r="H94" s="138"/>
+      <c r="I94" s="138"/>
+      <c r="J94" s="138"/>
+      <c r="K94" s="138"/>
+      <c r="L94" s="138"/>
+      <c r="M94" s="138"/>
+      <c r="N94" s="138"/>
+      <c r="O94" s="138"/>
+      <c r="P94" s="138"/>
+      <c r="Q94" s="138"/>
+      <c r="R94" s="138"/>
+      <c r="S94" s="138"/>
+      <c r="T94" s="138"/>
     </row>
     <row r="95" spans="2:20" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B95" s="33" t="s">
-        <v>371</v>
-      </c>
-      <c r="C95" s="145" t="s">
+        <v>370</v>
+      </c>
+      <c r="C95" s="140" t="s">
+        <v>442</v>
+      </c>
+      <c r="D95" s="140"/>
+      <c r="E95" s="140" t="s">
         <v>443</v>
       </c>
-      <c r="D95" s="145"/>
-      <c r="E95" s="145" t="s">
+      <c r="F95" s="140"/>
+      <c r="G95" s="140" t="s">
         <v>444</v>
       </c>
-      <c r="F95" s="145"/>
-      <c r="G95" s="145" t="s">
+      <c r="H95" s="140"/>
+      <c r="I95" s="140" t="s">
         <v>445</v>
       </c>
-      <c r="H95" s="145"/>
-      <c r="I95" s="145" t="s">
+      <c r="J95" s="140"/>
+      <c r="K95" s="140" t="s">
         <v>446</v>
       </c>
-      <c r="J95" s="145"/>
-      <c r="K95" s="145" t="s">
-        <v>447</v>
-      </c>
-      <c r="L95" s="145"/>
+      <c r="L95" s="140"/>
     </row>
     <row r="96" spans="2:20" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B96" s="109">
@@ -18585,81 +18585,81 @@
       </c>
     </row>
     <row r="104" spans="2:20" ht="21.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B104" s="139" t="s">
+      <c r="B104" s="137" t="s">
+        <v>447</v>
+      </c>
+      <c r="C104" s="137"/>
+      <c r="D104" s="137"/>
+      <c r="E104" s="137"/>
+      <c r="F104" s="137"/>
+      <c r="G104" s="137"/>
+      <c r="H104" s="137"/>
+      <c r="I104" s="137"/>
+      <c r="J104" s="137"/>
+      <c r="K104" s="137"/>
+      <c r="L104" s="137"/>
+      <c r="M104" s="137"/>
+      <c r="N104" s="137"/>
+      <c r="O104" s="137"/>
+      <c r="P104" s="137"/>
+      <c r="Q104" s="137"/>
+      <c r="R104" s="137"/>
+      <c r="S104" s="137"/>
+      <c r="T104" s="137"/>
+    </row>
+    <row r="105" spans="2:20" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B105" s="138" t="s">
         <v>448</v>
       </c>
-      <c r="C104" s="139"/>
-      <c r="D104" s="139"/>
-      <c r="E104" s="139"/>
-      <c r="F104" s="139"/>
-      <c r="G104" s="139"/>
-      <c r="H104" s="139"/>
-      <c r="I104" s="139"/>
-      <c r="J104" s="139"/>
-      <c r="K104" s="139"/>
-      <c r="L104" s="139"/>
-      <c r="M104" s="139"/>
-      <c r="N104" s="139"/>
-      <c r="O104" s="139"/>
-      <c r="P104" s="139"/>
-      <c r="Q104" s="139"/>
-      <c r="R104" s="139"/>
-      <c r="S104" s="139"/>
-      <c r="T104" s="139"/>
-    </row>
-    <row r="105" spans="2:20" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B105" s="137" t="s">
-        <v>449</v>
-      </c>
-      <c r="C105" s="137"/>
-      <c r="D105" s="137"/>
-      <c r="E105" s="137"/>
-      <c r="F105" s="137"/>
-      <c r="G105" s="137"/>
-      <c r="H105" s="137"/>
-      <c r="I105" s="137"/>
-      <c r="J105" s="137"/>
-      <c r="K105" s="137"/>
-      <c r="L105" s="137"/>
-      <c r="M105" s="137"/>
-      <c r="N105" s="137"/>
-      <c r="O105" s="137"/>
-      <c r="P105" s="137"/>
-      <c r="Q105" s="137"/>
-      <c r="R105" s="137"/>
-      <c r="S105" s="137"/>
-      <c r="T105" s="137"/>
+      <c r="C105" s="138"/>
+      <c r="D105" s="138"/>
+      <c r="E105" s="138"/>
+      <c r="F105" s="138"/>
+      <c r="G105" s="138"/>
+      <c r="H105" s="138"/>
+      <c r="I105" s="138"/>
+      <c r="J105" s="138"/>
+      <c r="K105" s="138"/>
+      <c r="L105" s="138"/>
+      <c r="M105" s="138"/>
+      <c r="N105" s="138"/>
+      <c r="O105" s="138"/>
+      <c r="P105" s="138"/>
+      <c r="Q105" s="138"/>
+      <c r="R105" s="138"/>
+      <c r="S105" s="138"/>
+      <c r="T105" s="138"/>
     </row>
     <row r="106" spans="2:20" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B106" s="137"/>
-      <c r="C106" s="137"/>
-      <c r="D106" s="137"/>
-      <c r="E106" s="137"/>
-      <c r="F106" s="137"/>
-      <c r="G106" s="137"/>
-      <c r="H106" s="137"/>
-      <c r="I106" s="137"/>
-      <c r="J106" s="137"/>
-      <c r="K106" s="137"/>
-      <c r="L106" s="137"/>
-      <c r="M106" s="137"/>
-      <c r="N106" s="137"/>
-      <c r="O106" s="137"/>
-      <c r="P106" s="137"/>
-      <c r="Q106" s="137"/>
-      <c r="R106" s="137"/>
-      <c r="S106" s="137"/>
-      <c r="T106" s="137"/>
+      <c r="B106" s="138"/>
+      <c r="C106" s="138"/>
+      <c r="D106" s="138"/>
+      <c r="E106" s="138"/>
+      <c r="F106" s="138"/>
+      <c r="G106" s="138"/>
+      <c r="H106" s="138"/>
+      <c r="I106" s="138"/>
+      <c r="J106" s="138"/>
+      <c r="K106" s="138"/>
+      <c r="L106" s="138"/>
+      <c r="M106" s="138"/>
+      <c r="N106" s="138"/>
+      <c r="O106" s="138"/>
+      <c r="P106" s="138"/>
+      <c r="Q106" s="138"/>
+      <c r="R106" s="138"/>
+      <c r="S106" s="138"/>
+      <c r="T106" s="138"/>
     </row>
     <row r="107" spans="2:20" ht="27.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B107" s="33" t="s">
+        <v>449</v>
+      </c>
+      <c r="C107" s="33" t="s">
         <v>450</v>
       </c>
-      <c r="C107" s="33" t="s">
-        <v>451</v>
-      </c>
       <c r="D107" s="33" t="s">
-        <v>371</v>
+        <v>370</v>
       </c>
     </row>
     <row r="108" spans="2:20" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -18729,46 +18729,46 @@
       </c>
     </row>
     <row r="116" spans="2:20" ht="21.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B116" s="139" t="s">
-        <v>452</v>
-      </c>
-      <c r="C116" s="139"/>
-      <c r="D116" s="139"/>
-      <c r="E116" s="139"/>
-      <c r="F116" s="139"/>
-      <c r="G116" s="139"/>
-      <c r="H116" s="139"/>
-      <c r="I116" s="139"/>
-      <c r="J116" s="139"/>
-      <c r="K116" s="139"/>
-      <c r="L116" s="139"/>
-      <c r="M116" s="139"/>
-      <c r="N116" s="139"/>
-      <c r="O116" s="139"/>
-      <c r="P116" s="139"/>
-      <c r="Q116" s="139"/>
-      <c r="R116" s="139"/>
-      <c r="S116" s="139"/>
-      <c r="T116" s="139"/>
+      <c r="B116" s="137" t="s">
+        <v>451</v>
+      </c>
+      <c r="C116" s="137"/>
+      <c r="D116" s="137"/>
+      <c r="E116" s="137"/>
+      <c r="F116" s="137"/>
+      <c r="G116" s="137"/>
+      <c r="H116" s="137"/>
+      <c r="I116" s="137"/>
+      <c r="J116" s="137"/>
+      <c r="K116" s="137"/>
+      <c r="L116" s="137"/>
+      <c r="M116" s="137"/>
+      <c r="N116" s="137"/>
+      <c r="O116" s="137"/>
+      <c r="P116" s="137"/>
+      <c r="Q116" s="137"/>
+      <c r="R116" s="137"/>
+      <c r="S116" s="137"/>
+      <c r="T116" s="137"/>
     </row>
     <row r="118" spans="2:20" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B118" s="33" t="s">
+        <v>452</v>
+      </c>
+      <c r="C118" s="33" t="s">
+        <v>366</v>
+      </c>
+      <c r="D118" s="139" t="s">
         <v>453</v>
       </c>
-      <c r="C118" s="33" t="s">
-        <v>367</v>
-      </c>
-      <c r="D118" s="142" t="s">
+      <c r="E118" s="139"/>
+      <c r="F118" s="139" t="s">
         <v>454</v>
       </c>
-      <c r="E118" s="142"/>
-      <c r="F118" s="142" t="s">
-        <v>455</v>
-      </c>
-      <c r="G118" s="142"/>
-      <c r="H118" s="142"/>
-      <c r="I118" s="142"/>
-      <c r="J118" s="142"/>
+      <c r="G118" s="139"/>
+      <c r="H118" s="139"/>
+      <c r="I118" s="139"/>
+      <c r="J118" s="139"/>
     </row>
     <row r="119" spans="2:20" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B119" s="13">
@@ -18777,17 +18777,17 @@
       <c r="C119" s="12">
         <v>30</v>
       </c>
-      <c r="D119" s="146" t="s">
+      <c r="D119" s="136" t="s">
+        <v>455</v>
+      </c>
+      <c r="E119" s="136"/>
+      <c r="F119" s="136" t="s">
         <v>456</v>
       </c>
-      <c r="E119" s="146"/>
-      <c r="F119" s="146" t="s">
-        <v>457</v>
-      </c>
-      <c r="G119" s="146"/>
-      <c r="H119" s="146"/>
-      <c r="I119" s="146"/>
-      <c r="J119" s="146"/>
+      <c r="G119" s="136"/>
+      <c r="H119" s="136"/>
+      <c r="I119" s="136"/>
+      <c r="J119" s="136"/>
     </row>
     <row r="120" spans="2:20" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B120" s="13">
@@ -18796,17 +18796,17 @@
       <c r="C120" s="12">
         <v>45</v>
       </c>
-      <c r="D120" s="146" t="s">
+      <c r="D120" s="136" t="s">
+        <v>457</v>
+      </c>
+      <c r="E120" s="136"/>
+      <c r="F120" s="136" t="s">
         <v>458</v>
       </c>
-      <c r="E120" s="146"/>
-      <c r="F120" s="146" t="s">
-        <v>459</v>
-      </c>
-      <c r="G120" s="146"/>
-      <c r="H120" s="146"/>
-      <c r="I120" s="146"/>
-      <c r="J120" s="146"/>
+      <c r="G120" s="136"/>
+      <c r="H120" s="136"/>
+      <c r="I120" s="136"/>
+      <c r="J120" s="136"/>
     </row>
     <row r="121" spans="2:20" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B121" s="13">
@@ -18815,17 +18815,17 @@
       <c r="C121" s="12">
         <v>60</v>
       </c>
-      <c r="D121" s="146" t="s">
+      <c r="D121" s="136" t="s">
+        <v>459</v>
+      </c>
+      <c r="E121" s="136"/>
+      <c r="F121" s="136" t="s">
         <v>460</v>
       </c>
-      <c r="E121" s="146"/>
-      <c r="F121" s="146" t="s">
-        <v>461</v>
-      </c>
-      <c r="G121" s="146"/>
-      <c r="H121" s="146"/>
-      <c r="I121" s="146"/>
-      <c r="J121" s="146"/>
+      <c r="G121" s="136"/>
+      <c r="H121" s="136"/>
+      <c r="I121" s="136"/>
+      <c r="J121" s="136"/>
     </row>
     <row r="122" spans="2:20" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B122" s="13">
@@ -18834,17 +18834,17 @@
       <c r="C122" s="12">
         <v>80</v>
       </c>
-      <c r="D122" s="146" t="s">
+      <c r="D122" s="136" t="s">
+        <v>461</v>
+      </c>
+      <c r="E122" s="136"/>
+      <c r="F122" s="136" t="s">
         <v>462</v>
       </c>
-      <c r="E122" s="146"/>
-      <c r="F122" s="146" t="s">
-        <v>463</v>
-      </c>
-      <c r="G122" s="146"/>
-      <c r="H122" s="146"/>
-      <c r="I122" s="146"/>
-      <c r="J122" s="146"/>
+      <c r="G122" s="136"/>
+      <c r="H122" s="136"/>
+      <c r="I122" s="136"/>
+      <c r="J122" s="136"/>
     </row>
     <row r="123" spans="2:20" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B123" s="13">
@@ -18853,17 +18853,17 @@
       <c r="C123" s="12">
         <v>120</v>
       </c>
-      <c r="D123" s="146" t="s">
+      <c r="D123" s="136" t="s">
+        <v>463</v>
+      </c>
+      <c r="E123" s="136"/>
+      <c r="F123" s="136" t="s">
         <v>464</v>
       </c>
-      <c r="E123" s="146"/>
-      <c r="F123" s="146" t="s">
-        <v>465</v>
-      </c>
-      <c r="G123" s="146"/>
-      <c r="H123" s="146"/>
-      <c r="I123" s="146"/>
-      <c r="J123" s="146"/>
+      <c r="G123" s="136"/>
+      <c r="H123" s="136"/>
+      <c r="I123" s="136"/>
+      <c r="J123" s="136"/>
     </row>
     <row r="124" spans="2:20" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B124" s="13">
@@ -18872,53 +18872,26 @@
       <c r="C124" s="12">
         <v>150</v>
       </c>
-      <c r="D124" s="146" t="s">
+      <c r="D124" s="136" t="s">
+        <v>465</v>
+      </c>
+      <c r="E124" s="136"/>
+      <c r="F124" s="136" t="s">
         <v>466</v>
       </c>
-      <c r="E124" s="146"/>
-      <c r="F124" s="146" t="s">
-        <v>467</v>
-      </c>
-      <c r="G124" s="146"/>
-      <c r="H124" s="146"/>
-      <c r="I124" s="146"/>
-      <c r="J124" s="146"/>
+      <c r="G124" s="136"/>
+      <c r="H124" s="136"/>
+      <c r="I124" s="136"/>
+      <c r="J124" s="136"/>
     </row>
   </sheetData>
   <mergeCells count="47">
-    <mergeCell ref="D122:E122"/>
-    <mergeCell ref="F122:J122"/>
-    <mergeCell ref="D123:E123"/>
-    <mergeCell ref="F123:J123"/>
-    <mergeCell ref="D124:E124"/>
-    <mergeCell ref="F124:J124"/>
-    <mergeCell ref="D119:E119"/>
-    <mergeCell ref="F119:J119"/>
-    <mergeCell ref="D120:E120"/>
-    <mergeCell ref="F120:J120"/>
-    <mergeCell ref="D121:E121"/>
-    <mergeCell ref="F121:J121"/>
-    <mergeCell ref="B104:T104"/>
-    <mergeCell ref="B105:T106"/>
-    <mergeCell ref="B116:T116"/>
-    <mergeCell ref="D118:E118"/>
-    <mergeCell ref="F118:J118"/>
-    <mergeCell ref="B93:T94"/>
-    <mergeCell ref="C95:D95"/>
-    <mergeCell ref="E95:F95"/>
-    <mergeCell ref="G95:H95"/>
-    <mergeCell ref="I95:J95"/>
-    <mergeCell ref="K95:L95"/>
-    <mergeCell ref="B53:E53"/>
-    <mergeCell ref="I53:L53"/>
-    <mergeCell ref="B72:E72"/>
-    <mergeCell ref="I72:L72"/>
-    <mergeCell ref="B92:T92"/>
-    <mergeCell ref="B29:Y29"/>
-    <mergeCell ref="B32:T32"/>
-    <mergeCell ref="B33:T33"/>
-    <mergeCell ref="B35:E35"/>
-    <mergeCell ref="I35:L35"/>
+    <mergeCell ref="B1:T1"/>
+    <mergeCell ref="AA1:BA1"/>
+    <mergeCell ref="B2:T4"/>
+    <mergeCell ref="AA2:BA3"/>
+    <mergeCell ref="B5:T5"/>
+    <mergeCell ref="V5:Y5"/>
     <mergeCell ref="B6:T7"/>
     <mergeCell ref="B8:B9"/>
     <mergeCell ref="C8:E8"/>
@@ -18927,12 +18900,39 @@
     <mergeCell ref="L8:N8"/>
     <mergeCell ref="O8:Q8"/>
     <mergeCell ref="R8:T8"/>
-    <mergeCell ref="B1:T1"/>
-    <mergeCell ref="AA1:BA1"/>
-    <mergeCell ref="B2:T4"/>
-    <mergeCell ref="AA2:BA3"/>
-    <mergeCell ref="B5:T5"/>
-    <mergeCell ref="V5:Y5"/>
+    <mergeCell ref="B29:Y29"/>
+    <mergeCell ref="B32:T32"/>
+    <mergeCell ref="B33:T33"/>
+    <mergeCell ref="B35:E35"/>
+    <mergeCell ref="I35:L35"/>
+    <mergeCell ref="B53:E53"/>
+    <mergeCell ref="I53:L53"/>
+    <mergeCell ref="B72:E72"/>
+    <mergeCell ref="I72:L72"/>
+    <mergeCell ref="B92:T92"/>
+    <mergeCell ref="B93:T94"/>
+    <mergeCell ref="C95:D95"/>
+    <mergeCell ref="E95:F95"/>
+    <mergeCell ref="G95:H95"/>
+    <mergeCell ref="I95:J95"/>
+    <mergeCell ref="K95:L95"/>
+    <mergeCell ref="B104:T104"/>
+    <mergeCell ref="B105:T106"/>
+    <mergeCell ref="B116:T116"/>
+    <mergeCell ref="D118:E118"/>
+    <mergeCell ref="F118:J118"/>
+    <mergeCell ref="D119:E119"/>
+    <mergeCell ref="F119:J119"/>
+    <mergeCell ref="D120:E120"/>
+    <mergeCell ref="F120:J120"/>
+    <mergeCell ref="D121:E121"/>
+    <mergeCell ref="F121:J121"/>
+    <mergeCell ref="D122:E122"/>
+    <mergeCell ref="F122:J122"/>
+    <mergeCell ref="D123:E123"/>
+    <mergeCell ref="F123:J123"/>
+    <mergeCell ref="D124:E124"/>
+    <mergeCell ref="F124:J124"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300"/>
@@ -18952,17 +18952,17 @@
   </cols>
   <sheetData>
     <row r="1" spans="2:6" ht="27.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B1" s="175" t="s">
-        <v>468</v>
-      </c>
-      <c r="C1" s="175"/>
-      <c r="D1" s="175"/>
-      <c r="E1" s="175"/>
-      <c r="F1" s="175"/>
+      <c r="B1" s="180" t="s">
+        <v>467</v>
+      </c>
+      <c r="C1" s="180"/>
+      <c r="D1" s="180"/>
+      <c r="E1" s="180"/>
+      <c r="F1" s="180"/>
     </row>
     <row r="3" spans="2:6" ht="45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B3" s="176" t="s">
-        <v>469</v>
+        <v>468</v>
       </c>
       <c r="C3" s="176"/>
       <c r="D3" s="176"/>
@@ -18970,35 +18970,35 @@
       <c r="F3" s="176"/>
     </row>
     <row r="5" spans="2:6" ht="25.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B5" s="177" t="s">
+      <c r="B5" s="179" t="s">
+        <v>469</v>
+      </c>
+      <c r="C5" s="179"/>
+      <c r="D5" s="179"/>
+      <c r="E5" s="179"/>
+      <c r="F5" s="179"/>
+    </row>
+    <row r="6" spans="2:6" ht="49.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B6" s="177" t="s">
         <v>470</v>
       </c>
-      <c r="C5" s="177"/>
-      <c r="D5" s="177"/>
-      <c r="E5" s="177"/>
-      <c r="F5" s="177"/>
-    </row>
-    <row r="6" spans="2:6" ht="49.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B6" s="178" t="s">
+      <c r="C6" s="177"/>
+      <c r="D6" s="177"/>
+      <c r="E6" s="177"/>
+      <c r="F6" s="177"/>
+    </row>
+    <row r="8" spans="2:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B8" s="178" t="s">
         <v>471</v>
       </c>
-      <c r="C6" s="178"/>
-      <c r="D6" s="178"/>
-      <c r="E6" s="178"/>
-      <c r="F6" s="178"/>
-    </row>
-    <row r="8" spans="2:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B8" s="179" t="s">
-        <v>472</v>
-      </c>
-      <c r="C8" s="179"/>
-      <c r="D8" s="179"/>
-      <c r="E8" s="179"/>
-      <c r="F8" s="179"/>
+      <c r="C8" s="178"/>
+      <c r="D8" s="178"/>
+      <c r="E8" s="178"/>
+      <c r="F8" s="178"/>
     </row>
     <row r="9" spans="2:6" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B9" s="113" t="s">
-        <v>371</v>
+        <v>370</v>
       </c>
       <c r="C9" s="114">
         <v>10</v>
@@ -19006,7 +19006,7 @@
     </row>
     <row r="10" spans="2:6" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B10" s="113" t="s">
-        <v>367</v>
+        <v>366</v>
       </c>
       <c r="C10" s="114">
         <v>30</v>
@@ -19022,7 +19022,7 @@
     </row>
     <row r="12" spans="2:6" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B12" s="113" t="s">
-        <v>473</v>
+        <v>472</v>
       </c>
       <c r="C12" s="114" t="s">
         <v>152</v>
@@ -19030,73 +19030,73 @@
     </row>
     <row r="13" spans="2:6" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B13" s="113" t="s">
-        <v>474</v>
+        <v>473</v>
       </c>
       <c r="C13" s="114" t="s">
         <v>293</v>
       </c>
     </row>
     <row r="15" spans="2:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B15" s="179" t="s">
-        <v>475</v>
-      </c>
-      <c r="C15" s="179"/>
-      <c r="D15" s="179"/>
-      <c r="E15" s="179"/>
-      <c r="F15" s="179"/>
+      <c r="B15" s="178" t="s">
+        <v>474</v>
+      </c>
+      <c r="C15" s="178"/>
+      <c r="D15" s="178"/>
+      <c r="E15" s="178"/>
+      <c r="F15" s="178"/>
     </row>
     <row r="16" spans="2:6" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B16" s="113" t="s">
-        <v>391</v>
+        <v>390</v>
       </c>
       <c r="C16" s="115" t="s">
-        <v>476</v>
+        <v>475</v>
       </c>
     </row>
     <row r="17" spans="2:6" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B17" s="113" t="s">
+        <v>476</v>
+      </c>
+      <c r="C17" s="115" t="s">
         <v>477</v>
-      </c>
-      <c r="C17" s="115" t="s">
-        <v>478</v>
       </c>
     </row>
     <row r="18" spans="2:6" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B18" s="113" t="s">
+        <v>478</v>
+      </c>
+      <c r="C18" s="115" t="s">
         <v>479</v>
       </c>
-      <c r="C18" s="115" t="s">
+    </row>
+    <row r="20" spans="2:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B20" s="178" t="s">
         <v>480</v>
       </c>
-    </row>
-    <row r="20" spans="2:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B20" s="179" t="s">
-        <v>481</v>
-      </c>
-      <c r="C20" s="179"/>
-      <c r="D20" s="179"/>
-      <c r="E20" s="179"/>
-      <c r="F20" s="179"/>
+      <c r="C20" s="178"/>
+      <c r="D20" s="178"/>
+      <c r="E20" s="178"/>
+      <c r="F20" s="178"/>
     </row>
     <row r="21" spans="2:6" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B21" s="113" t="s">
-        <v>391</v>
+        <v>390</v>
       </c>
       <c r="C21" s="116" t="s">
-        <v>482</v>
+        <v>481</v>
       </c>
     </row>
     <row r="22" spans="2:6" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B22" s="113" t="s">
+        <v>482</v>
+      </c>
+      <c r="C22" s="116" t="s">
         <v>483</v>
-      </c>
-      <c r="C22" s="116" t="s">
-        <v>484</v>
       </c>
     </row>
     <row r="24" spans="2:6" ht="54.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B24" s="176" t="s">
-        <v>485</v>
+        <v>484</v>
       </c>
       <c r="C24" s="176"/>
       <c r="D24" s="176"/>
@@ -19104,35 +19104,35 @@
       <c r="F24" s="176"/>
     </row>
     <row r="27" spans="2:6" ht="25.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B27" s="177" t="s">
+      <c r="B27" s="179" t="s">
+        <v>485</v>
+      </c>
+      <c r="C27" s="179"/>
+      <c r="D27" s="179"/>
+      <c r="E27" s="179"/>
+      <c r="F27" s="179"/>
+    </row>
+    <row r="28" spans="2:6" ht="49.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B28" s="177" t="s">
         <v>486</v>
       </c>
-      <c r="C27" s="177"/>
-      <c r="D27" s="177"/>
-      <c r="E27" s="177"/>
-      <c r="F27" s="177"/>
-    </row>
-    <row r="28" spans="2:6" ht="49.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B28" s="178" t="s">
-        <v>487</v>
-      </c>
-      <c r="C28" s="178"/>
-      <c r="D28" s="178"/>
-      <c r="E28" s="178"/>
-      <c r="F28" s="178"/>
+      <c r="C28" s="177"/>
+      <c r="D28" s="177"/>
+      <c r="E28" s="177"/>
+      <c r="F28" s="177"/>
     </row>
     <row r="30" spans="2:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B30" s="179" t="s">
-        <v>472</v>
-      </c>
-      <c r="C30" s="179"/>
-      <c r="D30" s="179"/>
-      <c r="E30" s="179"/>
-      <c r="F30" s="179"/>
+      <c r="B30" s="178" t="s">
+        <v>471</v>
+      </c>
+      <c r="C30" s="178"/>
+      <c r="D30" s="178"/>
+      <c r="E30" s="178"/>
+      <c r="F30" s="178"/>
     </row>
     <row r="31" spans="2:6" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B31" s="113" t="s">
-        <v>371</v>
+        <v>370</v>
       </c>
       <c r="C31" s="114">
         <v>5</v>
@@ -19140,7 +19140,7 @@
     </row>
     <row r="32" spans="2:6" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B32" s="113" t="s">
-        <v>367</v>
+        <v>366</v>
       </c>
       <c r="C32" s="114">
         <v>80</v>
@@ -19156,7 +19156,7 @@
     </row>
     <row r="34" spans="2:6" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B34" s="113" t="s">
-        <v>473</v>
+        <v>472</v>
       </c>
       <c r="C34" s="114" t="s">
         <v>152</v>
@@ -19164,73 +19164,73 @@
     </row>
     <row r="35" spans="2:6" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B35" s="113" t="s">
-        <v>474</v>
+        <v>473</v>
       </c>
       <c r="C35" s="114" t="s">
         <v>293</v>
       </c>
     </row>
     <row r="37" spans="2:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B37" s="179" t="s">
-        <v>475</v>
-      </c>
-      <c r="C37" s="179"/>
-      <c r="D37" s="179"/>
-      <c r="E37" s="179"/>
-      <c r="F37" s="179"/>
+      <c r="B37" s="178" t="s">
+        <v>474</v>
+      </c>
+      <c r="C37" s="178"/>
+      <c r="D37" s="178"/>
+      <c r="E37" s="178"/>
+      <c r="F37" s="178"/>
     </row>
     <row r="38" spans="2:6" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B38" s="113" t="s">
-        <v>391</v>
+        <v>390</v>
       </c>
       <c r="C38" s="115" t="s">
-        <v>488</v>
+        <v>487</v>
       </c>
     </row>
     <row r="39" spans="2:6" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B39" s="113" t="s">
-        <v>477</v>
+        <v>476</v>
       </c>
       <c r="C39" s="115" t="s">
-        <v>489</v>
+        <v>488</v>
       </c>
     </row>
     <row r="40" spans="2:6" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B40" s="113" t="s">
+        <v>489</v>
+      </c>
+      <c r="C40" s="115" t="s">
         <v>490</v>
       </c>
-      <c r="C40" s="115" t="s">
-        <v>491</v>
-      </c>
     </row>
     <row r="42" spans="2:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B42" s="179" t="s">
-        <v>481</v>
-      </c>
-      <c r="C42" s="179"/>
-      <c r="D42" s="179"/>
-      <c r="E42" s="179"/>
-      <c r="F42" s="179"/>
+      <c r="B42" s="178" t="s">
+        <v>480</v>
+      </c>
+      <c r="C42" s="178"/>
+      <c r="D42" s="178"/>
+      <c r="E42" s="178"/>
+      <c r="F42" s="178"/>
     </row>
     <row r="43" spans="2:6" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B43" s="113" t="s">
-        <v>391</v>
+        <v>390</v>
       </c>
       <c r="C43" s="116" t="s">
-        <v>492</v>
+        <v>491</v>
       </c>
     </row>
     <row r="44" spans="2:6" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B44" s="113" t="s">
-        <v>483</v>
+        <v>482</v>
       </c>
       <c r="C44" s="116" t="s">
-        <v>493</v>
+        <v>492</v>
       </c>
     </row>
     <row r="46" spans="2:6" ht="54.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B46" s="176" t="s">
-        <v>494</v>
+        <v>493</v>
       </c>
       <c r="C46" s="176"/>
       <c r="D46" s="176"/>
@@ -19238,35 +19238,35 @@
       <c r="F46" s="176"/>
     </row>
     <row r="49" spans="2:13" ht="25.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B49" s="177" t="s">
+      <c r="B49" s="179" t="s">
+        <v>494</v>
+      </c>
+      <c r="C49" s="179"/>
+      <c r="D49" s="179"/>
+      <c r="E49" s="179"/>
+      <c r="F49" s="179"/>
+    </row>
+    <row r="50" spans="2:13" ht="49.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B50" s="177" t="s">
         <v>495</v>
       </c>
-      <c r="C49" s="177"/>
-      <c r="D49" s="177"/>
-      <c r="E49" s="177"/>
-      <c r="F49" s="177"/>
-    </row>
-    <row r="50" spans="2:13" ht="49.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B50" s="178" t="s">
-        <v>496</v>
-      </c>
-      <c r="C50" s="178"/>
-      <c r="D50" s="178"/>
-      <c r="E50" s="178"/>
-      <c r="F50" s="178"/>
+      <c r="C50" s="177"/>
+      <c r="D50" s="177"/>
+      <c r="E50" s="177"/>
+      <c r="F50" s="177"/>
     </row>
     <row r="52" spans="2:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B52" s="179" t="s">
-        <v>472</v>
-      </c>
-      <c r="C52" s="179"/>
-      <c r="D52" s="179"/>
-      <c r="E52" s="179"/>
-      <c r="F52" s="179"/>
+      <c r="B52" s="178" t="s">
+        <v>471</v>
+      </c>
+      <c r="C52" s="178"/>
+      <c r="D52" s="178"/>
+      <c r="E52" s="178"/>
+      <c r="F52" s="178"/>
     </row>
     <row r="53" spans="2:13" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B53" s="113" t="s">
-        <v>371</v>
+        <v>370</v>
       </c>
       <c r="C53" s="114">
         <v>10</v>
@@ -19279,7 +19279,7 @@
     </row>
     <row r="54" spans="2:13" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B54" s="113" t="s">
-        <v>367</v>
+        <v>366</v>
       </c>
       <c r="C54" s="114">
         <v>120</v>
@@ -19296,29 +19296,29 @@
       </c>
       <c r="I55" s="117"/>
       <c r="K55" t="s">
-        <v>509</v>
+        <v>508</v>
       </c>
       <c r="M55" s="118"/>
     </row>
     <row r="56" spans="2:13" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B56" s="113" t="s">
-        <v>473</v>
+        <v>472</v>
       </c>
       <c r="C56" s="114" t="s">
-        <v>497</v>
+        <v>496</v>
       </c>
       <c r="I56" s="117" t="s">
-        <v>510</v>
+        <v>509</v>
       </c>
       <c r="J56" s="119"/>
       <c r="K56" t="s">
-        <v>514</v>
+        <v>513</v>
       </c>
       <c r="M56" s="118"/>
     </row>
     <row r="57" spans="2:13" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B57" s="113" t="s">
-        <v>474</v>
+        <v>473</v>
       </c>
       <c r="C57" s="114" t="s">
         <v>293</v>
@@ -19326,7 +19326,7 @@
       <c r="I57" s="117"/>
       <c r="J57" s="120"/>
       <c r="K57" t="s">
-        <v>515</v>
+        <v>514</v>
       </c>
       <c r="M57" s="118"/>
     </row>
@@ -19339,28 +19339,28 @@
       <c r="M58" s="118"/>
     </row>
     <row r="59" spans="2:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B59" s="179" t="s">
-        <v>475</v>
-      </c>
-      <c r="C59" s="179"/>
-      <c r="D59" s="179"/>
-      <c r="E59" s="179"/>
-      <c r="F59" s="179"/>
+      <c r="B59" s="178" t="s">
+        <v>474</v>
+      </c>
+      <c r="C59" s="178"/>
+      <c r="D59" s="178"/>
+      <c r="E59" s="178"/>
+      <c r="F59" s="178"/>
       <c r="I59" s="117" t="s">
-        <v>511</v>
+        <v>510</v>
       </c>
       <c r="J59" s="120"/>
       <c r="K59" t="s">
-        <v>515</v>
+        <v>514</v>
       </c>
       <c r="M59" s="118"/>
     </row>
     <row r="60" spans="2:13" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B60" s="113" t="s">
-        <v>391</v>
+        <v>390</v>
       </c>
       <c r="C60" s="115" t="s">
-        <v>498</v>
+        <v>497</v>
       </c>
       <c r="I60" s="117"/>
       <c r="J60" s="122"/>
@@ -19371,27 +19371,27 @@
     </row>
     <row r="61" spans="2:13" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B61" s="113" t="s">
-        <v>479</v>
+        <v>478</v>
       </c>
       <c r="C61" s="115" t="s">
-        <v>499</v>
+        <v>498</v>
       </c>
       <c r="I61" s="117"/>
       <c r="J61" s="122"/>
       <c r="K61" t="s">
-        <v>512</v>
+        <v>511</v>
       </c>
       <c r="M61" s="118"/>
     </row>
     <row r="62" spans="2:13" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B62" s="113" t="s">
-        <v>477</v>
+        <v>476</v>
       </c>
       <c r="C62" s="115" t="s">
-        <v>500</v>
+        <v>499</v>
       </c>
       <c r="I62" s="123" t="s">
-        <v>513</v>
+        <v>512</v>
       </c>
       <c r="J62" s="124"/>
       <c r="K62" s="124"/>
@@ -19400,48 +19400,48 @@
     </row>
     <row r="63" spans="2:13" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B63" s="113" t="s">
+        <v>500</v>
+      </c>
+      <c r="C63" s="115" t="s">
         <v>501</v>
-      </c>
-      <c r="C63" s="115" t="s">
-        <v>502</v>
       </c>
     </row>
     <row r="64" spans="2:13" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B64" s="113" t="s">
+        <v>502</v>
+      </c>
+      <c r="C64" s="115" t="s">
         <v>503</v>
       </c>
-      <c r="C64" s="115" t="s">
-        <v>504</v>
-      </c>
     </row>
     <row r="66" spans="2:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B66" s="179" t="s">
-        <v>481</v>
-      </c>
-      <c r="C66" s="179"/>
-      <c r="D66" s="179"/>
-      <c r="E66" s="179"/>
-      <c r="F66" s="179"/>
+      <c r="B66" s="178" t="s">
+        <v>480</v>
+      </c>
+      <c r="C66" s="178"/>
+      <c r="D66" s="178"/>
+      <c r="E66" s="178"/>
+      <c r="F66" s="178"/>
     </row>
     <row r="67" spans="2:11" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B67" s="113" t="s">
-        <v>391</v>
+        <v>390</v>
       </c>
       <c r="C67" s="116" t="s">
-        <v>505</v>
+        <v>504</v>
       </c>
     </row>
     <row r="68" spans="2:11" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B68" s="113" t="s">
-        <v>483</v>
+        <v>482</v>
       </c>
       <c r="C68" s="116" t="s">
-        <v>482</v>
+        <v>481</v>
       </c>
     </row>
     <row r="70" spans="2:11" ht="54.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B70" s="176" t="s">
-        <v>506</v>
+        <v>505</v>
       </c>
       <c r="C70" s="176"/>
       <c r="D70" s="176"/>
@@ -19450,39 +19450,39 @@
     </row>
     <row r="73" spans="2:11" ht="49.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B73" s="176" t="s">
-        <v>507</v>
+        <v>506</v>
       </c>
       <c r="C73" s="176"/>
       <c r="D73" s="176"/>
       <c r="E73" s="176"/>
       <c r="F73" s="176"/>
       <c r="K73" t="s">
-        <v>560</v>
+        <v>559</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="21">
+    <mergeCell ref="B1:F1"/>
+    <mergeCell ref="B3:F3"/>
+    <mergeCell ref="B5:F5"/>
+    <mergeCell ref="B6:F6"/>
+    <mergeCell ref="B8:F8"/>
+    <mergeCell ref="B15:F15"/>
+    <mergeCell ref="B20:F20"/>
+    <mergeCell ref="B24:F24"/>
+    <mergeCell ref="B27:F27"/>
+    <mergeCell ref="B28:F28"/>
+    <mergeCell ref="B30:F30"/>
+    <mergeCell ref="B37:F37"/>
+    <mergeCell ref="B42:F42"/>
+    <mergeCell ref="B46:F46"/>
+    <mergeCell ref="B49:F49"/>
     <mergeCell ref="B73:F73"/>
     <mergeCell ref="B50:F50"/>
     <mergeCell ref="B52:F52"/>
     <mergeCell ref="B59:F59"/>
     <mergeCell ref="B66:F66"/>
     <mergeCell ref="B70:F70"/>
-    <mergeCell ref="B30:F30"/>
-    <mergeCell ref="B37:F37"/>
-    <mergeCell ref="B42:F42"/>
-    <mergeCell ref="B46:F46"/>
-    <mergeCell ref="B49:F49"/>
-    <mergeCell ref="B15:F15"/>
-    <mergeCell ref="B20:F20"/>
-    <mergeCell ref="B24:F24"/>
-    <mergeCell ref="B27:F27"/>
-    <mergeCell ref="B28:F28"/>
-    <mergeCell ref="B1:F1"/>
-    <mergeCell ref="B3:F3"/>
-    <mergeCell ref="B5:F5"/>
-    <mergeCell ref="B6:F6"/>
-    <mergeCell ref="B8:F8"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300"/>
@@ -19490,26 +19490,6 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
-</file>
-
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement>
-    <lcf76f155ced4ddcb4097134ff3c332f xmlns="3c9f7625-f508-4699-980b-15a788d55c32">
-      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    </lcf76f155ced4ddcb4097134ff3c332f>
-    <TaxCatchAll xmlns="41c9fafd-c058-44f8-b2ce-53cd3afba157" xsi:nil="true"/>
-  </documentManagement>
-</p:properties>
-</file>
-
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x010100A8CC43999E69B146B21FD7037336070D" ma:contentTypeVersion="19" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="da949df7407854784e825555ef0470b6">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="3c9f7625-f508-4699-980b-15a788d55c32" xmlns:ns3="41c9fafd-c058-44f8-b2ce-53cd3afba157" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="15818a7baaa05f324ff0ec0f28430cf1" ns2:_="" ns3:_="">
     <xsd:import namespace="3c9f7625-f508-4699-980b-15a788d55c32"/>
@@ -19770,10 +19750,41 @@
 </ct:contentTypeSchema>
 </file>
 
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement>
+    <lcf76f155ced4ddcb4097134ff3c332f xmlns="3c9f7625-f508-4699-980b-15a788d55c32">
+      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    </lcf76f155ced4ddcb4097134ff3c332f>
+    <TaxCatchAll xmlns="41c9fafd-c058-44f8-b2ce-53cd3afba157" xsi:nil="true"/>
+  </documentManagement>
+</p:properties>
+</file>
+
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
+</file>
+
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{D5EDC946-FEBD-4BE9-AB68-AD52BD9E01B2}">
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{58E0CC4F-D9F7-4393-B9E6-E46F295174BA}">
   <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes"/>
+    <ds:schemaRef ds:uri="http://www.w3.org/2001/XMLSchema"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="3c9f7625-f508-4699-980b-15a788d55c32"/>
+    <ds:schemaRef ds:uri="41c9fafd-c058-44f8-b2ce-53cd3afba157"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/internal/obd"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
 </file>
@@ -19790,20 +19801,9 @@
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{58E0CC4F-D9F7-4393-B9E6-E46F295174BA}">
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{D5EDC946-FEBD-4BE9-AB68-AD52BD9E01B2}">
   <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes"/>
-    <ds:schemaRef ds:uri="http://www.w3.org/2001/XMLSchema"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="3c9f7625-f508-4699-980b-15a788d55c32"/>
-    <ds:schemaRef ds:uri="41c9fafd-c058-44f8-b2ce-53cd3afba157"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/internal/obd"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
 </file>